--- a/research/traditional_assets/database/data/south_korea/south_korea_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ51"/>
+  <dimension ref="A1:AQ46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1995</v>
+        <v>0.124</v>
       </c>
       <c r="E2">
-        <v>0.469</v>
+        <v>0.705</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,103 +600,103 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.001086795435459171</v>
+        <v>-0.0005337896610241782</v>
       </c>
       <c r="J2">
-        <v>-0.001012278845427905</v>
+        <v>-0.0004655883964642663</v>
       </c>
       <c r="K2">
-        <v>440.005</v>
+        <v>324.646</v>
       </c>
       <c r="L2">
-        <v>0.8050428040054083</v>
+        <v>0.4195948626945651</v>
       </c>
       <c r="M2">
-        <v>18.45786</v>
+        <v>45.42424</v>
       </c>
       <c r="N2">
-        <v>0.005866193333502835</v>
+        <v>0.01951070583333691</v>
       </c>
       <c r="O2">
-        <v>0.04194920512266906</v>
+        <v>0.1399192967108789</v>
       </c>
       <c r="P2">
-        <v>15.38786</v>
+        <v>19.16624</v>
       </c>
       <c r="Q2">
-        <v>0.004890499860161196</v>
+        <v>0.00823231980482525</v>
       </c>
       <c r="R2">
-        <v>0.03497201168168544</v>
+        <v>0.05903735145358329</v>
       </c>
       <c r="S2">
-        <v>3.07</v>
+        <v>26.258</v>
       </c>
       <c r="T2">
-        <v>0.1663248068844384</v>
+        <v>0.5780614051000083</v>
       </c>
       <c r="U2">
-        <v>237.579</v>
+        <v>199.721</v>
       </c>
       <c r="V2">
-        <v>0.07550628003356132</v>
+        <v>0.08578454322493632</v>
       </c>
       <c r="W2">
-        <v>-0.001351351351351351</v>
+        <v>0.002909863315854644</v>
       </c>
       <c r="X2">
-        <v>0.05004162480682665</v>
+        <v>0.08031357759078919</v>
       </c>
       <c r="Y2">
-        <v>-0.051392976158178</v>
+        <v>-0.07740371427493455</v>
       </c>
       <c r="Z2">
-        <v>0.474204916951823</v>
+        <v>0.3707386377249095</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04753941979295773</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="AC2">
-        <v>-0.04753941979295773</v>
+        <v>-0.07730243933280354</v>
       </c>
       <c r="AD2">
-        <v>183.42</v>
+        <v>177.407</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>183.42</v>
+        <v>177.407</v>
       </c>
       <c r="AG2">
-        <v>-54.15900000000002</v>
+        <v>-22.31399999999999</v>
       </c>
       <c r="AH2">
-        <v>0.05508273521727379</v>
+        <v>0.07080484854386834</v>
       </c>
       <c r="AI2">
-        <v>0.09531876857837734</v>
+        <v>0.07775903277541017</v>
       </c>
       <c r="AJ2">
-        <v>-0.01751402910629266</v>
+        <v>-0.009677100391351407</v>
       </c>
       <c r="AK2">
-        <v>-0.03210942544054934</v>
+        <v>-0.01071873246689365</v>
       </c>
       <c r="AL2">
-        <v>0.273</v>
+        <v>0.54</v>
       </c>
       <c r="AM2">
-        <v>-2.089</v>
+        <v>-5.965</v>
       </c>
       <c r="AO2">
-        <v>-2.175824175824176</v>
+        <v>-0.7648148148148147</v>
       </c>
       <c r="AQ2">
-        <v>0.2843465773097176</v>
+        <v>0.06923721709974853</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kyobo 9 Special Purpose Acquisition Company (KOSDAQ:A331520)</t>
+          <t>Daishin Balance No.10 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A387310)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,23 +715,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G3">
-        <v>-0</v>
-      </c>
-      <c r="H3">
-        <v>-0</v>
-      </c>
-      <c r="I3">
-        <v>-0</v>
-      </c>
-      <c r="J3">
-        <v>-0</v>
-      </c>
       <c r="K3">
-        <v>-0.037</v>
-      </c>
-      <c r="L3">
-        <v>1.423076923076923</v>
+        <v>0.067</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,7 +725,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,70 +734,73 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="V3">
-        <v>0.2177068214804064</v>
+        <v>0.06967741935483872</v>
       </c>
       <c r="W3">
-        <v>-0.005948553054662379</v>
+        <v>0.007502799552071669</v>
       </c>
       <c r="X3">
-        <v>0.05211439137533374</v>
+        <v>0.07865312974488173</v>
       </c>
       <c r="Y3">
-        <v>-0.05806294442999612</v>
+        <v>-0.07115033019281006</v>
       </c>
       <c r="Z3">
-        <v>-0.004347826086956522</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.007757488960496482</v>
       </c>
       <c r="AB3">
-        <v>0.04699562381041848</v>
+        <v>0.07731156925487494</v>
       </c>
       <c r="AC3">
-        <v>-0.04699562381041848</v>
+        <v>-0.06955408029437846</v>
       </c>
       <c r="AD3">
-        <v>1.34</v>
+        <v>0.725</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.34</v>
+        <v>0.725</v>
       </c>
       <c r="AG3">
-        <v>-0.1599999999999999</v>
+        <v>-0.3550000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1628189550425273</v>
+        <v>0.04468412942989214</v>
       </c>
       <c r="AI3">
-        <v>0.180349932705249</v>
+        <v>0.09023024268823895</v>
       </c>
       <c r="AJ3">
-        <v>-0.02377414561664189</v>
+        <v>-0.02344007923407066</v>
       </c>
       <c r="AK3">
-        <v>-0.02698145025295108</v>
+        <v>-0.05104241552839685</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="AM3">
-        <v>-0.031</v>
+        <v>-0.002000000000000002</v>
+      </c>
+      <c r="AO3">
+        <v>0.9848484848484849</v>
       </c>
       <c r="AQ3">
-        <v>-0</v>
+        <v>-32.49999999999997</v>
       </c>
     </row>
     <row r="4">
@@ -823,7 +811,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mirae Asset Daewoo Special Purpose Acquisition Company 3 Co., Ltd. (KOSDAQ:A328380)</t>
+          <t>HMCIB NO.5 Special Purpose Acquisition Company (KOSDAQ:A353060)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -831,23 +819,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G4">
-        <v>-0</v>
-      </c>
-      <c r="H4">
-        <v>-0</v>
-      </c>
-      <c r="I4">
-        <v>-0</v>
-      </c>
-      <c r="J4">
-        <v>-0</v>
-      </c>
       <c r="K4">
-        <v>-0.019</v>
-      </c>
-      <c r="L4">
-        <v>0.5277777777777778</v>
+        <v>0.041</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -856,7 +829,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -865,67 +838,67 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.04</v>
+        <v>1.42</v>
       </c>
       <c r="V4">
-        <v>0.1821428571428572</v>
+        <v>0.1742331288343558</v>
       </c>
       <c r="W4">
-        <v>-0.001743119266055046</v>
+        <v>0.004812206572769953</v>
       </c>
       <c r="X4">
-        <v>0.05151254751846359</v>
+        <v>0.08240460307261063</v>
       </c>
       <c r="Y4">
-        <v>-0.05325566678451864</v>
+        <v>-0.07759239649984068</v>
       </c>
       <c r="Z4">
-        <v>-0.003361344537815125</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04704006979526724</v>
+        <v>0.07603802043370259</v>
       </c>
       <c r="AC4">
-        <v>-0.04704006979526724</v>
+        <v>-0.07603802043370259</v>
       </c>
       <c r="AD4">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AG4">
-        <v>-0.1400000000000001</v>
+        <v>0.02000000000000002</v>
       </c>
       <c r="AH4">
-        <v>0.1450381679389313</v>
+        <v>0.1501564129301355</v>
       </c>
       <c r="AI4">
-        <v>0.1507936507936508</v>
+        <v>0.1696113074204947</v>
       </c>
       <c r="AJ4">
-        <v>-0.01265822784810128</v>
+        <v>0.002447980416156673</v>
       </c>
       <c r="AK4">
-        <v>-0.01325757575757577</v>
+        <v>0.002828854314002831</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.056</v>
+        <v>-0.1</v>
       </c>
       <c r="AQ4">
         <v>-0</v>
@@ -939,7 +912,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hana Financial Fifteenth Special Purpose Acquisition Company (KOSDAQ:A341160)</t>
+          <t>IBKS No.16 Special Purpose Acquisition Company (KOSDAQ:A388790)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -947,23 +920,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G5">
-        <v>-0</v>
-      </c>
-      <c r="H5">
-        <v>-0</v>
-      </c>
-      <c r="I5">
-        <v>-0</v>
-      </c>
-      <c r="J5">
-        <v>-0</v>
-      </c>
       <c r="K5">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="L5">
-        <v>-0.28125</v>
+        <v>-0.036</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -972,7 +930,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -981,67 +939,67 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1.35</v>
+        <v>0.93</v>
       </c>
       <c r="V5">
-        <v>0.1601423487544484</v>
+        <v>0.1522094926350246</v>
       </c>
       <c r="W5">
-        <v>0.001142131979695431</v>
+        <v>-0.006509945750452079</v>
       </c>
       <c r="X5">
-        <v>0.051081206181805</v>
+        <v>0.08154180366359629</v>
       </c>
       <c r="Y5">
-        <v>-0.04993907420210957</v>
+        <v>-0.08805174941404836</v>
       </c>
       <c r="Z5">
-        <v>-0.004123711340206186</v>
+        <v>0</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04707310361083624</v>
+        <v>0.07622446748457111</v>
       </c>
       <c r="AC5">
-        <v>-0.04707310361083624</v>
+        <v>-0.07622446748457111</v>
       </c>
       <c r="AD5">
-        <v>1.28</v>
+        <v>0.897</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.28</v>
+        <v>0.897</v>
       </c>
       <c r="AG5">
-        <v>-0.07000000000000006</v>
+        <v>-0.03300000000000003</v>
       </c>
       <c r="AH5">
-        <v>0.1318228630278064</v>
+        <v>0.1280148423005566</v>
       </c>
       <c r="AI5">
-        <v>0.141280353200883</v>
+        <v>0.1652846876727474</v>
       </c>
       <c r="AJ5">
-        <v>-0.008373205741626802</v>
+        <v>-0.005430311008721414</v>
       </c>
       <c r="AK5">
-        <v>-0.009079118028534379</v>
+        <v>-0.007338225483655777</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.059</v>
+        <v>-0.065</v>
       </c>
       <c r="AQ5">
         <v>-0</v>
@@ -1055,7 +1013,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ebest Ian Special Purpose Acquisition 1 Company (KOSDAQ:A323210)</t>
+          <t>KB No.20 Special Purpose Acquisition Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1063,23 +1021,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G6">
-        <v>-0</v>
-      </c>
-      <c r="H6">
-        <v>-0</v>
-      </c>
-      <c r="I6">
-        <v>-0</v>
-      </c>
-      <c r="J6">
-        <v>-0</v>
-      </c>
       <c r="K6">
-        <v>0.038</v>
-      </c>
-      <c r="L6">
-        <v>-1.407407407407407</v>
+        <v>0.014</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1103,61 +1046,61 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.054</v>
+        <v>0.089</v>
       </c>
       <c r="V6">
-        <v>0.00989010989010989</v>
+        <v>0.01193029490616622</v>
       </c>
       <c r="W6">
-        <v>0.007156308851224106</v>
+        <v>0.001333333333333333</v>
       </c>
       <c r="X6">
-        <v>0.05084142516511491</v>
+        <v>0.08121203689240122</v>
       </c>
       <c r="Y6">
-        <v>-0.04368511631389081</v>
+        <v>-0.07987870355906788</v>
       </c>
       <c r="Z6">
-        <v>-0.004507512520868113</v>
+        <v>0</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04709191244663731</v>
+        <v>0.07629832062832352</v>
       </c>
       <c r="AC6">
-        <v>-0.04709191244663731</v>
+        <v>-0.07629832062832352</v>
       </c>
       <c r="AD6">
-        <v>0.775</v>
+        <v>1.01</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.775</v>
+        <v>1.01</v>
       </c>
       <c r="AG6">
-        <v>0.721</v>
+        <v>0.921</v>
       </c>
       <c r="AH6">
-        <v>0.1242983159582999</v>
+        <v>0.1192443919716647</v>
       </c>
       <c r="AI6">
-        <v>0.1284175642087821</v>
+        <v>0.1042311661506708</v>
       </c>
       <c r="AJ6">
-        <v>0.116647791619479</v>
+        <v>0.1098914210714712</v>
       </c>
       <c r="AK6">
-        <v>0.120548403277044</v>
+        <v>0.09592750755129675</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-0.102</v>
+        <v>-0.109</v>
       </c>
       <c r="AQ6">
         <v>-0</v>
@@ -1171,7 +1114,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shinyoung HappyTomorrow No.5 Special Purpose Acquisition Company (KOSDAQ:A323280)</t>
+          <t>Leaders Technology Investment Co.,Ltd (KOSDAQ:A019570)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1180,22 +1123,22 @@
         </is>
       </c>
       <c r="G7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>0.019</v>
+        <v>-3.19</v>
       </c>
       <c r="L7">
-        <v>-0.9047619047619047</v>
+        <v>-0.3517089305402425</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1204,7 +1147,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1213,67 +1156,67 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.857</v>
+        <v>2.11</v>
       </c>
       <c r="V7">
-        <v>0.1382258064516129</v>
+        <v>0.05749318801089918</v>
       </c>
       <c r="W7">
-        <v>0.003220338983050847</v>
+        <v>-0.08264248704663212</v>
       </c>
       <c r="X7">
-        <v>0.0508139290085533</v>
+        <v>0.08642972059153353</v>
       </c>
       <c r="Y7">
-        <v>-0.04759359002550245</v>
+        <v>-0.1690722076381657</v>
       </c>
       <c r="Z7">
-        <v>-0.003571428571428572</v>
+        <v>0.1849133537206931</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04709409015037489</v>
+        <v>0.07666703825143154</v>
       </c>
       <c r="AC7">
-        <v>-0.04709409015037489</v>
+        <v>-0.07666703825143154</v>
       </c>
       <c r="AD7">
-        <v>0.873</v>
+        <v>11.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.873</v>
+        <v>11.6</v>
       </c>
       <c r="AG7">
-        <v>0.01600000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="AH7">
-        <v>0.1234271172062774</v>
+        <v>0.2401656314699793</v>
       </c>
       <c r="AI7">
-        <v>0.130240190959272</v>
+        <v>0.2959183673469388</v>
       </c>
       <c r="AJ7">
-        <v>0.002574002574002576</v>
+        <v>0.2054557263476943</v>
       </c>
       <c r="AK7">
-        <v>0.002736914129319195</v>
+        <v>0.2558641143165273</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.073</v>
+        <v>-0.103</v>
       </c>
       <c r="AQ7">
         <v>-0</v>
@@ -1287,7 +1230,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M-Venture Investment, Inc. (KOSDAQ:A019590)</t>
+          <t>NH Special Purpose Acquisition 19 Company (KOSE:A380440)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1295,26 +1238,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.0564</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
       <c r="K8">
-        <v>-7.61</v>
-      </c>
-      <c r="L8">
-        <v>-2.113888888888889</v>
+        <v>0.545</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1323,7 +1248,7 @@
         <v>-0</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P8">
         <v>-0</v>
@@ -1332,70 +1257,73 @@
         <v>-0</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>3.63</v>
+        <v>0.051</v>
       </c>
       <c r="V8">
-        <v>0.03140138408304499</v>
+        <v>0.0006431273644388398</v>
       </c>
       <c r="W8">
-        <v>-0.2454838709677419</v>
+        <v>0.006442080378250592</v>
       </c>
       <c r="X8">
-        <v>0.0505881685499761</v>
+        <v>0.0812716378390541</v>
       </c>
       <c r="Y8">
-        <v>-0.296072039517718</v>
+        <v>-0.07482955746080351</v>
       </c>
       <c r="Z8">
-        <v>0.09669621273166801</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>-0.0003927178579798918</v>
       </c>
       <c r="AB8">
-        <v>0.04711213563659714</v>
+        <v>0.07628486286737239</v>
       </c>
       <c r="AC8">
-        <v>-0.04711213563659714</v>
+        <v>-0.07667758072535229</v>
       </c>
       <c r="AD8">
-        <v>15.2</v>
+        <v>10.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>15.2</v>
+        <v>10.9</v>
       </c>
       <c r="AG8">
-        <v>11.57</v>
+        <v>10.849</v>
       </c>
       <c r="AH8">
-        <v>0.1162079510703364</v>
+        <v>0.1208425720620843</v>
       </c>
       <c r="AI8">
-        <v>0.3254817987152034</v>
+        <v>0.1344019728729963</v>
       </c>
       <c r="AJ8">
-        <v>0.09098057718015257</v>
+        <v>0.1203452062696203</v>
       </c>
       <c r="AK8">
-        <v>0.2686324587880195</v>
+        <v>0.1338572962035312</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>0.252</v>
       </c>
       <c r="AM8">
-        <v>-0.001</v>
+        <v>-0.732</v>
+      </c>
+      <c r="AO8">
+        <v>-0.1904761904761905</v>
       </c>
       <c r="AQ8">
-        <v>-0</v>
+        <v>0.06557377049180328</v>
       </c>
     </row>
     <row r="9">
@@ -1406,7 +1334,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KB No.20 Special Purpose Acquisition Company (KOSDAQ:A342550)</t>
+          <t>T.S. Investment Corporation (KOSDAQ:A246690)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1414,104 +1342,110 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.446</v>
+      </c>
+      <c r="E9">
+        <v>0.746</v>
+      </c>
       <c r="G9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>0.029</v>
+        <v>6.8</v>
       </c>
       <c r="L9">
-        <v>-1.380952380952381</v>
+        <v>0.3756906077348066</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>0.2744</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.005338521400778211</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.04035294117647059</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>0.2744</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.005338521400778211</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.04035294117647059</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>0.135</v>
+        <v>6.29</v>
       </c>
       <c r="V9">
-        <v>0.01205357142857143</v>
+        <v>0.1223735408560311</v>
       </c>
       <c r="W9">
-        <v>0.002710280373831776</v>
+        <v>0.1382113821138211</v>
       </c>
       <c r="X9">
-        <v>0.04999836237413144</v>
+        <v>0.08550480724514203</v>
       </c>
       <c r="Y9">
-        <v>-0.04728808200029967</v>
+        <v>0.05270657486867908</v>
       </c>
       <c r="Z9">
-        <v>-0.001791197543500512</v>
+        <v>0.3524143302180685</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04716071349129743</v>
+        <v>0.076717183148684</v>
       </c>
       <c r="AC9">
-        <v>-0.04716071349129743</v>
+        <v>-0.076717183148684</v>
       </c>
       <c r="AD9">
-        <v>1.2</v>
+        <v>14.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.2</v>
+        <v>14.6</v>
       </c>
       <c r="AG9">
-        <v>1.065</v>
+        <v>8.309999999999999</v>
       </c>
       <c r="AH9">
-        <v>0.09677419354838711</v>
+        <v>0.2212121212121212</v>
       </c>
       <c r="AI9">
-        <v>0.1025641025641026</v>
+        <v>0.2306477093206951</v>
       </c>
       <c r="AJ9">
-        <v>0.08683245006114962</v>
+        <v>0.139172667894825</v>
       </c>
       <c r="AK9">
-        <v>0.09208819714656291</v>
+        <v>0.1457639010699877</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-0.092</v>
-      </c>
-      <c r="AQ9">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1522,7 +1456,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KB No.19 Special Purpose Acquisition Company (KOSDAQ:A330990)</t>
+          <t>Q Capital Partners Co., Ltd. (KOSDAQ:A016600)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1531,22 +1465,22 @@
         </is>
       </c>
       <c r="G10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>-0.032</v>
+        <v>-5.56</v>
       </c>
       <c r="L10">
-        <v>1.777777777777778</v>
+        <v>-18.91156462585034</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1570,64 +1504,61 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0.022</v>
+        <v>0.697</v>
       </c>
       <c r="V10">
-        <v>0.002949061662198391</v>
+        <v>0.01300373134328358</v>
       </c>
       <c r="W10">
-        <v>-0.004526166902404526</v>
+        <v>-0.04951024042742654</v>
       </c>
       <c r="X10">
-        <v>0.04998119658314246</v>
+        <v>0.08301315561444138</v>
       </c>
       <c r="Y10">
-        <v>-0.05450736348554699</v>
+        <v>-0.1325233960418679</v>
       </c>
       <c r="Z10">
-        <v>-0.002307100743399128</v>
+        <v>0.002737940026075619</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04716215932088819</v>
+        <v>0.07686561388748069</v>
       </c>
       <c r="AC10">
-        <v>-0.04716215932088819</v>
+        <v>-0.07686561388748069</v>
       </c>
       <c r="AD10">
-        <v>0.794</v>
+        <v>10.6</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.794</v>
+        <v>10.6</v>
       </c>
       <c r="AG10">
-        <v>0.772</v>
+        <v>9.903</v>
       </c>
       <c r="AH10">
-        <v>0.09619578386236977</v>
+        <v>0.1651090342679128</v>
       </c>
       <c r="AI10">
-        <v>0.1027964785085448</v>
+        <v>0.1038197845249755</v>
       </c>
       <c r="AJ10">
-        <v>0.09378036929057339</v>
+        <v>0.1559453884068469</v>
       </c>
       <c r="AK10">
-        <v>0.1002337055310309</v>
+        <v>0.09765983254933286</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-0.04</v>
-      </c>
-      <c r="AQ10">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1638,7 +1569,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Daishin Balance No.7 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A332290)</t>
+          <t>Globon Co., Ltd. (KOSDAQ:A019660)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1647,22 +1578,22 @@
         </is>
       </c>
       <c r="G11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>-0.082</v>
+        <v>-10.3</v>
       </c>
       <c r="L11">
-        <v>1.171428571428571</v>
+        <v>-3.626760563380282</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1686,61 +1617,61 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>0.282</v>
+        <v>4.2</v>
       </c>
       <c r="V11">
-        <v>0.03022508038585209</v>
+        <v>0.08553971486761711</v>
       </c>
       <c r="W11">
-        <v>-0.00922384701912261</v>
+        <v>-0.6358024691358025</v>
       </c>
       <c r="X11">
-        <v>0.04988243945694172</v>
+        <v>0.08296606190064822</v>
       </c>
       <c r="Y11">
-        <v>-0.05910628647606433</v>
+        <v>-0.7187685310364508</v>
       </c>
       <c r="Z11">
-        <v>-0.00739879505337702</v>
+        <v>0.1476782278612656</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.0471705134799995</v>
+        <v>0.07686862551859609</v>
       </c>
       <c r="AC11">
-        <v>-0.0471705134799995</v>
+        <v>-0.07686862551859609</v>
       </c>
       <c r="AD11">
-        <v>0.955</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0.955</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AG11">
-        <v>0.673</v>
+        <v>5.430000000000001</v>
       </c>
       <c r="AH11">
-        <v>0.09285367039377734</v>
+        <v>0.1639707134343606</v>
       </c>
       <c r="AI11">
-        <v>0.09922077922077922</v>
+        <v>0.3909866017052375</v>
       </c>
       <c r="AJ11">
-        <v>0.06727981605518345</v>
+        <v>0.09957821382725106</v>
       </c>
       <c r="AK11">
-        <v>0.0720325377287809</v>
+        <v>0.2657856093979442</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-0.039</v>
+        <v>-0.757</v>
       </c>
       <c r="AQ11">
         <v>-0</v>
@@ -1754,7 +1685,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shinhan 6th Special Purpose Acquisition Company (KOSDAQ:A333050)</t>
+          <t>DSC Investment Inc. (KOSDAQ:A241520)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1762,101 +1693,107 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D12">
+        <v>0.485</v>
+      </c>
+      <c r="E12">
+        <v>0.705</v>
+      </c>
       <c r="G12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12">
+        <v>18.6</v>
+      </c>
+      <c r="L12">
+        <v>0.6179401993355482</v>
+      </c>
+      <c r="M12">
+        <v>-0</v>
+      </c>
+      <c r="N12">
+        <v>-0</v>
+      </c>
+      <c r="O12">
+        <v>-0</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>-0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>8.1</v>
+      </c>
+      <c r="V12">
+        <v>0.1094594594594595</v>
+      </c>
+      <c r="W12">
+        <v>0.3268892794376099</v>
+      </c>
+      <c r="X12">
+        <v>0.0827266005496208</v>
+      </c>
+      <c r="Y12">
+        <v>0.2441626788879891</v>
+      </c>
+      <c r="Z12">
+        <v>0.4649366697559468</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.07688406694254744</v>
+      </c>
+      <c r="AC12">
+        <v>-0.07688406694254744</v>
+      </c>
+      <c r="AD12">
+        <v>13.9</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>13.9</v>
+      </c>
+      <c r="AG12">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="AH12">
+        <v>0.1581342434584755</v>
+      </c>
+      <c r="AI12">
+        <v>0.1703431372549019</v>
+      </c>
+      <c r="AJ12">
+        <v>0.07268170426065164</v>
+      </c>
+      <c r="AK12">
+        <v>0.07891156462585035</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
         <v>-0.01</v>
-      </c>
-      <c r="L12">
-        <v>0.2083333333333333</v>
-      </c>
-      <c r="M12">
-        <v>-0</v>
-      </c>
-      <c r="N12">
-        <v>-0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>-0</v>
-      </c>
-      <c r="Q12">
-        <v>-0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>1.49</v>
-      </c>
-      <c r="V12">
-        <v>0.1706758304696449</v>
-      </c>
-      <c r="W12">
-        <v>-0.001277139208173691</v>
-      </c>
-      <c r="X12">
-        <v>0.04928416056427659</v>
-      </c>
-      <c r="Y12">
-        <v>-0.05056129977245028</v>
-      </c>
-      <c r="Z12">
-        <v>-0.006917423259835712</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0.04722247484509574</v>
-      </c>
-      <c r="AC12">
-        <v>-0.04722247484509574</v>
-      </c>
-      <c r="AD12">
-        <v>0.678</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0.678</v>
-      </c>
-      <c r="AG12">
-        <v>-0.8119999999999999</v>
-      </c>
-      <c r="AH12">
-        <v>0.07206632653061223</v>
-      </c>
-      <c r="AI12">
-        <v>0.08092623537837193</v>
-      </c>
-      <c r="AJ12">
-        <v>-0.1025511492801212</v>
-      </c>
-      <c r="AK12">
-        <v>-0.1178861788617886</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>-0.056</v>
       </c>
       <c r="AQ12">
         <v>-0</v>
@@ -1870,7 +1807,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Yuanta 5 SPECIAL PURPOSE ACQUISITION CO., LTD. (KOSDAQ:A336060)</t>
+          <t>M-Venture Investment, Inc. (KOSDAQ:A019590)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1878,101 +1815,107 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D13">
+        <v>0.119</v>
+      </c>
       <c r="G13">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>-0.02</v>
+        <v>7.26</v>
       </c>
       <c r="L13">
-        <v>0.689655172413793</v>
+        <v>0.654054054054054</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>0.436</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.004733984799131379</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>0.06005509641873279</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>0.436</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.004733984799131379</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>0.06005509641873279</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
       <c r="U13">
-        <v>0.01</v>
+        <v>1.31</v>
       </c>
       <c r="V13">
-        <v>0.0005917159763313611</v>
+        <v>0.01422366992399566</v>
       </c>
       <c r="W13">
-        <v>-0.00202020202020202</v>
+        <v>0.2304761904761905</v>
       </c>
       <c r="X13">
-        <v>0.04905119668790507</v>
+        <v>0.0826325815857161</v>
       </c>
       <c r="Y13">
-        <v>-0.05107139870810709</v>
+        <v>0.1478436088904744</v>
       </c>
       <c r="Z13">
-        <v>-0.002634687017352593</v>
+        <v>0.2577199907127931</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.04724335807192074</v>
+        <v>0.07689018876553329</v>
       </c>
       <c r="AC13">
-        <v>-0.04724335807192074</v>
+        <v>-0.07689018876553329</v>
       </c>
       <c r="AD13">
-        <v>1.15</v>
+        <v>17</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.15</v>
+        <v>17</v>
       </c>
       <c r="AG13">
-        <v>1.14</v>
+        <v>15.69</v>
       </c>
       <c r="AH13">
-        <v>0.06371191135734072</v>
+        <v>0.155820348304308</v>
       </c>
       <c r="AI13">
-        <v>0.1056985294117647</v>
+        <v>0.275974025974026</v>
       </c>
       <c r="AJ13">
-        <v>0.06319290465631928</v>
+        <v>0.1455608126913443</v>
       </c>
       <c r="AK13">
-        <v>0.1048758049678013</v>
+        <v>0.2602421628794162</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-0.066</v>
+        <v>-0.293</v>
       </c>
       <c r="AQ13">
         <v>-0</v>
@@ -1986,7 +1929,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dyc Co.,Ltd. (KOSDAQ:A310870)</t>
+          <t>NAU IB Capital (KOSDAQ:A293580)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1995,103 +1938,103 @@
         </is>
       </c>
       <c r="G14">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>-0.032</v>
+        <v>7.82</v>
       </c>
       <c r="L14">
-        <v>2.666666666666667</v>
+        <v>0.4418079096045198</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>1.65664</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.01738342077649528</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>0.211846547314578</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>0.97864</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.01026904512067156</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>0.1251457800511509</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>0.6779999999999999</v>
+      </c>
+      <c r="T14">
+        <v>0.4092621209194514</v>
       </c>
       <c r="U14">
-        <v>0.632</v>
+        <v>4.2</v>
       </c>
       <c r="V14">
-        <v>0.01385964912280702</v>
+        <v>0.04407135362014691</v>
       </c>
       <c r="W14">
-        <v>-0.005786618444846293</v>
+        <v>0.1148311306901615</v>
       </c>
       <c r="X14">
-        <v>0.04765019896584332</v>
+        <v>0.08163547880651098</v>
       </c>
       <c r="Y14">
-        <v>-0.05343681741068961</v>
+        <v>0.03319565188365056</v>
       </c>
       <c r="Z14">
-        <v>-0.002269718176659731</v>
+        <v>0.2688335358444715</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.04737733001465276</v>
+        <v>0.07695724586054327</v>
       </c>
       <c r="AC14">
-        <v>-0.04737733001465276</v>
+        <v>-0.07695724586054327</v>
       </c>
       <c r="AD14">
-        <v>0.466</v>
+        <v>14.3</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0.466</v>
+        <v>14.3</v>
       </c>
       <c r="AG14">
-        <v>-0.166</v>
+        <v>10.1</v>
       </c>
       <c r="AH14">
-        <v>0.01011592063560978</v>
+        <v>0.1304744525547445</v>
       </c>
       <c r="AI14">
-        <v>0.07930565010211028</v>
+        <v>0.1866840731070496</v>
       </c>
       <c r="AJ14">
-        <v>-0.003653651450455605</v>
+        <v>0.09582542694497155</v>
       </c>
       <c r="AK14">
-        <v>-0.03165522501906941</v>
+        <v>0.1395027624309392</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-0.036</v>
-      </c>
-      <c r="AQ14">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2102,7 +2045,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Woori Technology Investment Co., Ltd (KOSDAQ:A041190)</t>
+          <t>Mirae Asset Venture Investment Co., Ltd. (KOSDAQ:A100790)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2110,12 +2053,6 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D15">
-        <v>0.159</v>
-      </c>
-      <c r="E15">
-        <v>2.221</v>
-      </c>
       <c r="G15">
         <v>0</v>
       </c>
@@ -2129,91 +2066,91 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>254.5</v>
+        <v>55.6</v>
       </c>
       <c r="L15">
-        <v>124.7549019607843</v>
+        <v>0.2763419483101392</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>5.78</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.03567901234567902</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>0.1039568345323741</v>
       </c>
       <c r="P15">
-        <v>-0</v>
+        <v>2.64</v>
       </c>
       <c r="Q15">
-        <v>-0</v>
+        <v>0.0162962962962963</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0.04748201438848921</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>3.14</v>
+      </c>
+      <c r="T15">
+        <v>0.5432525951557093</v>
       </c>
       <c r="U15">
-        <v>3.76</v>
+        <v>40</v>
       </c>
       <c r="V15">
-        <v>0.006288677036293694</v>
+        <v>0.2469135802469136</v>
       </c>
       <c r="W15">
-        <v>3.406961178045515</v>
+        <v>0.3008658008658008</v>
       </c>
       <c r="X15">
-        <v>0.04740261641241918</v>
+        <v>0.08129528489324243</v>
       </c>
       <c r="Y15">
-        <v>3.359558561633096</v>
+        <v>0.2195705159725584</v>
       </c>
       <c r="Z15">
-        <v>0.0284876413908672</v>
+        <v>1.455618818865167</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.04740261641241918</v>
+        <v>0.07698105537646893</v>
       </c>
       <c r="AC15">
-        <v>-0.04740261641241918</v>
+        <v>-0.07698105537646893</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="AG15">
-        <v>-3.76</v>
+        <v>-17.6</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>0.1214750542299349</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>0.1009918845807033</v>
       </c>
       <c r="AJ15">
-        <v>-0.006328474770256168</v>
+        <v>-0.1218836565096953</v>
       </c>
       <c r="AK15">
-        <v>-0.01144457295915261</v>
+        <v>-0.09680968096809681</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-0.001</v>
-      </c>
-      <c r="AQ15">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2224,7 +2161,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Atinum Investment Co., Ltd (KOSDAQ:A021080)</t>
+          <t>Aju IB Investment Co., Ltd. (KOSDAQ:A027360)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2233,10 +2170,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.259</v>
+        <v>0.00697</v>
       </c>
       <c r="E16">
-        <v>0.387</v>
+        <v>-0.08990000000000001</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2251,94 +2188,91 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>23.8</v>
+        <v>3.9</v>
       </c>
       <c r="L16">
-        <v>0.576271186440678</v>
+        <v>0.1018276762402089</v>
       </c>
       <c r="M16">
-        <v>0.528</v>
+        <v>8.253000000000002</v>
       </c>
       <c r="N16">
-        <v>0.002466137319009809</v>
+        <v>0.03994675701839304</v>
       </c>
       <c r="O16">
-        <v>0.02218487394957983</v>
+        <v>2.116153846153847</v>
       </c>
       <c r="P16">
-        <v>-0</v>
+        <v>8.253000000000002</v>
       </c>
       <c r="Q16">
-        <v>-0</v>
+        <v>0.03994675701839304</v>
       </c>
       <c r="R16">
-        <v>-0</v>
+        <v>2.116153846153847</v>
       </c>
       <c r="S16">
-        <v>0.528</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>34.4</v>
+        <v>11.8</v>
       </c>
       <c r="V16">
-        <v>0.1606725829051845</v>
+        <v>0.05711519845111327</v>
       </c>
       <c r="W16">
-        <v>0.3324022346368715</v>
+        <v>0.01913640824337586</v>
       </c>
       <c r="X16">
-        <v>0.04740261641241918</v>
+        <v>0.08053116518682496</v>
       </c>
       <c r="Y16">
-        <v>0.2849996182244524</v>
+        <v>-0.06139475694344911</v>
       </c>
       <c r="Z16">
-        <v>0.8445807770961146</v>
+        <v>0.1829035339063992</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.04740261641241918</v>
+        <v>0.07703637413212232</v>
       </c>
       <c r="AC16">
-        <v>-0.04740261641241918</v>
+        <v>-0.07703637413212232</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="AG16">
-        <v>-34.4</v>
+        <v>11.3</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>0.1005659555942534</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>0.1201248049921997</v>
       </c>
       <c r="AJ16">
-        <v>-0.1914301613800779</v>
+        <v>0.05185865075722808</v>
       </c>
       <c r="AK16">
-        <v>-0.6209386281588447</v>
+        <v>0.06260387811634349</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-0.233</v>
-      </c>
-      <c r="AQ16">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2349,7 +2283,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SV Investment Corporation (KOSDAQ:A289080)</t>
+          <t>Hanwha Plus No2 Special Purpose Acquisition Company (KOSDAQ:A386580)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2357,104 +2291,89 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
       <c r="K17">
-        <v>9.15</v>
-      </c>
-      <c r="L17">
-        <v>0.3339416058394161</v>
+        <v>-0.012</v>
       </c>
       <c r="M17">
-        <v>2.2344</v>
+        <v>-0</v>
       </c>
       <c r="N17">
-        <v>0.01561425576519916</v>
+        <v>-0</v>
       </c>
       <c r="O17">
-        <v>0.2441967213114754</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>2.2344</v>
+        <v>-0</v>
       </c>
       <c r="Q17">
-        <v>0.01561425576519916</v>
+        <v>-0</v>
       </c>
       <c r="R17">
-        <v>0.2441967213114754</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
       <c r="U17">
-        <v>3.55</v>
+        <v>0.883</v>
       </c>
       <c r="V17">
-        <v>0.02480782669461915</v>
+        <v>0.13023598820059</v>
       </c>
       <c r="W17">
-        <v>0.2010989010989011</v>
+        <v>-0.001807228915662651</v>
       </c>
       <c r="X17">
-        <v>0.04740261641241918</v>
+        <v>0.08034345058099179</v>
       </c>
       <c r="Y17">
-        <v>0.1536962846864819</v>
+        <v>-0.08215067949665444</v>
       </c>
       <c r="Z17">
-        <v>0.6352886621840945</v>
+        <v>0</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.04740261641241918</v>
+        <v>0.07705036907001388</v>
       </c>
       <c r="AC17">
-        <v>-0.04740261641241918</v>
+        <v>-0.07705036907001388</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="AG17">
-        <v>-3.55</v>
+        <v>-0.169</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>0.09527622097678143</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>0.1156462585034014</v>
       </c>
       <c r="AJ17">
-        <v>-0.02543891078466499</v>
+        <v>-0.02556345484798064</v>
       </c>
       <c r="AK17">
-        <v>-0.07357512953367876</v>
+        <v>-0.03194103194103195</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>-0.08699999999999999</v>
+      </c>
+      <c r="AQ17">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -2465,7 +2384,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daesung Private Equity, Inc. (KOSDAQ:A027830)</t>
+          <t>Hana Must Seven Special Purpose Acquisition Company (KOSDAQ:A372290)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2473,29 +2392,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D18">
-        <v>0.114</v>
-      </c>
-      <c r="E18">
-        <v>-0.0556</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
       <c r="K18">
-        <v>1.46</v>
-      </c>
-      <c r="L18">
-        <v>0.1158730158730159</v>
+        <v>0.021</v>
       </c>
       <c r="M18">
         <v>-0</v>
@@ -2519,61 +2417,61 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>8.789999999999999</v>
+        <v>0.967</v>
       </c>
       <c r="V18">
-        <v>0.08878787878787878</v>
+        <v>0.1395382395382395</v>
       </c>
       <c r="W18">
-        <v>0.03194748358862144</v>
+        <v>0.003235747303543914</v>
       </c>
       <c r="X18">
-        <v>0.04740261641241918</v>
+        <v>0.07948591100059457</v>
       </c>
       <c r="Y18">
-        <v>-0.01545513282379774</v>
+        <v>-0.07625016369705066</v>
       </c>
       <c r="Z18">
-        <v>0.3529411764705882</v>
+        <v>0</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.04740261641241918</v>
+        <v>0.07711645387430567</v>
       </c>
       <c r="AC18">
-        <v>-0.04740261641241918</v>
+        <v>-0.07711645387430567</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="AG18">
-        <v>-8.789999999999999</v>
+        <v>-0.4429999999999999</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>0.07029782667024417</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>0.08890397013912453</v>
       </c>
       <c r="AJ18">
-        <v>-0.0974393082806784</v>
+        <v>-0.06829042700786186</v>
       </c>
       <c r="AK18">
-        <v>-0.2337144376495613</v>
+        <v>-0.08991272579663079</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-0.025</v>
+        <v>-0.053</v>
       </c>
       <c r="AQ18">
         <v>-0</v>
@@ -2587,7 +2485,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NAU IB Capital (KOSDAQ:A293580)</t>
+          <t>Company K Partners Limited (KOSDAQ:A307930)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2608,91 +2506,91 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>7.24</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>0.6407079646017699</v>
+        <v>0.591715976331361</v>
       </c>
       <c r="M19">
-        <v>2.06196</v>
+        <v>-0</v>
       </c>
       <c r="N19">
-        <v>0.0253935960591133</v>
+        <v>-0</v>
       </c>
       <c r="O19">
-        <v>0.2848011049723757</v>
+        <v>-0</v>
       </c>
       <c r="P19">
-        <v>1.20396</v>
+        <v>-0</v>
       </c>
       <c r="Q19">
-        <v>0.01482709359605911</v>
+        <v>-0</v>
       </c>
       <c r="R19">
-        <v>0.166292817679558</v>
+        <v>-0</v>
       </c>
       <c r="S19">
-        <v>0.8579999999999999</v>
-      </c>
-      <c r="T19">
-        <v>0.4161089448873886</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>2.26</v>
+        <v>0.634</v>
       </c>
       <c r="V19">
-        <v>0.02783251231527093</v>
+        <v>0.009392592592592593</v>
       </c>
       <c r="W19">
-        <v>0.1145569620253165</v>
+        <v>0.1915708812260536</v>
       </c>
       <c r="X19">
-        <v>0.04740261641241918</v>
+        <v>0.07893665398004032</v>
       </c>
       <c r="Y19">
-        <v>0.06715434561289726</v>
+        <v>0.1126342272460133</v>
       </c>
       <c r="Z19">
-        <v>0.1992242595204514</v>
+        <v>0.3128413024564521</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.04740261641241918</v>
+        <v>0.07716073304555084</v>
       </c>
       <c r="AC19">
-        <v>-0.04740261641241918</v>
+        <v>-0.07716073304555084</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AG19">
-        <v>-2.26</v>
+        <v>3.186</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>0.0535614133482894</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>0.07045370711914423</v>
       </c>
       <c r="AJ19">
-        <v>-0.02862933873828224</v>
+        <v>0.04507257448433918</v>
       </c>
       <c r="AK19">
-        <v>-0.03432563791008506</v>
+        <v>0.05945582801477998</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>-0.004</v>
+      </c>
+      <c r="AQ19">
+        <v>-0</v>
       </c>
     </row>
     <row r="20">
@@ -2703,7 +2601,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lindeman Asia Investment Co., Ltd. (KOSDAQ:A277070)</t>
+          <t>SBI Investment KOREA Co., Ltd. (KOSDAQ:A019550)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2711,6 +2609,9 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D20">
+        <v>0.06</v>
+      </c>
       <c r="G20">
         <v>0</v>
       </c>
@@ -2724,94 +2625,88 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>6.19</v>
+        <v>-1.24</v>
       </c>
       <c r="L20">
-        <v>0.4390070921985816</v>
+        <v>-0.07425149700598803</v>
       </c>
       <c r="M20">
-        <v>2.0956</v>
+        <v>-0</v>
       </c>
       <c r="N20">
-        <v>0.03374557165861514</v>
+        <v>-0</v>
       </c>
       <c r="O20">
-        <v>0.338546042003231</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>0.4256</v>
+        <v>-0</v>
       </c>
       <c r="Q20">
-        <v>0.006853462157809984</v>
+        <v>-0</v>
       </c>
       <c r="R20">
-        <v>0.06875605815831987</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>1.67</v>
-      </c>
-      <c r="T20">
-        <v>0.7969078068333652</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>4.46</v>
+        <v>14.5</v>
       </c>
       <c r="V20">
-        <v>0.0718196457326892</v>
+        <v>0.1068533529845247</v>
       </c>
       <c r="W20">
-        <v>0.1491566265060241</v>
+        <v>-0.01153488372093023</v>
       </c>
       <c r="X20">
-        <v>0.04740261641241918</v>
+        <v>0.07833877064940682</v>
       </c>
       <c r="Y20">
-        <v>0.1017540100936049</v>
+        <v>-0.08987365437033705</v>
       </c>
       <c r="Z20">
-        <v>0.3751995742416179</v>
+        <v>0.15311267993032</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.04740261641241918</v>
+        <v>0.07721078069312629</v>
       </c>
       <c r="AC20">
-        <v>-0.04740261641241918</v>
+        <v>-0.07721078069312629</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="AG20">
-        <v>-4.46</v>
+        <v>-9.629999999999999</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>0.03464466102297788</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>0.05260883655611969</v>
       </c>
       <c r="AJ20">
-        <v>-0.07737682165163082</v>
+        <v>-0.0763861346870786</v>
       </c>
       <c r="AK20">
-        <v>-0.1081474296799224</v>
+        <v>-0.1233508389906494</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-0.018</v>
-      </c>
-      <c r="AQ20">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2822,7 +2717,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Company K Partners Limited (KOSDAQ:A307930)</t>
+          <t>STIC Investments, Inc. (KOSE:A026890)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2830,6 +2725,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D21">
+        <v>0.129</v>
+      </c>
+      <c r="E21">
+        <v>-0.0608</v>
+      </c>
       <c r="G21">
         <v>0</v>
       </c>
@@ -2843,88 +2744,91 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>9.58</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="L21">
-        <v>0.5412429378531074</v>
+        <v>0.4595452141723956</v>
       </c>
       <c r="M21">
-        <v>-0</v>
+        <v>10.8728</v>
       </c>
       <c r="N21">
-        <v>-0</v>
+        <v>0.06978690629011554</v>
       </c>
       <c r="O21">
-        <v>-0</v>
+        <v>0.1251185270425777</v>
       </c>
       <c r="P21">
-        <v>-0</v>
+        <v>3.9728</v>
       </c>
       <c r="Q21">
-        <v>-0</v>
+        <v>0.02549935815147625</v>
       </c>
       <c r="R21">
-        <v>-0</v>
+        <v>0.04571691599539701</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>6.900000000000001</v>
+      </c>
+      <c r="T21">
+        <v>0.6346111397248179</v>
       </c>
       <c r="U21">
-        <v>0.429</v>
+        <v>5.05</v>
       </c>
       <c r="V21">
-        <v>0.00410919540229885</v>
+        <v>0.03241335044929396</v>
       </c>
       <c r="W21">
-        <v>0.2087145969498911</v>
+        <v>0.4906832298136646</v>
       </c>
       <c r="X21">
-        <v>0.04792474922080958</v>
+        <v>0.07735155589132341</v>
       </c>
       <c r="Y21">
-        <v>0.1607898477290815</v>
+        <v>0.4133316739223412</v>
       </c>
       <c r="Z21">
-        <v>0.4207073588134626</v>
+        <v>0.8754629629629629</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.04742294771651235</v>
+        <v>0.07729794694283947</v>
       </c>
       <c r="AC21">
-        <v>-0.04742294771651235</v>
+        <v>-0.07729794694283947</v>
       </c>
       <c r="AD21">
-        <v>2.25</v>
+        <v>0.265</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>2.25</v>
+        <v>0.265</v>
       </c>
       <c r="AG21">
-        <v>1.821</v>
+        <v>-4.785</v>
       </c>
       <c r="AH21">
-        <v>0.02109704641350211</v>
+        <v>0.00169801044436613</v>
       </c>
       <c r="AI21">
-        <v>0.04132231404958678</v>
+        <v>0.001611285075852005</v>
       </c>
       <c r="AJ21">
-        <v>0.01714350269720677</v>
+        <v>-0.03168559414627686</v>
       </c>
       <c r="AK21">
-        <v>0.03370911312267452</v>
+        <v>-0.03001599598532134</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-0.005</v>
+        <v>-2.14</v>
       </c>
       <c r="AQ21">
         <v>-0</v>
@@ -2938,7 +2842,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SBI Investment KOREA Co., Ltd. (KOSDAQ:A019550)</t>
+          <t>Atinum Investment Co., Ltd (KOSDAQ:A021080)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2947,10 +2851,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.229</v>
+        <v>0.713</v>
       </c>
       <c r="E22">
-        <v>1.134</v>
+        <v>0.802</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -2965,19 +2869,19 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>16.5</v>
+        <v>55.5</v>
       </c>
       <c r="L22">
-        <v>0.5830388692579506</v>
+        <v>0.4450681635926223</v>
       </c>
       <c r="M22">
-        <v>-0</v>
+        <v>2.92</v>
       </c>
       <c r="N22">
-        <v>-0</v>
+        <v>0.02997946611909651</v>
       </c>
       <c r="O22">
-        <v>-0</v>
+        <v>0.05261261261261261</v>
       </c>
       <c r="P22">
         <v>-0</v>
@@ -2989,64 +2893,70 @@
         <v>-0</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2.92</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
       </c>
       <c r="U22">
-        <v>4.35</v>
+        <v>30.2</v>
       </c>
       <c r="V22">
-        <v>0.01935914552736983</v>
+        <v>0.3100616016427105</v>
       </c>
       <c r="W22">
-        <v>0.1799345692475463</v>
+        <v>0.6180400890868597</v>
       </c>
       <c r="X22">
-        <v>0.04804090576209049</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="Y22">
-        <v>0.1318936634854558</v>
+        <v>0.5407376497540561</v>
       </c>
       <c r="Z22">
-        <v>0.3041048785729637</v>
+        <v>2.250902527075812</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.0474273546249722</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="AC22">
-        <v>-0.0474273546249722</v>
+        <v>-0.07730243933280354</v>
       </c>
       <c r="AD22">
-        <v>5.92</v>
+        <v>0</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>5.92</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>1.57</v>
+        <v>-30.2</v>
       </c>
       <c r="AH22">
-        <v>0.02566993322348452</v>
+        <v>0</v>
       </c>
       <c r="AI22">
-        <v>0.05219538000352671</v>
+        <v>0</v>
       </c>
       <c r="AJ22">
-        <v>0.006938613161267514</v>
+        <v>-0.4494047619047619</v>
       </c>
       <c r="AK22">
-        <v>0.01439442559823967</v>
+        <v>-0.3370535714285715</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>-0.384</v>
+      </c>
+      <c r="AQ22">
+        <v>-0</v>
       </c>
     </row>
     <row r="23">
@@ -3057,7 +2967,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mirae Asset Venture Investment Co., Ltd. (KOSDAQ:A100790)</t>
+          <t>Daol Investment Co.,Ltd. (KOSDAQ:A298870)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3078,91 +2988,94 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>53.4</v>
+        <v>3.34</v>
       </c>
       <c r="L23">
-        <v>0.2763975155279503</v>
+        <v>0.1546296296296296</v>
       </c>
       <c r="M23">
-        <v>6.0625</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N23">
-        <v>0.01846071863580999</v>
+        <v>0.03547364248910027</v>
       </c>
       <c r="O23">
-        <v>0.1135299625468165</v>
+        <v>2.679640718562874</v>
       </c>
       <c r="P23">
-        <v>6.0625</v>
+        <v>-0</v>
       </c>
       <c r="Q23">
-        <v>0.01846071863580999</v>
+        <v>-0</v>
       </c>
       <c r="R23">
-        <v>0.1135299625468165</v>
+        <v>-0</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23">
-        <v>66.5</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>0.2024969549330085</v>
+        <v>0.03963535473642489</v>
       </c>
       <c r="W23">
-        <v>0.3836206896551724</v>
+        <v>0.0202179176755448</v>
       </c>
       <c r="X23">
-        <v>0.04884118451543877</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="Y23">
-        <v>0.3347795051397336</v>
+        <v>-0.05708452165725874</v>
       </c>
       <c r="Z23">
-        <v>2.303290414878398</v>
+        <v>0.1290399665451939</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.04745663257905704</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="AC23">
-        <v>-0.04745663257905704</v>
+        <v>-0.07730243933280354</v>
       </c>
       <c r="AD23">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>-47</v>
+        <v>-10</v>
       </c>
       <c r="AH23">
-        <v>0.05605058924978443</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>0.09521484375</v>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <v>-0.1670220326936745</v>
+        <v>-0.04127115146512587</v>
       </c>
       <c r="AK23">
-        <v>-0.3398409255242227</v>
+        <v>-0.05277044854881267</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>-0.002</v>
+      </c>
+      <c r="AQ23">
+        <v>-0</v>
       </c>
     </row>
     <row r="24">
@@ -3173,7 +3086,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aju IB Investment Co., Ltd. (KOSDAQ:A027360)</t>
+          <t>Stonebridge Ventures Inc. (KOSDAQ:A330730)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3181,12 +3094,6 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D24">
-        <v>0.17</v>
-      </c>
-      <c r="E24">
-        <v>0.469</v>
-      </c>
       <c r="G24">
         <v>0</v>
       </c>
@@ -3200,91 +3107,94 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>53.7</v>
+        <v>10.4</v>
       </c>
       <c r="L24">
-        <v>0.4881818181818182</v>
+        <v>0.3741007194244604</v>
       </c>
       <c r="M24">
-        <v>4.914000000000001</v>
+        <v>2.25</v>
       </c>
       <c r="N24">
-        <v>0.01249745676500509</v>
+        <v>0.03488372093023256</v>
       </c>
       <c r="O24">
-        <v>0.09150837988826817</v>
+        <v>0.2163461538461538</v>
       </c>
       <c r="P24">
-        <v>4.914000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q24">
-        <v>0.01249745676500509</v>
+        <v>-0</v>
       </c>
       <c r="R24">
-        <v>0.09150837988826817</v>
+        <v>-0</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24">
-        <v>28.9</v>
+        <v>7.33</v>
       </c>
       <c r="V24">
-        <v>0.07349949135300102</v>
+        <v>0.1136434108527132</v>
       </c>
       <c r="W24">
-        <v>0.3431309904153355</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="X24">
-        <v>0.04952832902602892</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="Y24">
-        <v>0.2936026613893065</v>
+        <v>0.1278257657954016</v>
       </c>
       <c r="Z24">
-        <v>0.6084070796460177</v>
+        <v>0.6414397784956161</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.04748035263309618</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="AC24">
-        <v>-0.04748035263309618</v>
+        <v>-0.07730243933280354</v>
       </c>
       <c r="AD24">
-        <v>34.5</v>
+        <v>0</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>34.5</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>5.600000000000001</v>
+        <v>-7.33</v>
       </c>
       <c r="AH24">
-        <v>0.08066401683422961</v>
+        <v>0</v>
       </c>
       <c r="AI24">
-        <v>0.1447754930759547</v>
+        <v>0</v>
       </c>
       <c r="AJ24">
-        <v>0.01404212637913742</v>
+        <v>-0.1282140983033059</v>
       </c>
       <c r="AK24">
-        <v>0.02674307545367718</v>
+        <v>-0.1307294453361869</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>-0.289</v>
+      </c>
+      <c r="AQ24">
+        <v>-0</v>
       </c>
     </row>
     <row r="25">
@@ -3295,7 +3205,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DSC Investment Inc. (KOSDAQ:A241520)</t>
+          <t>SV Investment Corporation (KOSDAQ:A289080)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3303,12 +3213,6 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D25">
-        <v>0.519</v>
-      </c>
-      <c r="E25">
-        <v>0.752</v>
-      </c>
       <c r="G25">
         <v>0</v>
       </c>
@@ -3322,91 +3226,91 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>19.2</v>
+        <v>7.66</v>
       </c>
       <c r="L25">
-        <v>0.5549132947976878</v>
+        <v>0.3191666666666667</v>
       </c>
       <c r="M25">
-        <v>-0</v>
+        <v>2.2344</v>
       </c>
       <c r="N25">
-        <v>-0</v>
+        <v>0.02786034912718205</v>
       </c>
       <c r="O25">
-        <v>-0</v>
+        <v>0.2916971279373369</v>
       </c>
       <c r="P25">
-        <v>-0</v>
+        <v>2.2344</v>
       </c>
       <c r="Q25">
-        <v>-0</v>
+        <v>0.02786034912718205</v>
       </c>
       <c r="R25">
-        <v>-0</v>
+        <v>0.2916971279373369</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
       <c r="U25">
-        <v>4.46</v>
+        <v>4.17</v>
       </c>
       <c r="V25">
-        <v>0.03234227701232777</v>
+        <v>0.05199501246882793</v>
       </c>
       <c r="W25">
-        <v>0.5245901639344261</v>
+        <v>0.1478764478764479</v>
       </c>
       <c r="X25">
-        <v>0.04956354198460603</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="Y25">
-        <v>0.4750266219498201</v>
+        <v>0.07057400854364435</v>
       </c>
       <c r="Z25">
-        <v>0.9857549857549855</v>
+        <v>0.4974093264248705</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.04748153490051769</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="AC25">
-        <v>-0.04748153490051769</v>
+        <v>-0.07730243933280354</v>
       </c>
       <c r="AD25">
-        <v>12.3</v>
+        <v>0</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>12.3</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>7.840000000000001</v>
+        <v>-4.17</v>
       </c>
       <c r="AH25">
-        <v>0.08189081225033289</v>
+        <v>0</v>
       </c>
       <c r="AI25">
-        <v>0.1759656652360515</v>
+        <v>0</v>
       </c>
       <c r="AJ25">
-        <v>0.05379442843419789</v>
+        <v>-0.05484677101144285</v>
       </c>
       <c r="AK25">
-        <v>0.1198044009779951</v>
+        <v>-0.09059309146208994</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-0.006</v>
-      </c>
-      <c r="AQ25">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3417,7 +3321,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Q Capital Partners Co., Ltd. (KOSDAQ:A016600)</t>
+          <t>Daesung Private Equity, Inc. (KOSDAQ:A027830)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3426,7 +3330,7 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.161</v>
+        <v>0.218</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3441,10 +3345,10 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>3.16</v>
+        <v>3.88</v>
       </c>
       <c r="L26">
-        <v>1.654450261780105</v>
+        <v>0.2621621621621621</v>
       </c>
       <c r="M26">
         <v>-0</v>
@@ -3468,61 +3372,64 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>13.4</v>
+        <v>4.37</v>
       </c>
       <c r="V26">
-        <v>0.1576470588235294</v>
+        <v>0.04860956618464961</v>
       </c>
       <c r="W26">
-        <v>0.028649138712602</v>
+        <v>0.08362068965517241</v>
       </c>
       <c r="X26">
-        <v>0.04981961218163079</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="Y26">
-        <v>-0.02117047346902879</v>
+        <v>0.006318250322368879</v>
       </c>
       <c r="Z26">
-        <v>0.01577117755373347</v>
+        <v>0.3935123637330498</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.04749003841009629</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="AC26">
-        <v>-0.04749003841009629</v>
+        <v>-0.07730243933280354</v>
       </c>
       <c r="AD26">
-        <v>8.48</v>
+        <v>0</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>8.48</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>-4.92</v>
+        <v>-4.37</v>
       </c>
       <c r="AH26">
-        <v>0.09071459135643987</v>
+        <v>0</v>
       </c>
       <c r="AI26">
-        <v>0.07021029971849645</v>
+        <v>0</v>
       </c>
       <c r="AJ26">
-        <v>-0.06143856143856144</v>
+        <v>-0.05109318367824155</v>
       </c>
       <c r="AK26">
-        <v>-0.04581858819146955</v>
+        <v>-0.1161307467446187</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>-0.018</v>
+      </c>
+      <c r="AQ26">
+        <v>-0</v>
       </c>
     </row>
     <row r="27">
@@ -3533,7 +3440,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Globon Co., Ltd. (KOSDAQ:A019660)</t>
+          <t>Woori Technology Investment Co., Ltd (KOSDAQ:A041190)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3541,6 +3448,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D27">
+        <v>-0.196</v>
+      </c>
+      <c r="E27">
+        <v>0.836</v>
+      </c>
       <c r="G27">
         <v>0</v>
       </c>
@@ -3554,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>-6.61</v>
+        <v>64.3</v>
       </c>
       <c r="L27">
-        <v>-14.88738738738739</v>
+        <v>65.67926455566905</v>
       </c>
       <c r="M27">
         <v>-0</v>
@@ -3566,7 +3479,7 @@
         <v>-0</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P27">
         <v>-0</v>
@@ -3575,70 +3488,67 @@
         <v>-0</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
       <c r="U27">
-        <v>5.05</v>
+        <v>13.7</v>
       </c>
       <c r="V27">
-        <v>0.06188725490196079</v>
+        <v>0.0593073593073593</v>
       </c>
       <c r="W27">
-        <v>-0.5045801526717557</v>
+        <v>0.193499849533554</v>
       </c>
       <c r="X27">
-        <v>0.05141075355918075</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="Y27">
-        <v>-0.5559909062309365</v>
+        <v>0.1161974102007505</v>
       </c>
       <c r="Z27">
-        <v>0.02455752212389381</v>
+        <v>0.002979850246545322</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.04753941979295773</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="AC27">
-        <v>-0.04753941979295773</v>
+        <v>-0.07730243933280354</v>
       </c>
       <c r="AD27">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>8.449999999999999</v>
+        <v>-13.7</v>
       </c>
       <c r="AH27">
-        <v>0.1419558359621451</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>0.4192546583850931</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <v>0.09383675735702388</v>
+        <v>-0.06304647952139898</v>
       </c>
       <c r="AK27">
-        <v>0.3112338858195212</v>
+        <v>-0.0423100679431748</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-0.716</v>
-      </c>
-      <c r="AQ27">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3649,7 +3559,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>T.S. Investment Corporation (KOSDAQ:A246690)</t>
+          <t>Lindeman Asia Investment Co., Ltd. (KOSDAQ:A277070)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3658,10 +3568,10 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.289</v>
+        <v>0.0653</v>
       </c>
       <c r="E28">
-        <v>0.413</v>
+        <v>0.00219</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3676,91 +3586,94 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>6.76</v>
+        <v>2.4</v>
       </c>
       <c r="L28">
-        <v>0.4794326241134751</v>
+        <v>0.2846975088967971</v>
       </c>
       <c r="M28">
-        <v>0.5614</v>
+        <v>1.797</v>
       </c>
       <c r="N28">
-        <v>0.006386803185437997</v>
+        <v>0.04361650485436893</v>
       </c>
       <c r="O28">
-        <v>0.08304733727810651</v>
+        <v>0.74875</v>
       </c>
       <c r="P28">
-        <v>0.5474</v>
+        <v>0.377</v>
       </c>
       <c r="Q28">
-        <v>0.006227531285551763</v>
+        <v>0.009150485436893204</v>
       </c>
       <c r="R28">
-        <v>0.08097633136094674</v>
+        <v>0.1570833333333334</v>
       </c>
       <c r="S28">
-        <v>0.01400000000000001</v>
+        <v>1.42</v>
       </c>
       <c r="T28">
-        <v>0.02493765586034915</v>
+        <v>0.7902058987200891</v>
       </c>
       <c r="U28">
-        <v>15.3</v>
+        <v>7.02</v>
       </c>
       <c r="V28">
-        <v>0.174061433447099</v>
+        <v>0.1703883495145631</v>
       </c>
       <c r="W28">
-        <v>0.2060975609756098</v>
+        <v>0.0525164113785558</v>
       </c>
       <c r="X28">
-        <v>0.05250157890072767</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="Y28">
-        <v>0.1535959820748821</v>
+        <v>-0.02478602795424774</v>
       </c>
       <c r="Z28">
-        <v>0.4747474747474748</v>
+        <v>0.2044131910766246</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.04757017769587121</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="AC28">
-        <v>-0.04757017769587121</v>
+        <v>-0.07730243933280354</v>
       </c>
       <c r="AD28">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>3.199999999999999</v>
+        <v>-7.02</v>
       </c>
       <c r="AH28">
-        <v>0.1738721804511278</v>
+        <v>0</v>
       </c>
       <c r="AI28">
-        <v>0.2688953488372093</v>
+        <v>0</v>
       </c>
       <c r="AJ28">
-        <v>0.03512623490669593</v>
+        <v>-0.2053832650672908</v>
       </c>
       <c r="AK28">
-        <v>0.05981308411214952</v>
+        <v>-0.2244245524296675</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>-0.02</v>
+      </c>
+      <c r="AQ28">
+        <v>-0</v>
       </c>
     </row>
     <row r="29">
@@ -3771,7 +3684,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Leaders Technology Investment Co., Ltd (KOSDAQ:A019570)</t>
+          <t>Samsung Special Purpose Acquisition 4 Company (KOSDAQ:A377630)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3779,26 +3692,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D29">
-        <v>0.498</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
       <c r="K29">
-        <v>-9.609999999999999</v>
-      </c>
-      <c r="L29">
-        <v>-0.2777456647398844</v>
+        <v>-0.01</v>
       </c>
       <c r="M29">
         <v>-0</v>
@@ -3822,61 +3717,61 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>6.85</v>
+        <v>0.963</v>
       </c>
       <c r="V29">
-        <v>0.1268518518518519</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="W29">
-        <v>-0.4388127853881278</v>
+        <v>-0.001540832049306626</v>
       </c>
       <c r="X29">
-        <v>0.05516421730040324</v>
+        <v>0.07890991617494809</v>
       </c>
       <c r="Y29">
-        <v>-0.4939770026885311</v>
+        <v>-0.08045074822425471</v>
       </c>
       <c r="Z29">
-        <v>0.7207432404282799</v>
+        <v>0</v>
       </c>
       <c r="AA29">
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>0.04763644637009767</v>
+        <v>0.07731321346195724</v>
       </c>
       <c r="AC29">
-        <v>-0.04763644637009767</v>
+        <v>-0.07731321346195724</v>
       </c>
       <c r="AD29">
-        <v>17.3</v>
+        <v>0.835</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>17.3</v>
+        <v>0.835</v>
       </c>
       <c r="AG29">
-        <v>10.45</v>
+        <v>-0.128</v>
       </c>
       <c r="AH29">
-        <v>0.2426367461430575</v>
+        <v>0.05273129144300599</v>
       </c>
       <c r="AI29">
-        <v>0.3094812164579606</v>
+        <v>0.1354420113544201</v>
       </c>
       <c r="AJ29">
-        <v>0.1621411947245927</v>
+        <v>-0.008606777837547069</v>
       </c>
       <c r="AK29">
-        <v>0.2130479102956167</v>
+        <v>-0.02460592079969243</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-0.049</v>
+        <v>-0.064</v>
       </c>
       <c r="AQ29">
         <v>-0</v>
@@ -3890,7 +3785,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hana Financial Sixteenth Special Purpose Acquisition Company (KOSDAQ:A343510)</t>
+          <t>Kyobo 10 Special Purpose Acquisition Company (KOSDAQ:A355150)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3898,23 +3793,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G30">
-        <v>-0</v>
-      </c>
-      <c r="H30">
-        <v>-0</v>
-      </c>
-      <c r="I30">
-        <v>-0</v>
-      </c>
-      <c r="J30">
-        <v>-0</v>
-      </c>
       <c r="K30">
-        <v>-0.004</v>
-      </c>
-      <c r="L30">
-        <v>0.2</v>
+        <v>0.002</v>
       </c>
       <c r="M30">
         <v>-0</v>
@@ -3923,7 +3803,7 @@
         <v>-0</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P30">
         <v>-0</v>
@@ -3932,67 +3812,67 @@
         <v>-0</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S30">
         <v>0</v>
       </c>
       <c r="U30">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="V30">
-        <v>0.1497252747252747</v>
+        <v>0.1697699890470975</v>
       </c>
       <c r="W30">
-        <v>-0.0006309148264984228</v>
+        <v>0.0002638522427440633</v>
       </c>
       <c r="X30">
-        <v>0.05004162480682665</v>
+        <v>0.07924442983803422</v>
       </c>
       <c r="Y30">
-        <v>-0.05067253963332507</v>
+        <v>-0.07898057759529015</v>
       </c>
       <c r="Z30">
-        <v>-0.003331112591605597</v>
+        <v>0</v>
       </c>
       <c r="AA30">
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0.04772173633997825</v>
+        <v>0.07731531426247394</v>
       </c>
       <c r="AC30">
-        <v>-0.04772173633997825</v>
+        <v>-0.07731531426247394</v>
       </c>
       <c r="AD30">
-        <v>0.793</v>
+        <v>0.614</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>0.793</v>
+        <v>0.614</v>
       </c>
       <c r="AG30">
-        <v>-0.297</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="AH30">
-        <v>0.09822866344605476</v>
+        <v>0.06301313628899835</v>
       </c>
       <c r="AI30">
-        <v>0.1127541589648798</v>
+        <v>0.08958272541581558</v>
       </c>
       <c r="AJ30">
-        <v>-0.04253186309609051</v>
+        <v>-0.1142299243348792</v>
       </c>
       <c r="AK30">
-        <v>-0.04997476022211005</v>
+        <v>-0.1764705882352941</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-0.029</v>
+        <v>-0.061</v>
       </c>
       <c r="AQ30">
         <v>-0</v>
@@ -4006,7 +3886,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sangsangin Ian No.2 Special Purpose Acquisition Company (KOSDAQ:A329560)</t>
+          <t>Shinyoung HappyTomorrow No.6 Special Purpose Acquisition Company (KOSDAQ:A344050)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4014,23 +3894,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G31">
-        <v>-0</v>
-      </c>
-      <c r="H31">
-        <v>-0</v>
-      </c>
-      <c r="I31">
-        <v>-0</v>
-      </c>
-      <c r="J31">
-        <v>-0</v>
-      </c>
       <c r="K31">
-        <v>0.007</v>
-      </c>
-      <c r="L31">
-        <v>-0.5</v>
+        <v>-0.004</v>
       </c>
       <c r="M31">
         <v>-0</v>
@@ -4039,7 +3904,7 @@
         <v>-0</v>
       </c>
       <c r="O31">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P31">
         <v>-0</v>
@@ -4048,67 +3913,67 @@
         <v>-0</v>
       </c>
       <c r="R31">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
       </c>
       <c r="U31">
-        <v>0.187</v>
+        <v>0.931</v>
       </c>
       <c r="V31">
-        <v>0.02833333333333334</v>
+        <v>0.08166666666666667</v>
       </c>
       <c r="W31">
-        <v>0.001151315789473684</v>
+        <v>-0.0005563282336578581</v>
       </c>
       <c r="X31">
-        <v>0.05005657001084862</v>
+        <v>0.07982282927597062</v>
       </c>
       <c r="Y31">
-        <v>-0.04890525422137494</v>
+        <v>-0.08037915750962847</v>
       </c>
       <c r="Z31">
-        <v>-0.002114484216885667</v>
+        <v>0</v>
       </c>
       <c r="AA31">
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>0.0477233651480114</v>
+        <v>0.07731884108775815</v>
       </c>
       <c r="AC31">
-        <v>-0.0477233651480114</v>
+        <v>-0.07731884108775815</v>
       </c>
       <c r="AD31">
-        <v>0.723</v>
+        <v>0.995</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>0.723</v>
+        <v>0.995</v>
       </c>
       <c r="AG31">
-        <v>0.536</v>
+        <v>0.06399999999999995</v>
       </c>
       <c r="AH31">
-        <v>0.09873002867677182</v>
+        <v>0.08027430415490117</v>
       </c>
       <c r="AI31">
-        <v>0.107541276215975</v>
+        <v>0.1440984793627806</v>
       </c>
       <c r="AJ31">
-        <v>0.07511210762331839</v>
+        <v>0.005582693649685969</v>
       </c>
       <c r="AK31">
-        <v>0.08200734394124848</v>
+        <v>0.01071309005691328</v>
       </c>
       <c r="AL31">
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-0.043</v>
+        <v>-0.059</v>
       </c>
       <c r="AQ31">
         <v>-0</v>
@@ -4122,7 +3987,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hana Financial Fourteen Special Purpose Acquisition Company (KOSDAQ:A332710)</t>
+          <t>Hana Financial Sixteenth Special Purpose Acquisition Company (KOSDAQ:A343510)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4130,23 +3995,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G32">
-        <v>-0</v>
-      </c>
-      <c r="H32">
-        <v>-0</v>
-      </c>
-      <c r="I32">
-        <v>-0</v>
-      </c>
-      <c r="J32">
-        <v>-0</v>
-      </c>
       <c r="K32">
-        <v>-0.008</v>
-      </c>
-      <c r="L32">
-        <v>0.5</v>
+        <v>0.005</v>
       </c>
       <c r="M32">
         <v>-0</v>
@@ -4155,7 +4005,7 @@
         <v>-0</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P32">
         <v>-0</v>
@@ -4164,67 +4014,67 @@
         <v>-0</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S32">
         <v>0</v>
       </c>
       <c r="U32">
-        <v>1.13</v>
+        <v>0.89</v>
       </c>
       <c r="V32">
-        <v>0.1443167305236271</v>
+        <v>0.1373456790123457</v>
       </c>
       <c r="W32">
-        <v>-0.001123595505617978</v>
+        <v>0.0008012820512820513</v>
       </c>
       <c r="X32">
-        <v>0.05042557199047795</v>
+        <v>0.08028370460058659</v>
       </c>
       <c r="Y32">
-        <v>-0.05154916749609593</v>
+        <v>-0.07948242254930454</v>
       </c>
       <c r="Z32">
-        <v>-0.002307137707281903</v>
+        <v>0</v>
       </c>
       <c r="AA32">
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0.04776301431700859</v>
+        <v>0.07732155962787678</v>
       </c>
       <c r="AC32">
-        <v>-0.04776301431700859</v>
+        <v>-0.07732155962787678</v>
       </c>
       <c r="AD32">
-        <v>0.977</v>
+        <v>0.669</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>0.977</v>
+        <v>0.669</v>
       </c>
       <c r="AG32">
-        <v>-0.1529999999999999</v>
+        <v>-0.221</v>
       </c>
       <c r="AH32">
-        <v>0.1109344839332349</v>
+        <v>0.09357952161141418</v>
       </c>
       <c r="AI32">
-        <v>0.1223237761362213</v>
+        <v>0.1151661215355483</v>
       </c>
       <c r="AJ32">
-        <v>-0.01992966002344665</v>
+        <v>-0.03530915481706342</v>
       </c>
       <c r="AK32">
-        <v>-0.02231296485343443</v>
+        <v>-0.04492783085993088</v>
       </c>
       <c r="AL32">
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-0.038</v>
+        <v>-0.051</v>
       </c>
       <c r="AQ32">
         <v>-0</v>
@@ -4238,7 +4088,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NH Special Purpose Acquisition 17 Company (KOSDAQ:A359090)</t>
+          <t>Shinhan 7th Special Purpose Acquisition Company (KOSDAQ:A366330)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4246,23 +4096,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G33">
-        <v>-0</v>
-      </c>
-      <c r="H33">
-        <v>-0</v>
-      </c>
-      <c r="I33">
-        <v>-0</v>
-      </c>
-      <c r="J33">
-        <v>-0</v>
-      </c>
       <c r="K33">
-        <v>-0.015</v>
-      </c>
-      <c r="L33">
-        <v>0.3846153846153846</v>
+        <v>-0.001</v>
       </c>
       <c r="M33">
         <v>-0</v>
@@ -4286,61 +4121,61 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>0.023</v>
+        <v>1.18</v>
       </c>
       <c r="V33">
-        <v>0.001885245901639344</v>
+        <v>0.1612021857923497</v>
       </c>
       <c r="W33">
-        <v>-0.001351351351351351</v>
+        <v>-0.0001375515818431912</v>
       </c>
       <c r="X33">
-        <v>0.05052034844730637</v>
+        <v>0.08057672464491696</v>
       </c>
       <c r="Y33">
-        <v>-0.05187169979865772</v>
+        <v>-0.08071427622676014</v>
       </c>
       <c r="Z33">
-        <v>-0.003092047887100611</v>
+        <v>0</v>
       </c>
       <c r="AA33">
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>0.04777302530294177</v>
+        <v>0.07732324752033135</v>
       </c>
       <c r="AC33">
-        <v>-0.04777302530294177</v>
+        <v>-0.07732324752033135</v>
       </c>
       <c r="AD33">
-        <v>1.57</v>
+        <v>0.83</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.57</v>
+        <v>0.83</v>
       </c>
       <c r="AG33">
-        <v>1.547</v>
+        <v>-0.35</v>
       </c>
       <c r="AH33">
-        <v>0.1140159767610748</v>
+        <v>0.101840490797546</v>
       </c>
       <c r="AI33">
-        <v>0.1259021651964715</v>
+        <v>0.1218795888399413</v>
       </c>
       <c r="AJ33">
-        <v>0.1125336437040809</v>
+        <v>-0.05021520803443328</v>
       </c>
       <c r="AK33">
-        <v>0.1242869767815538</v>
+        <v>-0.06216696269982237</v>
       </c>
       <c r="AL33">
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-0.075</v>
+        <v>-0.049</v>
       </c>
       <c r="AQ33">
         <v>-0</v>
@@ -4354,7 +4189,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sk No.6 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A340350)</t>
+          <t>HMCIB No.4 Special Purpose Acquisition Company (KOSDAQ:A353070)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4362,23 +4197,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G34">
-        <v>-0</v>
-      </c>
-      <c r="H34">
-        <v>-0</v>
-      </c>
-      <c r="I34">
-        <v>-0</v>
-      </c>
-      <c r="J34">
-        <v>-0</v>
-      </c>
       <c r="K34">
-        <v>0.016</v>
-      </c>
-      <c r="L34">
-        <v>-0.3076923076923077</v>
+        <v>0.027</v>
       </c>
       <c r="M34">
         <v>-0</v>
@@ -4402,61 +4222,61 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>1.59</v>
+        <v>1.1</v>
       </c>
       <c r="V34">
-        <v>0.159</v>
+        <v>0.1601164483260553</v>
       </c>
       <c r="W34">
-        <v>0.001658031088082902</v>
+        <v>0.003868194842406877</v>
       </c>
       <c r="X34">
-        <v>0.0507943911357232</v>
+        <v>0.08143850923493004</v>
       </c>
       <c r="Y34">
-        <v>-0.0491363600476403</v>
+        <v>-0.07757031439252317</v>
       </c>
       <c r="Z34">
-        <v>-0.005473684210526315</v>
+        <v>0</v>
       </c>
       <c r="AA34">
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>0.04780158515705515</v>
+        <v>0.07732803803635693</v>
       </c>
       <c r="AC34">
-        <v>-0.04780158515705515</v>
+        <v>-0.07732803803635693</v>
       </c>
       <c r="AD34">
-        <v>1.4</v>
+        <v>0.984</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.4</v>
+        <v>0.984</v>
       </c>
       <c r="AG34">
-        <v>-0.1900000000000002</v>
+        <v>-0.1160000000000001</v>
       </c>
       <c r="AH34">
-        <v>0.1228070175438596</v>
+        <v>0.1252864782276547</v>
       </c>
       <c r="AI34">
-        <v>0.1280878316559927</v>
+        <v>0.1456914421083802</v>
       </c>
       <c r="AJ34">
-        <v>-0.01936799184505608</v>
+        <v>-0.01717500740302045</v>
       </c>
       <c r="AK34">
-        <v>-0.02034261241970023</v>
+        <v>-0.02051644853201275</v>
       </c>
       <c r="AL34">
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-0.093</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="AQ34">
         <v>-0</v>
@@ -4470,7 +4290,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shinyoung HappyTomorrow No.6 Special Purpose Acquisition Company (KOSDAQ:A344050)</t>
+          <t>IBKS No.13 Special Purpose Acquisition Company (KOSDAQ:A351340)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4478,23 +4298,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G35">
-        <v>-0</v>
-      </c>
-      <c r="H35">
-        <v>-0</v>
-      </c>
-      <c r="I35">
-        <v>-0</v>
-      </c>
-      <c r="J35">
-        <v>-0</v>
-      </c>
       <c r="K35">
-        <v>-0.007</v>
-      </c>
-      <c r="L35">
-        <v>0.2916666666666667</v>
+        <v>-0.018</v>
       </c>
       <c r="M35">
         <v>-0</v>
@@ -4518,61 +4323,61 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="V35">
-        <v>0.1515544041450777</v>
+        <v>0.1862745098039216</v>
       </c>
       <c r="W35">
-        <v>-0.0009589041095890412</v>
+        <v>-0.002155688622754491</v>
       </c>
       <c r="X35">
-        <v>0.05110570132498278</v>
+        <v>0.08218602079229517</v>
       </c>
       <c r="Y35">
-        <v>-0.05206460543457182</v>
+        <v>-0.08434170941504966</v>
       </c>
       <c r="Z35">
-        <v>-0.003305785123966942</v>
+        <v>0</v>
       </c>
       <c r="AA35">
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0.04783334896080144</v>
+        <v>0.07733199525272538</v>
       </c>
       <c r="AC35">
-        <v>-0.04783334896080144</v>
+        <v>-0.07733199525272538</v>
       </c>
       <c r="AD35">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AE35">
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AG35">
-        <v>0.01000000000000001</v>
+        <v>-0.1400000000000001</v>
       </c>
       <c r="AH35">
-        <v>0.1325842696629213</v>
+        <v>0.1446540880503145</v>
       </c>
       <c r="AI35">
-        <v>0.1409796893667861</v>
+        <v>0.1674757281553398</v>
       </c>
       <c r="AJ35">
-        <v>0.001293661060802071</v>
+        <v>-0.01745635910224441</v>
       </c>
       <c r="AK35">
-        <v>0.00138888888888889</v>
+        <v>-0.02083333333333335</v>
       </c>
       <c r="AL35">
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-0.051</v>
+        <v>-0.09</v>
       </c>
       <c r="AQ35">
         <v>-0</v>
@@ -4586,7 +4391,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HMCIB No.4 Special Purpose Acquisition Company (KOSDAQ:A353070)</t>
+          <t>DB Finance No.9 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A367360)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4594,23 +4399,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G36">
-        <v>-0</v>
-      </c>
-      <c r="H36">
-        <v>-0</v>
-      </c>
-      <c r="I36">
-        <v>-0</v>
-      </c>
-      <c r="J36">
-        <v>-0</v>
-      </c>
       <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>-0</v>
+        <v>0.02</v>
       </c>
       <c r="M36">
         <v>-0</v>
@@ -4618,74 +4408,83 @@
       <c r="N36">
         <v>-0</v>
       </c>
+      <c r="O36">
+        <v>-0</v>
+      </c>
       <c r="P36">
         <v>-0</v>
       </c>
       <c r="Q36">
         <v>-0</v>
       </c>
+      <c r="R36">
+        <v>-0</v>
+      </c>
       <c r="S36">
         <v>0</v>
       </c>
       <c r="U36">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V36">
-        <v>0.1788079470198676</v>
+        <v>0.1776913099870298</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>0.002583979328165375</v>
       </c>
       <c r="X36">
-        <v>0.05115699335306791</v>
+        <v>0.08042233543827293</v>
       </c>
       <c r="Y36">
-        <v>-0.05115699335306791</v>
+        <v>-0.07783835611010756</v>
       </c>
       <c r="Z36">
-        <v>-0.004233576642335767</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>-0.002066070768360844</v>
       </c>
       <c r="AB36">
-        <v>0.04783851460343773</v>
+        <v>0.07648136648865392</v>
       </c>
       <c r="AC36">
-        <v>-0.04783851460343773</v>
+        <v>-0.07854743725701477</v>
       </c>
       <c r="AD36">
-        <v>1.17</v>
+        <v>0.833</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.17</v>
+        <v>0.833</v>
       </c>
       <c r="AG36">
-        <v>-0.1800000000000002</v>
+        <v>-0.5370000000000001</v>
       </c>
       <c r="AH36">
-        <v>0.1341743119266055</v>
+        <v>0.09750673065667799</v>
       </c>
       <c r="AI36">
-        <v>0.1435582822085889</v>
+        <v>0.1095620149940813</v>
       </c>
       <c r="AJ36">
-        <v>-0.0244233378561737</v>
+        <v>-0.07486407360936849</v>
       </c>
       <c r="AK36">
-        <v>-0.02647058823529414</v>
+        <v>-0.08615433980426764</v>
       </c>
       <c r="AL36">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="AM36">
-        <v>-0.052</v>
+        <v>-0.046</v>
+      </c>
+      <c r="AO36">
+        <v>-1.055555555555556</v>
       </c>
       <c r="AQ36">
-        <v>-0</v>
+        <v>0.4130434782608696</v>
       </c>
     </row>
     <row r="37">
@@ -4696,7 +4495,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IBKS No.13 Special Purpose Acquisition Company (KOSDAQ:A351340)</t>
+          <t>DB Finance No.8 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A367340)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4704,23 +4503,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G37">
-        <v>-0</v>
-      </c>
-      <c r="H37">
-        <v>-0</v>
-      </c>
-      <c r="I37">
-        <v>-0</v>
-      </c>
-      <c r="J37">
-        <v>-0</v>
-      </c>
       <c r="K37">
-        <v>-0.026</v>
-      </c>
-      <c r="L37">
-        <v>0.7027027027027027</v>
+        <v>0.054</v>
       </c>
       <c r="M37">
         <v>-0</v>
@@ -4729,7 +4513,7 @@
         <v>-0</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P37">
         <v>-0</v>
@@ -4738,70 +4522,73 @@
         <v>-0</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S37">
         <v>0</v>
       </c>
       <c r="U37">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="V37">
-        <v>0.2064864864864865</v>
+        <v>0.1265560165975104</v>
       </c>
       <c r="W37">
-        <v>-0.003066037735849056</v>
+        <v>0.005831533477321815</v>
       </c>
       <c r="X37">
-        <v>0.05172418266218878</v>
+        <v>0.07915666728511206</v>
       </c>
       <c r="Y37">
-        <v>-0.05479022039803784</v>
+        <v>-0.07332513380779024</v>
       </c>
       <c r="Z37">
-        <v>-0.004539877300613496</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>-0.001731601731601731</v>
       </c>
       <c r="AB37">
-        <v>0.04789439898690166</v>
+        <v>0.07731476752478186</v>
       </c>
       <c r="AC37">
-        <v>-0.04789439898690166</v>
+        <v>-0.0790463692563836</v>
       </c>
       <c r="AD37">
-        <v>1.65</v>
+        <v>0.619</v>
       </c>
       <c r="AE37">
         <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.65</v>
+        <v>0.619</v>
       </c>
       <c r="AG37">
-        <v>-0.26</v>
+        <v>-0.601</v>
       </c>
       <c r="AH37">
-        <v>0.1513761467889908</v>
+        <v>0.06033726484062774</v>
       </c>
       <c r="AI37">
-        <v>0.165</v>
+        <v>0.07467728314633852</v>
       </c>
       <c r="AJ37">
-        <v>-0.0289210233592881</v>
+        <v>-0.06648965593539106</v>
       </c>
       <c r="AK37">
-        <v>-0.03213844252163164</v>
+        <v>-0.08501909746781723</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="AM37">
-        <v>-0.06</v>
+        <v>-0.083</v>
+      </c>
+      <c r="AO37">
+        <v>-1.285714285714286</v>
       </c>
       <c r="AQ37">
-        <v>-0</v>
+        <v>0.216867469879518</v>
       </c>
     </row>
     <row r="38">
@@ -4812,7 +4599,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IBKS No.12 Special Purpose Acquisition Company (KOSDAQ:A335870)</t>
+          <t>Samsung Must Special Purpose Acquisition 5 Company (KOSDAQ:A380320)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4820,23 +4607,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G38">
-        <v>-0</v>
-      </c>
-      <c r="H38">
-        <v>-0</v>
-      </c>
-      <c r="I38">
-        <v>-0</v>
-      </c>
-      <c r="J38">
-        <v>-0</v>
-      </c>
       <c r="K38">
-        <v>-0.027</v>
-      </c>
-      <c r="L38">
-        <v>1.227272727272727</v>
+        <v>0.033</v>
       </c>
       <c r="M38">
         <v>-0</v>
@@ -4845,7 +4617,7 @@
         <v>-0</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P38">
         <v>-0</v>
@@ -4854,70 +4626,73 @@
         <v>-0</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S38">
         <v>0</v>
       </c>
       <c r="U38">
-        <v>1.07</v>
+        <v>0.986</v>
       </c>
       <c r="V38">
-        <v>0.1893805309734513</v>
+        <v>0.08285714285714285</v>
       </c>
       <c r="W38">
-        <v>-0.005273437499999999</v>
+        <v>0.004471544715447155</v>
       </c>
       <c r="X38">
-        <v>0.05181921308119686</v>
+        <v>0.07855457748589556</v>
       </c>
       <c r="Y38">
-        <v>-0.05709265058119686</v>
+        <v>-0.07408303277044841</v>
       </c>
       <c r="Z38">
-        <v>-0.004391217564870258</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>-0.003754376005298514</v>
       </c>
       <c r="AB38">
-        <v>0.04790354573229894</v>
+        <v>0.07731093078105428</v>
       </c>
       <c r="AC38">
-        <v>-0.04790354573229894</v>
+        <v>-0.08106530678635279</v>
       </c>
       <c r="AD38">
-        <v>1.03</v>
+        <v>0.516</v>
       </c>
       <c r="AE38">
         <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.03</v>
+        <v>0.516</v>
       </c>
       <c r="AG38">
-        <v>-0.04000000000000004</v>
+        <v>-0.47</v>
       </c>
       <c r="AH38">
-        <v>0.1541916167664671</v>
+        <v>0.04155927835051546</v>
       </c>
       <c r="AI38">
-        <v>0.1702479338842975</v>
+        <v>0.07787503773015393</v>
       </c>
       <c r="AJ38">
-        <v>-0.007130124777183606</v>
+        <v>-0.04111986001749781</v>
       </c>
       <c r="AK38">
-        <v>-0.008032128514056233</v>
+        <v>-0.08333333333333331</v>
       </c>
       <c r="AL38">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="AM38">
-        <v>-0.037</v>
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AO38">
+        <v>-2.818181818181818</v>
       </c>
       <c r="AQ38">
-        <v>-0</v>
+        <v>0.4428571428571428</v>
       </c>
     </row>
     <row r="39">
@@ -4928,7 +4703,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ebest Special Purpose Acquisition No5 Company (KOSDAQ:A349720)</t>
+          <t>Shinhan 8th Special Purpose Acquisition Company (KOSDAQ:A393360)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4936,23 +4711,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G39">
-        <v>-0</v>
-      </c>
-      <c r="H39">
-        <v>-0</v>
-      </c>
-      <c r="I39">
-        <v>-0</v>
-      </c>
-      <c r="J39">
-        <v>-0</v>
-      </c>
       <c r="K39">
-        <v>-0.013</v>
-      </c>
-      <c r="L39">
-        <v>0.325</v>
+        <v>0.022</v>
       </c>
       <c r="M39">
         <v>-0</v>
@@ -4961,7 +4721,7 @@
         <v>-0</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P39">
         <v>-0</v>
@@ -4970,70 +4730,73 @@
         <v>-0</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S39">
         <v>0</v>
       </c>
       <c r="U39">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="V39">
-        <v>0.2160883280757098</v>
+        <v>0.1271186440677966</v>
       </c>
       <c r="W39">
-        <v>-0.002113821138211382</v>
+        <v>0.001929824561403509</v>
       </c>
       <c r="X39">
-        <v>0.05233207719775287</v>
+        <v>0.07947799030103633</v>
       </c>
       <c r="Y39">
-        <v>-0.05444589833596425</v>
+        <v>-0.07754816573963283</v>
       </c>
       <c r="Z39">
-        <v>-0.006666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>-0.005521638854972187</v>
       </c>
       <c r="AB39">
-        <v>0.04795188006703596</v>
+        <v>0.07671248084029506</v>
       </c>
       <c r="AC39">
-        <v>-0.04795188006703596</v>
+        <v>-0.08223411969526724</v>
       </c>
       <c r="AD39">
-        <v>1.29</v>
+        <v>0.889</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.29</v>
+        <v>0.889</v>
       </c>
       <c r="AG39">
-        <v>-0.08000000000000007</v>
+        <v>-0.611</v>
       </c>
       <c r="AH39">
-        <v>0.1690694626474443</v>
+        <v>0.07006068248088895</v>
       </c>
       <c r="AI39">
-        <v>0.1759890859481583</v>
+        <v>0.08640295461172126</v>
       </c>
       <c r="AJ39">
-        <v>-0.01277955271565496</v>
+        <v>-0.05460720350344088</v>
       </c>
       <c r="AK39">
-        <v>-0.01342281879194632</v>
+        <v>-0.06951871657754011</v>
       </c>
       <c r="AL39">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AM39">
-        <v>-0.057</v>
+        <v>-0.102</v>
+      </c>
+      <c r="AO39">
+        <v>-2.466666666666667</v>
       </c>
       <c r="AQ39">
-        <v>-0</v>
+        <v>0.7254901960784312</v>
       </c>
     </row>
     <row r="40">
@@ -5044,7 +4807,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kyobo 10 Special Purpose Acquisition Company (KOSDAQ:A355150)</t>
+          <t>Eugene Special Purpose Acquisition 7 Co., Ltd (KOSDAQ:A388800)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5053,7 +4816,7 @@
         </is>
       </c>
       <c r="K40">
-        <v>-0.013</v>
+        <v>0.002</v>
       </c>
       <c r="M40">
         <v>-0</v>
@@ -5062,7 +4825,7 @@
         <v>-0</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P40">
         <v>-0</v>
@@ -5071,73 +4834,73 @@
         <v>-0</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S40">
         <v>0</v>
       </c>
       <c r="U40">
-        <v>1.92</v>
+        <v>0.001</v>
       </c>
       <c r="V40">
-        <v>0.2012578616352201</v>
+        <v>0.0001237623762376238</v>
       </c>
       <c r="W40">
-        <v>-0.001688311688311688</v>
+        <v>0.0002645502645502646</v>
       </c>
       <c r="X40">
-        <v>0.04925646153671683</v>
+        <v>0.07947177541031082</v>
       </c>
       <c r="Y40">
-        <v>-0.05094477322502852</v>
+        <v>-0.07920722514576056</v>
       </c>
       <c r="Z40">
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>-0.008092125739184563</v>
+        <v>-0.007619738751814223</v>
       </c>
       <c r="AB40">
-        <v>0.04763353989919485</v>
+        <v>0.07671404841133377</v>
       </c>
       <c r="AC40">
-        <v>-0.05572566563837941</v>
+        <v>-0.08433378716314799</v>
       </c>
       <c r="AD40">
-        <v>0.73</v>
+        <v>0.607</v>
       </c>
       <c r="AE40">
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>0.73</v>
+        <v>0.607</v>
       </c>
       <c r="AG40">
-        <v>-1.19</v>
+        <v>0.606</v>
       </c>
       <c r="AH40">
-        <v>0.07108081791626096</v>
+        <v>0.06987452515252676</v>
       </c>
       <c r="AI40">
-        <v>0.0878459687123947</v>
+        <v>0.08878162936960654</v>
       </c>
       <c r="AJ40">
-        <v>-0.1425149700598802</v>
+        <v>0.06976744186046512</v>
       </c>
       <c r="AK40">
-        <v>-0.1862284820031299</v>
+        <v>0.08864833235810415</v>
       </c>
       <c r="AL40">
-        <v>0.018</v>
+        <v>0.027</v>
       </c>
       <c r="AM40">
-        <v>-0.035</v>
+        <v>-0.064</v>
       </c>
       <c r="AO40">
-        <v>-2.888888888888889</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="AQ40">
-        <v>1.485714285714286</v>
+        <v>0.984375</v>
       </c>
     </row>
     <row r="41">
@@ -5148,7 +4911,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Daishin Balance No.9 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A369370)</t>
+          <t>Eugene Special Purpose Acquisitions 6 Company (KOSDAQ:A373340)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5157,7 +4920,7 @@
         </is>
       </c>
       <c r="K41">
-        <v>-0.016</v>
+        <v>0.007</v>
       </c>
       <c r="M41">
         <v>-0</v>
@@ -5166,7 +4929,7 @@
         <v>-0</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P41">
         <v>-0</v>
@@ -5175,58 +4938,73 @@
         <v>-0</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S41">
         <v>0</v>
       </c>
       <c r="U41">
-        <v>0.381</v>
+        <v>0.004</v>
       </c>
       <c r="V41">
-        <v>0.02202312138728324</v>
+        <v>0.0007782101167315176</v>
+      </c>
+      <c r="W41">
+        <v>0.001431492842535787</v>
       </c>
       <c r="X41">
-        <v>0.04849072911266989</v>
+        <v>0.0814598038911121</v>
+      </c>
+      <c r="Y41">
+        <v>-0.08002831104857631</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>-0.004595836712625034</v>
       </c>
       <c r="AB41">
-        <v>0.04754225657656765</v>
+        <v>0.08040519406171513</v>
+      </c>
+      <c r="AC41">
+        <v>-0.08500103077434017</v>
       </c>
       <c r="AD41">
-        <v>0.777</v>
+        <v>0.74</v>
       </c>
       <c r="AE41">
         <v>0</v>
       </c>
       <c r="AF41">
-        <v>0.777</v>
+        <v>0.74</v>
       </c>
       <c r="AG41">
-        <v>0.396</v>
+        <v>0.736</v>
       </c>
       <c r="AH41">
-        <v>0.04298279581789013</v>
+        <v>0.1258503401360544</v>
       </c>
       <c r="AI41">
-        <v>0.1081118686517323</v>
+        <v>0.1551362683438155</v>
       </c>
       <c r="AJ41">
-        <v>0.02237793851717902</v>
+        <v>0.1252552756977536</v>
       </c>
       <c r="AK41">
-        <v>0.05818395533352924</v>
+        <v>0.1544271926143516</v>
       </c>
       <c r="AL41">
-        <v>0.011</v>
+        <v>0.024</v>
       </c>
       <c r="AM41">
-        <v>0.002</v>
+        <v>-0.042</v>
       </c>
       <c r="AO41">
-        <v>-1.636363636363636</v>
+        <v>-1.416666666666667</v>
       </c>
       <c r="AQ41">
-        <v>-9</v>
+        <v>0.8095238095238095</v>
       </c>
     </row>
     <row r="42">
@@ -5237,7 +5015,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Korea No.9 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A368770)</t>
+          <t>Daishin Balance No.11 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A397500)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5246,7 +5024,7 @@
         </is>
       </c>
       <c r="K42">
-        <v>-0.039</v>
+        <v>-0.047</v>
       </c>
       <c r="M42">
         <v>-0</v>
@@ -5270,52 +5048,52 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="V42">
-        <v>0.1017391304347826</v>
+        <v>0.1178861788617886</v>
       </c>
       <c r="X42">
-        <v>0.04871929914662106</v>
+        <v>0.0790021811667639</v>
       </c>
       <c r="AB42">
-        <v>0.04757007752025608</v>
+        <v>0.07731379749191357</v>
       </c>
       <c r="AD42">
-        <v>0.625</v>
+        <v>0.724</v>
       </c>
       <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42">
-        <v>0.625</v>
+        <v>0.724</v>
       </c>
       <c r="AG42">
-        <v>-0.5449999999999999</v>
+        <v>-0.726</v>
       </c>
       <c r="AH42">
-        <v>0.05154639175257732</v>
+        <v>0.05558968058968058</v>
       </c>
       <c r="AI42">
-        <v>0.07856693903205531</v>
+        <v>0.06859958309645632</v>
       </c>
       <c r="AJ42">
-        <v>-0.04974897307165677</v>
+        <v>-0.06272680145152928</v>
       </c>
       <c r="AK42">
-        <v>-0.08032424465733234</v>
+        <v>-0.07974516695957821</v>
       </c>
       <c r="AL42">
-        <v>0.008999999999999999</v>
+        <v>0.037</v>
       </c>
       <c r="AM42">
-        <v>0.008</v>
+        <v>0.001999999999999995</v>
       </c>
       <c r="AO42">
-        <v>-4.666666666666667</v>
+        <v>-1.243243243243243</v>
       </c>
       <c r="AQ42">
-        <v>-5.25</v>
+        <v>-23.00000000000006</v>
       </c>
     </row>
     <row r="43">
@@ -5326,7 +5104,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Yuanta 8 Special Purpose Acquisition Company (KOSDAQ:A367480)</t>
+          <t>Mirae Asset Vision Special Purpose Acquisition 1 Company (KOSDAQ:A412930)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5335,7 +5113,7 @@
         </is>
       </c>
       <c r="K43">
-        <v>-0.074</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M43">
         <v>-0</v>
@@ -5359,52 +5137,52 @@
         <v>0</v>
       </c>
       <c r="U43">
-        <v>0.678</v>
+        <v>2.13</v>
       </c>
       <c r="V43">
-        <v>0.05947368421052632</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="X43">
-        <v>0.05186547789045078</v>
+        <v>0.08264784841522496</v>
       </c>
       <c r="AB43">
-        <v>0.0479079768222914</v>
+        <v>0.07733435370473951</v>
       </c>
       <c r="AD43">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AE43">
         <v>0</v>
       </c>
       <c r="AF43">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AG43">
-        <v>1.422</v>
+        <v>-0.2899999999999998</v>
       </c>
       <c r="AH43">
-        <v>0.1555555555555556</v>
+        <v>0.1561969439728353</v>
       </c>
       <c r="AI43">
-        <v>0.1627906976744186</v>
+        <v>0.1800391389432485</v>
       </c>
       <c r="AJ43">
-        <v>0.1109031352363126</v>
+        <v>-0.03005181347150257</v>
       </c>
       <c r="AK43">
-        <v>0.1163475699558174</v>
+        <v>-0.03584672435105065</v>
       </c>
       <c r="AL43">
-        <v>0.039</v>
+        <v>0.025</v>
       </c>
       <c r="AM43">
-        <v>0.037</v>
+        <v>0.024</v>
       </c>
       <c r="AO43">
-        <v>-1.487179487179487</v>
+        <v>-2.6</v>
       </c>
       <c r="AQ43">
-        <v>-1.567567567567568</v>
+        <v>-2.708333333333333</v>
       </c>
     </row>
     <row r="44">
@@ -5415,7 +5193,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DB Finance No.8 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A367340)</t>
+          <t>Sangsangin No.3 Special Purpose Acquisition Company (KOSDAQ:A415580)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5424,7 +5202,7 @@
         </is>
       </c>
       <c r="K44">
-        <v>-0.053</v>
+        <v>-0.028</v>
       </c>
       <c r="M44">
         <v>-0</v>
@@ -5448,52 +5226,52 @@
         <v>0</v>
       </c>
       <c r="U44">
-        <v>1.49</v>
+        <v>0.016</v>
       </c>
       <c r="V44">
-        <v>0.1392523364485981</v>
+        <v>0.001927710843373494</v>
       </c>
       <c r="X44">
-        <v>0.04906680494488144</v>
+        <v>0.07902113255844254</v>
       </c>
       <c r="AB44">
-        <v>0.04761143389704062</v>
+        <v>0.07731391701663035</v>
       </c>
       <c r="AD44">
-        <v>0.735</v>
+        <v>0.494</v>
       </c>
       <c r="AE44">
         <v>0</v>
       </c>
       <c r="AF44">
-        <v>0.735</v>
+        <v>0.494</v>
       </c>
       <c r="AG44">
-        <v>-0.755</v>
+        <v>0.478</v>
       </c>
       <c r="AH44">
-        <v>0.06427634455618715</v>
+        <v>0.05617466454400728</v>
       </c>
       <c r="AI44">
-        <v>0.0735367683841921</v>
+        <v>0.06791311520483916</v>
       </c>
       <c r="AJ44">
-        <v>-0.07591754650578181</v>
+        <v>0.05445431761221235</v>
       </c>
       <c r="AK44">
-        <v>-0.08877131099353322</v>
+        <v>0.06585836318545053</v>
       </c>
       <c r="AL44">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="AM44">
-        <v>-0.008</v>
+        <v>0.004</v>
       </c>
       <c r="AO44">
-        <v>-6.333333333333333</v>
+        <v>-7.75</v>
       </c>
       <c r="AQ44">
-        <v>9.5</v>
+        <v>-7.75</v>
       </c>
     </row>
     <row r="45">
@@ -5504,7 +5282,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Yuanta 7 SPECIAL PURPOSE ACQUISITION COMPANY (KOSDAQ:A367460)</t>
+          <t>Shinhan 9th Special Purpose Acquisition Company Co., Ltd. (KOSDAQ:A405640)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5513,7 +5291,7 @@
         </is>
       </c>
       <c r="K45">
-        <v>-0.07099999999999999</v>
+        <v>-0.046</v>
       </c>
       <c r="M45">
         <v>-0</v>
@@ -5537,52 +5315,52 @@
         <v>0</v>
       </c>
       <c r="U45">
-        <v>0.651</v>
+        <v>1.25</v>
       </c>
       <c r="V45">
-        <v>0.06569122098890011</v>
+        <v>0.1717032967032967</v>
       </c>
       <c r="X45">
-        <v>0.05048293654458227</v>
+        <v>0.08094377579992376</v>
       </c>
       <c r="AB45">
-        <v>0.04776908188421551</v>
+        <v>0.07732531893855908</v>
       </c>
       <c r="AD45">
-        <v>1.26</v>
+        <v>0.918</v>
       </c>
       <c r="AE45">
         <v>0</v>
       </c>
       <c r="AF45">
-        <v>1.26</v>
+        <v>0.918</v>
       </c>
       <c r="AG45">
-        <v>0.609</v>
+        <v>-0.332</v>
       </c>
       <c r="AH45">
-        <v>0.1128021486123545</v>
+        <v>0.1119785313491095</v>
       </c>
       <c r="AI45">
-        <v>0.1316614420062696</v>
+        <v>0.1342497806376133</v>
       </c>
       <c r="AJ45">
-        <v>0.05789523718984694</v>
+        <v>-0.04778353483016694</v>
       </c>
       <c r="AK45">
-        <v>0.0682811974436596</v>
+        <v>-0.05941302791696491</v>
       </c>
       <c r="AL45">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="AM45">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="AO45">
-        <v>-3.260869565217391</v>
+        <v>-2</v>
       </c>
       <c r="AQ45">
-        <v>-5</v>
+        <v>-2.105263157894737</v>
       </c>
     </row>
     <row r="46">
@@ -5593,7 +5371,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NH SPECIAL PURPOSE ACQUISITION 18 COMPANY Co., Ltd. (KOSDAQ:A365590)</t>
+          <t>Hana Financial Twenty Special Purpose Acquisition Company (KOSDAQ:A400560)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5602,7 +5380,7 @@
         </is>
       </c>
       <c r="K46">
-        <v>-0.089</v>
+        <v>-0.012</v>
       </c>
       <c r="M46">
         <v>-0</v>
@@ -5626,497 +5404,52 @@
         <v>0</v>
       </c>
       <c r="U46">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="V46">
+        <v>0.1077071290944123</v>
+      </c>
+      <c r="X46">
+        <v>0.08077989953265935</v>
+      </c>
+      <c r="AB46">
+        <v>0.07732439992603866</v>
+      </c>
+      <c r="AD46">
+        <v>0.625</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0.625</v>
+      </c>
+      <c r="AG46">
+        <v>0.06599999999999995</v>
+      </c>
+      <c r="AH46">
+        <v>0.1074806534823732</v>
+      </c>
+      <c r="AI46">
+        <v>0.1311647429171039</v>
+      </c>
+      <c r="AJ46">
+        <v>0.01255707762557077</v>
+      </c>
+      <c r="AK46">
+        <v>0.01569186875891582</v>
+      </c>
+      <c r="AL46">
         <v>0.012</v>
       </c>
-      <c r="V46">
-        <v>0.00130718954248366</v>
-      </c>
-      <c r="X46">
-        <v>0.05136127038452938</v>
-      </c>
-      <c r="AB46">
-        <v>0.04785890089163768</v>
-      </c>
-      <c r="AD46">
-        <v>1.5</v>
-      </c>
-      <c r="AE46">
-        <v>0</v>
-      </c>
-      <c r="AF46">
-        <v>1.5</v>
-      </c>
-      <c r="AG46">
-        <v>1.488</v>
-      </c>
-      <c r="AH46">
-        <v>0.1404494382022472</v>
-      </c>
-      <c r="AI46">
-        <v>0.1798561151079137</v>
-      </c>
-      <c r="AJ46">
-        <v>0.1394825646794151</v>
-      </c>
-      <c r="AK46">
-        <v>0.1786743515850144</v>
-      </c>
-      <c r="AL46">
-        <v>0.025</v>
-      </c>
       <c r="AM46">
-        <v>0.006000000000000002</v>
+        <v>0.007</v>
       </c>
       <c r="AO46">
-        <v>-3.76</v>
+        <v>-0.7499999999999999</v>
       </c>
       <c r="AQ46">
-        <v>-15.66666666666666</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>HMCIB NO.5 Special Purpose Acquisition Company (KOSDAQ:A353060)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K47">
-        <v>-0.037</v>
-      </c>
-      <c r="M47">
-        <v>-0</v>
-      </c>
-      <c r="N47">
-        <v>-0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>-0</v>
-      </c>
-      <c r="Q47">
-        <v>-0</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-      <c r="U47">
-        <v>1.74</v>
-      </c>
-      <c r="V47">
-        <v>0.195067264573991</v>
-      </c>
-      <c r="X47">
-        <v>0.0520741831357399</v>
-      </c>
-      <c r="AB47">
-        <v>0.04792778955586857</v>
-      </c>
-      <c r="AD47">
-        <v>1.72</v>
-      </c>
-      <c r="AE47">
-        <v>0</v>
-      </c>
-      <c r="AF47">
-        <v>1.72</v>
-      </c>
-      <c r="AG47">
-        <v>-0.02000000000000002</v>
-      </c>
-      <c r="AH47">
-        <v>0.1616541353383459</v>
-      </c>
-      <c r="AI47">
-        <v>0.16796875</v>
-      </c>
-      <c r="AJ47">
-        <v>-0.002247191011235957</v>
-      </c>
-      <c r="AK47">
-        <v>-0.00235294117647059</v>
-      </c>
-      <c r="AL47">
-        <v>0.037</v>
-      </c>
-      <c r="AM47">
-        <v>0.029</v>
-      </c>
-      <c r="AO47">
-        <v>-0.5135135135135135</v>
-      </c>
-      <c r="AQ47">
-        <v>-0.6551724137931034</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>DB Finance No.9 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A367360)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K48">
-        <v>-0.038</v>
-      </c>
-      <c r="M48">
-        <v>-0</v>
-      </c>
-      <c r="N48">
-        <v>-0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>-0</v>
-      </c>
-      <c r="Q48">
-        <v>-0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>1.52</v>
-      </c>
-      <c r="V48">
-        <v>0.1784037558685446</v>
-      </c>
-      <c r="X48">
-        <v>0.0499561154914995</v>
-      </c>
-      <c r="AB48">
-        <v>0.04771238212189551</v>
-      </c>
-      <c r="AD48">
-        <v>0.898</v>
-      </c>
-      <c r="AE48">
-        <v>0</v>
-      </c>
-      <c r="AF48">
-        <v>0.898</v>
-      </c>
-      <c r="AG48">
-        <v>-0.622</v>
-      </c>
-      <c r="AH48">
-        <v>0.09534933106816734</v>
-      </c>
-      <c r="AI48">
-        <v>0.1082188479151603</v>
-      </c>
-      <c r="AJ48">
-        <v>-0.07875411496581414</v>
-      </c>
-      <c r="AK48">
-        <v>-0.09176748303334316</v>
-      </c>
-      <c r="AL48">
-        <v>0.015</v>
-      </c>
-      <c r="AM48">
-        <v>0.014</v>
-      </c>
-      <c r="AO48">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="AQ48">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Shinhan 7th Special Purpose Acquisition Company (KOSDAQ:A366330)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K49">
-        <v>-0.08699999999999999</v>
-      </c>
-      <c r="M49">
-        <v>-0</v>
-      </c>
-      <c r="N49">
-        <v>-0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>-0</v>
-      </c>
-      <c r="Q49">
-        <v>-0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>0</v>
-      </c>
-      <c r="U49">
-        <v>1.47</v>
-      </c>
-      <c r="V49">
-        <v>0.1849056603773585</v>
-      </c>
-      <c r="X49">
-        <v>0.05026718805653938</v>
-      </c>
-      <c r="AB49">
-        <v>0.04774612830921486</v>
-      </c>
-      <c r="AD49">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AE49">
-        <v>0</v>
-      </c>
-      <c r="AF49">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AG49">
-        <v>-0.53</v>
-      </c>
-      <c r="AH49">
-        <v>0.1057367829021372</v>
-      </c>
-      <c r="AI49">
-        <v>0.1144945188794153</v>
-      </c>
-      <c r="AJ49">
-        <v>-0.07142857142857144</v>
-      </c>
-      <c r="AK49">
-        <v>-0.07863501483679526</v>
-      </c>
-      <c r="AL49">
-        <v>0.058</v>
-      </c>
-      <c r="AM49">
-        <v>0.057</v>
-      </c>
-      <c r="AO49">
-        <v>-0.9310344827586207</v>
-      </c>
-      <c r="AQ49">
-        <v>-0.9473684210526315</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Hana Must Seven Special Purpose Acquisition Company (KOSDAQ:A372290)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K50">
-        <v>-0.022</v>
-      </c>
-      <c r="M50">
-        <v>-0</v>
-      </c>
-      <c r="N50">
-        <v>-0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>-0</v>
-      </c>
-      <c r="Q50">
-        <v>-0</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>1.19</v>
-      </c>
-      <c r="V50">
-        <v>0.1523687580025608</v>
-      </c>
-      <c r="X50">
-        <v>0.04932898563061179</v>
-      </c>
-      <c r="AB50">
-        <v>0.04764190842410868</v>
-      </c>
-      <c r="AD50">
-        <v>0.621</v>
-      </c>
-      <c r="AE50">
-        <v>0</v>
-      </c>
-      <c r="AF50">
-        <v>0.621</v>
-      </c>
-      <c r="AG50">
-        <v>-0.569</v>
-      </c>
-      <c r="AH50">
-        <v>0.07365674297236391</v>
-      </c>
-      <c r="AI50">
-        <v>0.0873294895232738</v>
-      </c>
-      <c r="AJ50">
-        <v>-0.07858030658748791</v>
-      </c>
-      <c r="AK50">
-        <v>-0.09609863198783988</v>
-      </c>
-      <c r="AL50">
-        <v>0.011</v>
-      </c>
-      <c r="AM50">
-        <v>0.009999999999999998</v>
-      </c>
-      <c r="AO50">
-        <v>-1.636363636363636</v>
-      </c>
-      <c r="AQ50">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Eugene Special Purpose Acquisitions 6 Company (KOSDAQ:A373340)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K51">
-        <v>-0.052</v>
-      </c>
-      <c r="M51">
-        <v>-0</v>
-      </c>
-      <c r="N51">
-        <v>-0</v>
-      </c>
-      <c r="O51">
-        <v>0</v>
-      </c>
-      <c r="P51">
-        <v>-0</v>
-      </c>
-      <c r="Q51">
-        <v>-0</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>0</v>
-      </c>
-      <c r="U51">
-        <v>0.006</v>
-      </c>
-      <c r="V51">
-        <v>0.001029159519725557</v>
-      </c>
-      <c r="X51">
-        <v>0.05101796070214535</v>
-      </c>
-      <c r="AB51">
-        <v>0.04782446843899696</v>
-      </c>
-      <c r="AD51">
-        <v>0.87</v>
-      </c>
-      <c r="AE51">
-        <v>0</v>
-      </c>
-      <c r="AF51">
-        <v>0.87</v>
-      </c>
-      <c r="AG51">
-        <v>0.864</v>
-      </c>
-      <c r="AH51">
-        <v>0.1298507462686567</v>
-      </c>
-      <c r="AI51">
-        <v>0.1510416666666667</v>
-      </c>
-      <c r="AJ51">
-        <v>0.1290708096803107</v>
-      </c>
-      <c r="AK51">
-        <v>0.1501564129301356</v>
-      </c>
-      <c r="AL51">
-        <v>0.015</v>
-      </c>
-      <c r="AM51">
-        <v>0.015</v>
-      </c>
-      <c r="AO51">
-        <v>-3.533333333333333</v>
-      </c>
-      <c r="AQ51">
-        <v>-3.533333333333333</v>
+        <v>-1.285714285714286</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_korea/south_korea_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ46"/>
+  <dimension ref="A1:AQ73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,115 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.124</v>
+        <v>0.0296</v>
       </c>
       <c r="E2">
-        <v>0.705</v>
+        <v>-0.0842</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.01666146507850302</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.01666146507850302</v>
       </c>
       <c r="I2">
-        <v>-0.0005337896610241782</v>
+        <v>-0.002459900670144768</v>
       </c>
       <c r="J2">
-        <v>-0.0004655883964642663</v>
+        <v>-0.002233835199375192</v>
       </c>
       <c r="K2">
-        <v>324.646</v>
+        <v>30.109</v>
       </c>
       <c r="L2">
-        <v>0.4195948626945651</v>
+        <v>0.07399115811926954</v>
       </c>
       <c r="M2">
-        <v>45.42424</v>
+        <v>20.0657</v>
       </c>
       <c r="N2">
-        <v>0.01951070583333691</v>
+        <v>0.007007158821064395</v>
       </c>
       <c r="O2">
-        <v>0.1399192967108789</v>
+        <v>0.6664352851306918</v>
       </c>
       <c r="P2">
-        <v>19.16624</v>
+        <v>9.8057</v>
       </c>
       <c r="Q2">
-        <v>0.00823231980482525</v>
+        <v>0.003424256181030871</v>
       </c>
       <c r="R2">
-        <v>0.05903735145358329</v>
+        <v>0.3256733866950082</v>
       </c>
       <c r="S2">
-        <v>26.258</v>
+        <v>10.26</v>
       </c>
       <c r="T2">
-        <v>0.5780614051000083</v>
+        <v>0.5113203127725422</v>
       </c>
       <c r="U2">
-        <v>199.721</v>
+        <v>300.57</v>
       </c>
       <c r="V2">
-        <v>0.08578454322493632</v>
+        <v>0.1049622852353681</v>
       </c>
       <c r="W2">
-        <v>0.002909863315854644</v>
+        <v>0.01962518217148409</v>
       </c>
       <c r="X2">
-        <v>0.08031357759078919</v>
+        <v>0.0680419468053504</v>
       </c>
       <c r="Y2">
-        <v>-0.07740371427493455</v>
+        <v>-0.04841676463386631</v>
       </c>
       <c r="Z2">
-        <v>0.3707386377249095</v>
+        <v>0.2087463482072551</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>-0.006144043690977358</v>
       </c>
       <c r="AB2">
-        <v>0.07730243933280354</v>
+        <v>0.06585592774441308</v>
       </c>
       <c r="AC2">
-        <v>-0.07730243933280354</v>
+        <v>-0.07201776396174449</v>
       </c>
       <c r="AD2">
-        <v>177.407</v>
+        <v>178.759</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>177.407</v>
+        <v>178.759</v>
       </c>
       <c r="AG2">
-        <v>-22.31399999999999</v>
+        <v>-121.811</v>
       </c>
       <c r="AH2">
-        <v>0.07080484854386834</v>
+        <v>0.05875670819913101</v>
       </c>
       <c r="AI2">
-        <v>0.07775903277541017</v>
+        <v>0.06592334690087362</v>
       </c>
       <c r="AJ2">
-        <v>-0.009677100391351407</v>
+        <v>-0.04442756171244395</v>
       </c>
       <c r="AK2">
-        <v>-0.01071873246689365</v>
+        <v>-0.05052199270939744</v>
       </c>
       <c r="AL2">
-        <v>0.54</v>
+        <v>3.121</v>
       </c>
       <c r="AM2">
-        <v>-5.965</v>
+        <v>-11.167</v>
+      </c>
+      <c r="AN2">
+        <v>125.8866197183099</v>
       </c>
       <c r="AO2">
-        <v>-0.7648148148148147</v>
+        <v>-0.3207305350849087</v>
+      </c>
+      <c r="AP2">
+        <v>-85.78239436619717</v>
       </c>
       <c r="AQ2">
-        <v>0.06923721709974853</v>
+        <v>0.08963911525029104</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Daishin Balance No.10 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A387310)</t>
+          <t>Capstone Partners Co., Ltd. (KOSDAQ:A452300)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,8 +721,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G3">
+        <v>1.606635071090047</v>
+      </c>
+      <c r="H3">
+        <v>1.606635071090047</v>
+      </c>
+      <c r="I3">
+        <v>0.2819905213270142</v>
+      </c>
+      <c r="J3">
+        <v>0.2188107334037983</v>
+      </c>
       <c r="K3">
-        <v>0.067</v>
+        <v>0.755</v>
+      </c>
+      <c r="L3">
+        <v>0.1789099526066351</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,67 +761,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.08</v>
+        <v>0.309</v>
       </c>
       <c r="V3">
-        <v>0.06967741935483872</v>
-      </c>
-      <c r="W3">
-        <v>0.007502799552071669</v>
+        <v>0.005732838589981447</v>
       </c>
       <c r="X3">
-        <v>0.07865312974488173</v>
-      </c>
-      <c r="Y3">
-        <v>-0.07115033019281006</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0.007757488960496482</v>
+        <v>0.06807560317948583</v>
       </c>
       <c r="AB3">
-        <v>0.07731156925487494</v>
-      </c>
-      <c r="AC3">
-        <v>-0.06955408029437846</v>
+        <v>0.06586636617139528</v>
       </c>
       <c r="AD3">
-        <v>0.725</v>
+        <v>5.49</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.725</v>
+        <v>5.49</v>
       </c>
       <c r="AG3">
-        <v>-0.3550000000000001</v>
+        <v>5.181</v>
       </c>
       <c r="AH3">
-        <v>0.04468412942989214</v>
+        <v>0.09243980468092272</v>
       </c>
       <c r="AI3">
-        <v>0.09023024268823895</v>
+        <v>0.2260189378344998</v>
       </c>
       <c r="AJ3">
-        <v>-0.02344007923407066</v>
+        <v>0.08769316700800596</v>
       </c>
       <c r="AK3">
-        <v>-0.05104241552839685</v>
+        <v>0.2160460364455194</v>
       </c>
       <c r="AL3">
-        <v>0.066</v>
+        <v>0.374</v>
       </c>
       <c r="AM3">
-        <v>-0.002000000000000002</v>
+        <v>0.374</v>
+      </c>
+      <c r="AN3">
+        <v>3.866197183098592</v>
       </c>
       <c r="AO3">
-        <v>0.9848484848484849</v>
+        <v>3.181818181818182</v>
+      </c>
+      <c r="AP3">
+        <v>3.648591549295775</v>
       </c>
       <c r="AQ3">
-        <v>-32.49999999999997</v>
+        <v>3.181818181818182</v>
       </c>
     </row>
     <row r="4">
@@ -811,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HMCIB NO.5 Special Purpose Acquisition Company (KOSDAQ:A353060)</t>
+          <t>DSC Investment Inc. (KOSDAQ:A241520)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -819,17 +831,38 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.225</v>
+      </c>
+      <c r="E4">
+        <v>0.327</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
       <c r="K4">
-        <v>0.041</v>
+        <v>4.27</v>
+      </c>
+      <c r="L4">
+        <v>0.2754838709677419</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>2.22</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.03394495412844037</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.5199063231850118</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -841,64 +874,67 @@
         <v>-0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.22</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>1.42</v>
+        <v>10.8</v>
       </c>
       <c r="V4">
-        <v>0.1742331288343558</v>
+        <v>0.1651376146788991</v>
       </c>
       <c r="W4">
-        <v>0.004812206572769953</v>
+        <v>0.0646969696969697</v>
       </c>
       <c r="X4">
-        <v>0.08240460307261063</v>
+        <v>0.07136264089636737</v>
       </c>
       <c r="Y4">
-        <v>-0.07759239649984068</v>
+        <v>-0.006665671199397677</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>0.2158774373259053</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07603802043370259</v>
+        <v>0.06437707044207397</v>
       </c>
       <c r="AC4">
-        <v>-0.07603802043370259</v>
+        <v>-0.06437707044207397</v>
       </c>
       <c r="AD4">
-        <v>1.44</v>
+        <v>17.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.44</v>
+        <v>17.2</v>
       </c>
       <c r="AG4">
-        <v>0.02000000000000002</v>
+        <v>6.399999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.1501564129301355</v>
+        <v>0.2082324455205811</v>
       </c>
       <c r="AI4">
-        <v>0.1696113074204947</v>
+        <v>0.1888035126234907</v>
       </c>
       <c r="AJ4">
-        <v>0.002447980416156673</v>
+        <v>0.08913649025069635</v>
       </c>
       <c r="AK4">
-        <v>0.002828854314002831</v>
+        <v>0.07970112079701118</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.1</v>
+        <v>-0.032</v>
       </c>
       <c r="AQ4">
         <v>-0</v>
@@ -912,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IBKS No.16 Special Purpose Acquisition Company (KOSDAQ:A388790)</t>
+          <t>Kyobo 11 Special Purpose Acquisition Company (KOSDAQ:A397880)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -921,7 +957,7 @@
         </is>
       </c>
       <c r="K5">
-        <v>-0.036</v>
+        <v>0.092</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -930,7 +966,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -939,25 +975,25 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.93</v>
+        <v>1.69</v>
       </c>
       <c r="V5">
-        <v>0.1522094926350246</v>
+        <v>0.1656862745098039</v>
       </c>
       <c r="W5">
-        <v>-0.006509945750452079</v>
+        <v>0.01525704809286899</v>
       </c>
       <c r="X5">
-        <v>0.08154180366359629</v>
+        <v>0.06927766314593735</v>
       </c>
       <c r="Y5">
-        <v>-0.08805174941404836</v>
+        <v>-0.05402061505306836</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -966,40 +1002,40 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07622446748457111</v>
+        <v>0.0649197501606084</v>
       </c>
       <c r="AC5">
-        <v>-0.07622446748457111</v>
+        <v>-0.0649197501606084</v>
       </c>
       <c r="AD5">
-        <v>0.897</v>
+        <v>1.64</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.897</v>
+        <v>1.64</v>
       </c>
       <c r="AG5">
-        <v>-0.03300000000000003</v>
+        <v>-0.05000000000000004</v>
       </c>
       <c r="AH5">
-        <v>0.1280148423005566</v>
+        <v>0.1385135135135135</v>
       </c>
       <c r="AI5">
-        <v>0.1652846876727474</v>
+        <v>0.2009803921568627</v>
       </c>
       <c r="AJ5">
-        <v>-0.005430311008721414</v>
+        <v>-0.004926108374384242</v>
       </c>
       <c r="AK5">
-        <v>-0.007338225483655777</v>
+        <v>-0.007727975270479141</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.065</v>
+        <v>-0.243</v>
       </c>
       <c r="AQ5">
         <v>-0</v>
@@ -1013,7 +1049,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KB No.20 Special Purpose Acquisition Company</t>
+          <t>Kiwoom No.6 Special Purpose Acquisition Company (KOSDAQ:A413600)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1022,7 +1058,7 @@
         </is>
       </c>
       <c r="K6">
-        <v>0.014</v>
+        <v>0.026</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1046,19 +1082,19 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.089</v>
+        <v>0.93</v>
       </c>
       <c r="V6">
-        <v>0.01193029490616622</v>
+        <v>0.1634446397188049</v>
       </c>
       <c r="W6">
-        <v>0.001333333333333333</v>
+        <v>0.005664488017429194</v>
       </c>
       <c r="X6">
-        <v>0.08121203689240122</v>
+        <v>0.06910249204279173</v>
       </c>
       <c r="Y6">
-        <v>-0.07987870355906788</v>
+        <v>-0.06343800402536254</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1067,40 +1103,40 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07629832062832352</v>
+        <v>0.06496972831930256</v>
       </c>
       <c r="AC6">
-        <v>-0.07629832062832352</v>
+        <v>-0.06496972831930256</v>
       </c>
       <c r="AD6">
-        <v>1.01</v>
+        <v>0.866</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.01</v>
+        <v>0.866</v>
       </c>
       <c r="AG6">
-        <v>0.921</v>
+        <v>-0.06400000000000006</v>
       </c>
       <c r="AH6">
-        <v>0.1192443919716647</v>
+        <v>0.1320927394752898</v>
       </c>
       <c r="AI6">
-        <v>0.1042311661506708</v>
+        <v>0.1496716211545109</v>
       </c>
       <c r="AJ6">
-        <v>0.1098914210714712</v>
+        <v>-0.01137575542125845</v>
       </c>
       <c r="AK6">
-        <v>0.09592750755129675</v>
+        <v>-0.01317957166392093</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-0.109</v>
+        <v>-0.092</v>
       </c>
       <c r="AQ6">
         <v>-0</v>
@@ -1114,7 +1150,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Leaders Technology Investment Co.,Ltd (KOSDAQ:A019570)</t>
+          <t>Q Capital Partners Co., Ltd. (KOSDAQ:A016600)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1122,6 +1158,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D7">
+        <v>-0.22</v>
+      </c>
+      <c r="E7">
+        <v>-0.0842</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1135,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>-3.19</v>
+        <v>4.62</v>
       </c>
       <c r="L7">
-        <v>-0.3517089305402425</v>
+        <v>1.711111111111111</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1147,7 +1189,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1156,67 +1198,67 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2.11</v>
+        <v>17.5</v>
       </c>
       <c r="V7">
-        <v>0.05749318801089918</v>
+        <v>0.3608247422680412</v>
       </c>
       <c r="W7">
-        <v>-0.08264248704663212</v>
+        <v>0.05049180327868853</v>
       </c>
       <c r="X7">
-        <v>0.08642972059153353</v>
+        <v>0.06810505202416858</v>
       </c>
       <c r="Y7">
-        <v>-0.1690722076381657</v>
+        <v>-0.01761324874548006</v>
       </c>
       <c r="Z7">
-        <v>0.1849133537206931</v>
+        <v>0.02662643117067543</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07666703825143154</v>
+        <v>0.06526913597009119</v>
       </c>
       <c r="AC7">
-        <v>-0.07666703825143154</v>
+        <v>-0.06526913597009119</v>
       </c>
       <c r="AD7">
-        <v>11.6</v>
+        <v>5.01</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>11.6</v>
+        <v>5.01</v>
       </c>
       <c r="AG7">
-        <v>9.49</v>
+        <v>-12.49</v>
       </c>
       <c r="AH7">
-        <v>0.2401656314699793</v>
+        <v>0.09362735937207999</v>
       </c>
       <c r="AI7">
-        <v>0.2959183673469388</v>
+        <v>0.04681805438744042</v>
       </c>
       <c r="AJ7">
-        <v>0.2054557263476943</v>
+        <v>-0.3468480977506249</v>
       </c>
       <c r="AK7">
-        <v>0.2558641143165273</v>
+        <v>-0.1395374818456038</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.103</v>
+        <v>-0.057</v>
       </c>
       <c r="AQ7">
         <v>-0</v>
@@ -1230,7 +1272,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NH Special Purpose Acquisition 19 Company (KOSE:A380440)</t>
+          <t>NAU IB Capital (KOSDAQ:A293580)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1238,92 +1280,110 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D8">
+        <v>0.118</v>
+      </c>
+      <c r="E8">
+        <v>0.109</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
       <c r="K8">
-        <v>0.545</v>
+        <v>4.8</v>
+      </c>
+      <c r="L8">
+        <v>0.3428571428571429</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>1.2233</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.01490012180267966</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.2548541666666667</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>1.2233</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.01490012180267966</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.2548541666666667</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>0.051</v>
+        <v>3.17</v>
       </c>
       <c r="V8">
-        <v>0.0006431273644388398</v>
+        <v>0.03861144945188794</v>
       </c>
       <c r="W8">
-        <v>0.006442080378250592</v>
+        <v>0.07704654895666131</v>
       </c>
       <c r="X8">
-        <v>0.0812716378390541</v>
+        <v>0.07061924115833633</v>
       </c>
       <c r="Y8">
-        <v>-0.07482955746080351</v>
+        <v>0.006427307798324983</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>0.1933701657458564</v>
       </c>
       <c r="AA8">
-        <v>-0.0003927178579798918</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07628486286737239</v>
+        <v>0.06536532594912216</v>
       </c>
       <c r="AC8">
-        <v>-0.07667758072535229</v>
+        <v>-0.06536532594912216</v>
       </c>
       <c r="AD8">
-        <v>10.9</v>
+        <v>18.6</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>10.9</v>
+        <v>18.6</v>
       </c>
       <c r="AG8">
-        <v>10.849</v>
+        <v>15.43</v>
       </c>
       <c r="AH8">
-        <v>0.1208425720620843</v>
+        <v>0.1847070506454817</v>
       </c>
       <c r="AI8">
-        <v>0.1344019728729963</v>
+        <v>0.2099322799097066</v>
       </c>
       <c r="AJ8">
-        <v>0.1203452062696203</v>
+        <v>0.1582077309545781</v>
       </c>
       <c r="AK8">
-        <v>0.1338572962035312</v>
+        <v>0.1806157087674119</v>
       </c>
       <c r="AL8">
-        <v>0.252</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>-0.732</v>
-      </c>
-      <c r="AO8">
-        <v>-0.1904761904761905</v>
-      </c>
-      <c r="AQ8">
-        <v>0.06557377049180328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1334,7 +1394,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T.S. Investment Corporation (KOSDAQ:A246690)</t>
+          <t>Leaders Technology Investment Co.,Ltd (KOSDAQ:A019570)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1342,12 +1402,6 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.446</v>
-      </c>
-      <c r="E9">
-        <v>0.746</v>
-      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -1360,92 +1414,74 @@
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
-        <v>6.8</v>
-      </c>
-      <c r="L9">
-        <v>0.3756906077348066</v>
-      </c>
       <c r="M9">
-        <v>0.2744</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.005338521400778211</v>
-      </c>
-      <c r="O9">
-        <v>0.04035294117647059</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>0.2744</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.005338521400778211</v>
-      </c>
-      <c r="R9">
-        <v>0.04035294117647059</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>6.29</v>
+        <v>10.6</v>
       </c>
       <c r="V9">
-        <v>0.1223735408560311</v>
-      </c>
-      <c r="W9">
-        <v>0.1382113821138211</v>
+        <v>0.3955223880597015</v>
       </c>
       <c r="X9">
-        <v>0.08550480724514203</v>
-      </c>
-      <c r="Y9">
-        <v>0.05270657486867908</v>
+        <v>0.0699634314606413</v>
       </c>
       <c r="Z9">
-        <v>0.3524143302180685</v>
+        <v>0.02266215160197969</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.076717183148684</v>
+        <v>0.06544048507257749</v>
       </c>
       <c r="AC9">
-        <v>-0.076717183148684</v>
+        <v>-0.06544048507257749</v>
       </c>
       <c r="AD9">
-        <v>14.6</v>
+        <v>5.21</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>14.6</v>
+        <v>5.21</v>
       </c>
       <c r="AG9">
-        <v>8.309999999999999</v>
+        <v>-5.39</v>
       </c>
       <c r="AH9">
-        <v>0.2212121212121212</v>
+        <v>0.1627616369884411</v>
       </c>
       <c r="AI9">
-        <v>0.2306477093206951</v>
+        <v>0.1612503868771278</v>
       </c>
       <c r="AJ9">
-        <v>0.139172667894825</v>
+        <v>-0.2517515179822513</v>
       </c>
       <c r="AK9">
-        <v>0.1457639010699877</v>
+        <v>-0.2482726853984339</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>-0.153</v>
+      </c>
+      <c r="AQ9">
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -1456,7 +1492,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Q Capital Partners Co., Ltd. (KOSDAQ:A016600)</t>
+          <t>T.S. Investment Corporation (KOSDAQ:A246690)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1464,6 +1500,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.154</v>
+      </c>
+      <c r="E10">
+        <v>0.08130000000000001</v>
+      </c>
       <c r="G10">
         <v>0</v>
       </c>
@@ -1477,82 +1519,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>-5.56</v>
+        <v>5.53</v>
       </c>
       <c r="L10">
-        <v>-18.91156462585034</v>
+        <v>0.3072222222222222</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>1.1526</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.02590112359550562</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>0.2084267631103074</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>0.2856</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.006417977528089887</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>0.05164556962025316</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>0.8670000000000001</v>
+      </c>
+      <c r="T10">
+        <v>0.752212389380531</v>
       </c>
       <c r="U10">
-        <v>0.697</v>
+        <v>7.81</v>
       </c>
       <c r="V10">
-        <v>0.01300373134328358</v>
+        <v>0.1755056179775281</v>
       </c>
       <c r="W10">
-        <v>-0.04951024042742654</v>
+        <v>0.1194384449244061</v>
       </c>
       <c r="X10">
-        <v>0.08301315561444138</v>
+        <v>0.06904163629931483</v>
       </c>
       <c r="Y10">
-        <v>-0.1325233960418679</v>
+        <v>0.05039680862509123</v>
       </c>
       <c r="Z10">
-        <v>0.002737940026075619</v>
+        <v>0.3348401138456387</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.07686561388748069</v>
+        <v>0.06555323697981864</v>
       </c>
       <c r="AC10">
-        <v>-0.07686561388748069</v>
+        <v>-0.06555323697981864</v>
       </c>
       <c r="AD10">
-        <v>10.6</v>
+        <v>6.64</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>10.6</v>
+        <v>6.64</v>
       </c>
       <c r="AG10">
-        <v>9.903</v>
+        <v>-1.17</v>
       </c>
       <c r="AH10">
-        <v>0.1651090342679128</v>
+        <v>0.1298396558466954</v>
       </c>
       <c r="AI10">
-        <v>0.1038197845249755</v>
+        <v>0.1005451241671714</v>
       </c>
       <c r="AJ10">
-        <v>0.1559453884068469</v>
+        <v>-0.02700207708285253</v>
       </c>
       <c r="AK10">
-        <v>0.09765983254933286</v>
+        <v>-0.02009273570324575</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1569,7 +1614,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Globon Co., Ltd. (KOSDAQ:A019660)</t>
+          <t>M-Venture Investment, Inc. (KOSDAQ:A019590)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1577,23 +1622,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
       <c r="K11">
-        <v>-10.3</v>
-      </c>
-      <c r="L11">
-        <v>-3.626760563380282</v>
+        <v>-18.4</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1617,61 +1647,61 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="V11">
-        <v>0.08553971486761711</v>
+        <v>0.04161849710982659</v>
       </c>
       <c r="W11">
-        <v>-0.6358024691358025</v>
+        <v>-0.4125560538116592</v>
       </c>
       <c r="X11">
-        <v>0.08296606190064822</v>
+        <v>0.06796995994498148</v>
       </c>
       <c r="Y11">
-        <v>-0.7187685310364508</v>
+        <v>-0.4805260137566406</v>
       </c>
       <c r="Z11">
-        <v>0.1476782278612656</v>
+        <v>0</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07686862551859609</v>
+        <v>0.06569600322679256</v>
       </c>
       <c r="AC11">
-        <v>-0.07686862551859609</v>
+        <v>-0.06569600322679256</v>
       </c>
       <c r="AD11">
-        <v>9.630000000000001</v>
+        <v>6.69</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>9.630000000000001</v>
+        <v>6.69</v>
       </c>
       <c r="AG11">
-        <v>5.430000000000001</v>
+        <v>3.81</v>
       </c>
       <c r="AH11">
-        <v>0.1639707134343606</v>
+        <v>0.08815390697061537</v>
       </c>
       <c r="AI11">
-        <v>0.3909866017052375</v>
+        <v>0.1284315607602227</v>
       </c>
       <c r="AJ11">
-        <v>0.09957821382725106</v>
+        <v>0.05218463224215861</v>
       </c>
       <c r="AK11">
-        <v>0.2657856093979442</v>
+        <v>0.07742328794960375</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-0.757</v>
+        <v>-0.507</v>
       </c>
       <c r="AQ11">
         <v>-0</v>
@@ -1685,7 +1715,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DSC Investment Inc. (KOSDAQ:A241520)</t>
+          <t>AJU IB INVESTMENT Co., Ltd. (KOSDAQ:A027360)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1694,10 +1724,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.485</v>
+        <v>0.0164</v>
       </c>
       <c r="E12">
-        <v>0.705</v>
+        <v>-0.08</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1712,91 +1742,91 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>18.6</v>
+        <v>10.7</v>
       </c>
       <c r="L12">
-        <v>0.6179401993355482</v>
+        <v>0.2622549019607843</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>1.7745</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.007019382911392404</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0.1658411214953271</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>1.7745</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.007019382911392404</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0.1658411214953271</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
       <c r="U12">
-        <v>8.1</v>
+        <v>39.3</v>
       </c>
       <c r="V12">
-        <v>0.1094594594594595</v>
+        <v>0.1554588607594936</v>
       </c>
       <c r="W12">
-        <v>0.3268892794376099</v>
+        <v>0.06323877068557919</v>
       </c>
       <c r="X12">
-        <v>0.0827266005496208</v>
+        <v>0.06757943892574299</v>
       </c>
       <c r="Y12">
-        <v>0.2441626788879891</v>
+        <v>-0.004340668240163797</v>
       </c>
       <c r="Z12">
-        <v>0.4649366697559468</v>
+        <v>0.2260387811634349</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.07688406694254744</v>
+        <v>0.06575148840531604</v>
       </c>
       <c r="AC12">
-        <v>-0.07688406694254744</v>
+        <v>-0.06575148840531604</v>
       </c>
       <c r="AD12">
-        <v>13.9</v>
+        <v>19.6</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>13.9</v>
+        <v>19.6</v>
       </c>
       <c r="AG12">
-        <v>5.800000000000001</v>
+        <v>-19.7</v>
       </c>
       <c r="AH12">
-        <v>0.1581342434584755</v>
+        <v>0.07195301027900146</v>
       </c>
       <c r="AI12">
-        <v>0.1703431372549019</v>
+        <v>0.09328891004283675</v>
       </c>
       <c r="AJ12">
-        <v>0.07268170426065164</v>
+        <v>-0.08451308451308448</v>
       </c>
       <c r="AK12">
-        <v>0.07891156462585035</v>
+        <v>-0.1153395784543325</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-0.01</v>
-      </c>
-      <c r="AQ12">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1807,7 +1837,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M-Venture Investment, Inc. (KOSDAQ:A019590)</t>
+          <t>Mirae Asset Venture Investment Co., Ltd. (KOSDAQ:A100790)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1816,7 +1846,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.119</v>
+        <v>0.103</v>
+      </c>
+      <c r="E13">
+        <v>0.135</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1831,94 +1864,91 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>7.26</v>
+        <v>24.5</v>
       </c>
       <c r="L13">
-        <v>0.654054054054054</v>
+        <v>0.2078032230703986</v>
       </c>
       <c r="M13">
-        <v>0.436</v>
+        <v>3.99</v>
       </c>
       <c r="N13">
-        <v>0.004733984799131379</v>
+        <v>0.01683544303797468</v>
       </c>
       <c r="O13">
-        <v>0.06005509641873279</v>
+        <v>0.1628571428571429</v>
       </c>
       <c r="P13">
-        <v>0.436</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.004733984799131379</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>0.06005509641873279</v>
+        <v>-0</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13">
-        <v>1.31</v>
+        <v>41.4</v>
       </c>
       <c r="V13">
-        <v>0.01422366992399566</v>
+        <v>0.1746835443037975</v>
       </c>
       <c r="W13">
-        <v>0.2304761904761905</v>
+        <v>0.1230537418382722</v>
       </c>
       <c r="X13">
-        <v>0.0826325815857161</v>
+        <v>0.06728895486929623</v>
       </c>
       <c r="Y13">
-        <v>0.1478436088904744</v>
+        <v>0.05576478696897599</v>
       </c>
       <c r="Z13">
-        <v>0.2577199907127931</v>
+        <v>0.6483436716378513</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.07689018876553329</v>
+        <v>0.06579405619868781</v>
       </c>
       <c r="AC13">
-        <v>-0.07689018876553329</v>
+        <v>-0.06579405619868781</v>
       </c>
       <c r="AD13">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG13">
-        <v>15.69</v>
+        <v>-26.4</v>
       </c>
       <c r="AH13">
-        <v>0.155820348304308</v>
+        <v>0.05952380952380952</v>
       </c>
       <c r="AI13">
-        <v>0.275974025974026</v>
+        <v>0.0562429696287964</v>
       </c>
       <c r="AJ13">
-        <v>0.1455608126913443</v>
+        <v>-0.1253561253561254</v>
       </c>
       <c r="AK13">
-        <v>0.2602421628794162</v>
+        <v>-0.1171770972037284</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-0.293</v>
-      </c>
-      <c r="AQ13">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1929,7 +1959,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NAU IB Capital (KOSDAQ:A293580)</t>
+          <t>Hi Special Purpose Acquisition Company VII (KOSDAQ:A400840)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1937,104 +1967,89 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
       <c r="K14">
-        <v>7.82</v>
-      </c>
-      <c r="L14">
-        <v>0.4418079096045198</v>
+        <v>0.23</v>
       </c>
       <c r="M14">
-        <v>1.65664</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.01738342077649528</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>0.211846547314578</v>
+        <v>-0</v>
       </c>
       <c r="P14">
-        <v>0.97864</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.01026904512067156</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.1251457800511509</v>
+        <v>-0</v>
       </c>
       <c r="S14">
-        <v>0.6779999999999999</v>
-      </c>
-      <c r="T14">
-        <v>0.4092621209194514</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>4.2</v>
+        <v>1.24</v>
       </c>
       <c r="V14">
-        <v>0.04407135362014691</v>
+        <v>0.1485029940119761</v>
       </c>
       <c r="W14">
-        <v>0.1148311306901615</v>
+        <v>0.03234880450070324</v>
       </c>
       <c r="X14">
-        <v>0.08163547880651098</v>
+        <v>0.0688561385798188</v>
       </c>
       <c r="Y14">
-        <v>0.03319565188365056</v>
+        <v>-0.03650733407911556</v>
       </c>
       <c r="Z14">
-        <v>0.2688335358444715</v>
+        <v>0</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.07695724586054327</v>
+        <v>0.06582302033288701</v>
       </c>
       <c r="AC14">
-        <v>-0.07695724586054327</v>
+        <v>-0.06582302033288701</v>
       </c>
       <c r="AD14">
-        <v>14.3</v>
+        <v>1.17</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>14.3</v>
+        <v>1.17</v>
       </c>
       <c r="AG14">
-        <v>10.1</v>
+        <v>-0.07000000000000006</v>
       </c>
       <c r="AH14">
-        <v>0.1304744525547445</v>
+        <v>0.1228991596638655</v>
       </c>
       <c r="AI14">
-        <v>0.1866840731070496</v>
+        <v>0.1302895322939866</v>
       </c>
       <c r="AJ14">
-        <v>0.09582542694497155</v>
+        <v>-0.008454106280193245</v>
       </c>
       <c r="AK14">
-        <v>0.1395027624309392</v>
+        <v>-0.009043927648578819</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>-0.294</v>
+      </c>
+      <c r="AQ14">
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -2045,7 +2060,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mirae Asset Venture Investment Co., Ltd. (KOSDAQ:A100790)</t>
+          <t>Hana Financial Twenty-one Special Purpose Acquisition Company (KOSDAQ:A406760)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2053,104 +2068,89 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
       <c r="K15">
-        <v>55.6</v>
-      </c>
-      <c r="L15">
-        <v>0.2763419483101392</v>
+        <v>0.208</v>
       </c>
       <c r="M15">
-        <v>5.78</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.03567901234567902</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>0.1039568345323741</v>
+        <v>-0</v>
       </c>
       <c r="P15">
-        <v>2.64</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.0162962962962963</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>0.04748201438848921</v>
+        <v>-0</v>
       </c>
       <c r="S15">
-        <v>3.14</v>
-      </c>
-      <c r="T15">
-        <v>0.5432525951557093</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>40</v>
+        <v>0.333</v>
       </c>
       <c r="V15">
-        <v>0.2469135802469136</v>
+        <v>0.02775</v>
       </c>
       <c r="W15">
-        <v>0.3008658008658008</v>
+        <v>0.02238966630785791</v>
       </c>
       <c r="X15">
-        <v>0.08129528489324243</v>
+        <v>0.06766718662812742</v>
       </c>
       <c r="Y15">
-        <v>0.2195705159725584</v>
+        <v>-0.04527752032026951</v>
       </c>
       <c r="Z15">
-        <v>1.455618818865167</v>
+        <v>0</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.07698105537646893</v>
+        <v>0.06589026894245481</v>
       </c>
       <c r="AC15">
-        <v>-0.07698105537646893</v>
+        <v>-0.06589026894245481</v>
       </c>
       <c r="AD15">
-        <v>22.4</v>
+        <v>0.982</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>22.4</v>
+        <v>0.982</v>
       </c>
       <c r="AG15">
-        <v>-17.6</v>
+        <v>0.649</v>
       </c>
       <c r="AH15">
-        <v>0.1214750542299349</v>
+        <v>0.07564319827453397</v>
       </c>
       <c r="AI15">
-        <v>0.1009918845807033</v>
+        <v>0.08861216386933767</v>
       </c>
       <c r="AJ15">
-        <v>-0.1218836565096953</v>
+        <v>0.05130840382638944</v>
       </c>
       <c r="AK15">
-        <v>-0.09680968096809681</v>
+        <v>0.06037770955437716</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>-0.302</v>
+      </c>
+      <c r="AQ15">
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aju IB Investment Co., Ltd. (KOSDAQ:A027360)</t>
+          <t>Company K Partners Limited (KOSDAQ:A307930)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2169,12 +2169,6 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D16">
-        <v>0.00697</v>
-      </c>
-      <c r="E16">
-        <v>-0.08990000000000001</v>
-      </c>
       <c r="G16">
         <v>0</v>
       </c>
@@ -2188,91 +2182,91 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>3.9</v>
+        <v>6.51</v>
       </c>
       <c r="L16">
-        <v>0.1018276762402089</v>
+        <v>0.4969465648854962</v>
       </c>
       <c r="M16">
-        <v>8.253000000000002</v>
+        <v>-0</v>
       </c>
       <c r="N16">
-        <v>0.03994675701839304</v>
+        <v>-0</v>
       </c>
       <c r="O16">
-        <v>2.116153846153847</v>
+        <v>-0</v>
       </c>
       <c r="P16">
-        <v>8.253000000000002</v>
+        <v>-0</v>
       </c>
       <c r="Q16">
-        <v>0.03994675701839304</v>
+        <v>-0</v>
       </c>
       <c r="R16">
-        <v>2.116153846153847</v>
+        <v>-0</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
       <c r="U16">
-        <v>11.8</v>
+        <v>2.25</v>
       </c>
       <c r="V16">
-        <v>0.05711519845111327</v>
+        <v>0.02781211372064277</v>
       </c>
       <c r="W16">
-        <v>0.01913640824337586</v>
+        <v>0.1291666666666667</v>
       </c>
       <c r="X16">
-        <v>0.08053116518682496</v>
+        <v>0.06662827419703168</v>
       </c>
       <c r="Y16">
-        <v>-0.06139475694344911</v>
+        <v>0.062538392469635</v>
       </c>
       <c r="Z16">
-        <v>0.1829035339063992</v>
+        <v>0.2444668383533012</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.07703637413212232</v>
+        <v>0.06589525210488668</v>
       </c>
       <c r="AC16">
-        <v>-0.07703637413212232</v>
+        <v>-0.06589525210488668</v>
       </c>
       <c r="AD16">
-        <v>23.1</v>
+        <v>2.5</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>23.1</v>
+        <v>2.5</v>
       </c>
       <c r="AG16">
-        <v>11.3</v>
+        <v>0.25</v>
       </c>
       <c r="AH16">
-        <v>0.1005659555942534</v>
+        <v>0.02997601918465228</v>
       </c>
       <c r="AI16">
-        <v>0.1201248049921997</v>
+        <v>0.03955696202531645</v>
       </c>
       <c r="AJ16">
-        <v>0.05185865075722808</v>
+        <v>0.003080714725816389</v>
       </c>
       <c r="AK16">
-        <v>0.06260387811634349</v>
+        <v>0.004101722723543888</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>-0.004</v>
+      </c>
+      <c r="AQ16">
+        <v>-0</v>
       </c>
     </row>
     <row r="17">
@@ -2283,7 +2277,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hanwha Plus No2 Special Purpose Acquisition Company (KOSDAQ:A386580)</t>
+          <t>SV Investment Corporation (KOSDAQ:A289080)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2291,89 +2285,110 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D17">
+        <v>-0.0563</v>
+      </c>
+      <c r="E17">
+        <v>-0.333</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
       <c r="K17">
-        <v>-0.012</v>
+        <v>1.12</v>
+      </c>
+      <c r="L17">
+        <v>0.06292134831460675</v>
       </c>
       <c r="M17">
-        <v>-0</v>
+        <v>0.798</v>
       </c>
       <c r="N17">
-        <v>-0</v>
+        <v>0.009366197183098592</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>0.7125</v>
       </c>
       <c r="P17">
-        <v>-0</v>
+        <v>0.798</v>
       </c>
       <c r="Q17">
-        <v>-0</v>
+        <v>0.009366197183098592</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>0.7125</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
       <c r="U17">
-        <v>0.883</v>
+        <v>3.88</v>
       </c>
       <c r="V17">
-        <v>0.13023598820059</v>
+        <v>0.04553990610328638</v>
       </c>
       <c r="W17">
-        <v>-0.001807228915662651</v>
+        <v>0.02231075697211156</v>
       </c>
       <c r="X17">
-        <v>0.08034345058099179</v>
+        <v>0.0665318173437658</v>
       </c>
       <c r="Y17">
-        <v>-0.08215067949665444</v>
+        <v>-0.04422106037165424</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>0.3867043232674343</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.07705036907001388</v>
+        <v>0.06591056071430519</v>
       </c>
       <c r="AC17">
-        <v>-0.07705036907001388</v>
+        <v>-0.06591056071430519</v>
       </c>
       <c r="AD17">
-        <v>0.714</v>
+        <v>2.23</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>0.714</v>
+        <v>2.23</v>
       </c>
       <c r="AG17">
-        <v>-0.169</v>
+        <v>-1.65</v>
       </c>
       <c r="AH17">
-        <v>0.09527622097678143</v>
+        <v>0.02550611918105913</v>
       </c>
       <c r="AI17">
-        <v>0.1156462585034014</v>
+        <v>0.04052335089950936</v>
       </c>
       <c r="AJ17">
-        <v>-0.02556345484798064</v>
+        <v>-0.01974865350089767</v>
       </c>
       <c r="AK17">
-        <v>-0.03194103194103195</v>
+        <v>-0.03225806451612903</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-0.08699999999999999</v>
-      </c>
-      <c r="AQ17">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2384,7 +2399,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hana Must Seven Special Purpose Acquisition Company (KOSDAQ:A372290)</t>
+          <t>Globon Co., Ltd. (KOSDAQ:A019660)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2392,8 +2407,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D18">
+        <v>-0.0565</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
       <c r="K18">
-        <v>0.021</v>
+        <v>-4.81</v>
+      </c>
+      <c r="L18">
+        <v>-0.3272108843537415</v>
       </c>
       <c r="M18">
         <v>-0</v>
@@ -2402,7 +2435,7 @@
         <v>-0</v>
       </c>
       <c r="O18">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P18">
         <v>-0</v>
@@ -2411,67 +2444,67 @@
         <v>-0</v>
       </c>
       <c r="R18">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
       <c r="U18">
-        <v>0.967</v>
+        <v>2.32</v>
       </c>
       <c r="V18">
-        <v>0.1395382395382395</v>
+        <v>0.08560885608856088</v>
       </c>
       <c r="W18">
-        <v>0.003235747303543914</v>
+        <v>-0.4042016806722689</v>
       </c>
       <c r="X18">
-        <v>0.07948591100059457</v>
+        <v>0.06646610012283115</v>
       </c>
       <c r="Y18">
-        <v>-0.07625016369705066</v>
+        <v>-0.4706677807951</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>0.8825118568769886</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.07711645387430567</v>
+        <v>0.0659210717159309</v>
       </c>
       <c r="AC18">
-        <v>-0.07711645387430567</v>
+        <v>-0.0659210717159309</v>
       </c>
       <c r="AD18">
-        <v>0.524</v>
+        <v>0.622</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>0.524</v>
+        <v>0.622</v>
       </c>
       <c r="AG18">
-        <v>-0.4429999999999999</v>
+        <v>-1.698</v>
       </c>
       <c r="AH18">
-        <v>0.07029782667024417</v>
+        <v>0.0224370536036361</v>
       </c>
       <c r="AI18">
-        <v>0.08890397013912453</v>
+        <v>0.06378178835110745</v>
       </c>
       <c r="AJ18">
-        <v>-0.06829042700786186</v>
+        <v>-0.06684513030470041</v>
       </c>
       <c r="AK18">
-        <v>-0.08991272579663079</v>
+        <v>-0.2284714747039828</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-0.053</v>
+        <v>-0.612</v>
       </c>
       <c r="AQ18">
         <v>-0</v>
@@ -2485,7 +2518,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Company K Partners Limited (KOSDAQ:A307930)</t>
+          <t>Hana Must Seven Special Purpose Acquisition Company (KOSDAQ:A372290)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2493,23 +2526,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
       <c r="K19">
-        <v>10</v>
-      </c>
-      <c r="L19">
-        <v>0.591715976331361</v>
+        <v>0.092</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2533,61 +2551,61 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>0.634</v>
+        <v>1.02</v>
       </c>
       <c r="V19">
-        <v>0.009392592592592593</v>
+        <v>0.06538461538461539</v>
       </c>
       <c r="W19">
-        <v>0.1915708812260536</v>
+        <v>0.01713221601489758</v>
       </c>
       <c r="X19">
-        <v>0.07893665398004032</v>
+        <v>0.06674847245452631</v>
       </c>
       <c r="Y19">
-        <v>0.1126342272460133</v>
+        <v>-0.04961625643962873</v>
       </c>
       <c r="Z19">
-        <v>0.3128413024564521</v>
+        <v>0</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.07716073304555084</v>
+        <v>0.06594741115526</v>
       </c>
       <c r="AC19">
-        <v>-0.07716073304555084</v>
+        <v>-0.06594741115526</v>
       </c>
       <c r="AD19">
-        <v>3.82</v>
+        <v>0.574</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>3.82</v>
+        <v>0.574</v>
       </c>
       <c r="AG19">
-        <v>3.186</v>
+        <v>-0.4460000000000001</v>
       </c>
       <c r="AH19">
-        <v>0.0535614133482894</v>
+        <v>0.03548905651044887</v>
       </c>
       <c r="AI19">
-        <v>0.07045370711914423</v>
+        <v>0.08977166093212385</v>
       </c>
       <c r="AJ19">
-        <v>0.04507257448433918</v>
+        <v>-0.02943117328758084</v>
       </c>
       <c r="AK19">
-        <v>0.05945582801477998</v>
+        <v>-0.08299218459248232</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-0.004</v>
+        <v>-0.136</v>
       </c>
       <c r="AQ19">
         <v>-0</v>
@@ -2601,7 +2619,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SBI Investment KOREA Co., Ltd. (KOSDAQ:A019550)</t>
+          <t>Stonebridge Ventures Inc. (KOSDAQ:A330730)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2609,9 +2627,6 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D20">
-        <v>0.06</v>
-      </c>
       <c r="G20">
         <v>0</v>
       </c>
@@ -2625,19 +2640,19 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>-1.24</v>
+        <v>1.99</v>
       </c>
       <c r="L20">
-        <v>-0.07425149700598803</v>
+        <v>0.1825688073394495</v>
       </c>
       <c r="M20">
-        <v>-0</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="N20">
-        <v>-0</v>
+        <v>0.01080924855491329</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>0.4698492462311558</v>
       </c>
       <c r="P20">
         <v>-0</v>
@@ -2646,67 +2661,73 @@
         <v>-0</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
       </c>
       <c r="U20">
-        <v>14.5</v>
+        <v>2.61</v>
       </c>
       <c r="V20">
-        <v>0.1068533529845247</v>
+        <v>0.03017341040462428</v>
       </c>
       <c r="W20">
-        <v>-0.01153488372093023</v>
+        <v>0.03138801261829653</v>
       </c>
       <c r="X20">
-        <v>0.07833877064940682</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="Y20">
-        <v>-0.08987365437033705</v>
+        <v>-0.03460990200012524</v>
       </c>
       <c r="Z20">
-        <v>0.15311267993032</v>
+        <v>0.1943998573212057</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.07721078069312629</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="AC20">
-        <v>-0.07721078069312629</v>
+        <v>-0.06599791461842178</v>
       </c>
       <c r="AD20">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>-9.629999999999999</v>
+        <v>-2.61</v>
       </c>
       <c r="AH20">
-        <v>0.03464466102297788</v>
+        <v>0</v>
       </c>
       <c r="AI20">
-        <v>0.05260883655611969</v>
+        <v>0</v>
       </c>
       <c r="AJ20">
-        <v>-0.0763861346870786</v>
+        <v>-0.03111217069972583</v>
       </c>
       <c r="AK20">
-        <v>-0.1233508389906494</v>
+        <v>-0.04104418933794621</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>-0.512</v>
+      </c>
+      <c r="AQ20">
+        <v>-0</v>
       </c>
     </row>
     <row r="21">
@@ -2717,7 +2738,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>STIC Investments, Inc. (KOSE:A026890)</t>
+          <t>LB Investment Inc. (KOSDAQ:A309960)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2725,12 +2746,6 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D21">
-        <v>0.129</v>
-      </c>
-      <c r="E21">
-        <v>-0.0608</v>
-      </c>
       <c r="G21">
         <v>0</v>
       </c>
@@ -2744,94 +2759,91 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>86.90000000000001</v>
+        <v>1.58</v>
       </c>
       <c r="L21">
-        <v>0.4595452141723956</v>
+        <v>0.1097222222222222</v>
       </c>
       <c r="M21">
-        <v>10.8728</v>
+        <v>0.047</v>
       </c>
       <c r="N21">
-        <v>0.06978690629011554</v>
+        <v>0.0005649038461538462</v>
       </c>
       <c r="O21">
-        <v>0.1251185270425777</v>
+        <v>0.02974683544303797</v>
       </c>
       <c r="P21">
-        <v>3.9728</v>
+        <v>-0</v>
       </c>
       <c r="Q21">
-        <v>0.02549935815147625</v>
+        <v>-0</v>
       </c>
       <c r="R21">
-        <v>0.04571691599539701</v>
+        <v>-0</v>
       </c>
       <c r="S21">
-        <v>6.900000000000001</v>
+        <v>0.047</v>
       </c>
       <c r="T21">
-        <v>0.6346111397248179</v>
+        <v>1</v>
       </c>
       <c r="U21">
-        <v>5.05</v>
+        <v>8.59</v>
       </c>
       <c r="V21">
-        <v>0.03241335044929396</v>
+        <v>0.1032451923076923</v>
       </c>
       <c r="W21">
-        <v>0.4906832298136646</v>
+        <v>0.02354694485842027</v>
       </c>
       <c r="X21">
-        <v>0.07735155589132341</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="Y21">
-        <v>0.4133316739223412</v>
+        <v>-0.0424509697600015</v>
       </c>
       <c r="Z21">
-        <v>0.8754629629629629</v>
+        <v>0.2356406480117821</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.07729794694283947</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="AC21">
-        <v>-0.07729794694283947</v>
+        <v>-0.06599791461842178</v>
       </c>
       <c r="AD21">
-        <v>0.265</v>
+        <v>0</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>0.265</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>-4.785</v>
+        <v>-8.59</v>
       </c>
       <c r="AH21">
-        <v>0.00169801044436613</v>
+        <v>0</v>
       </c>
       <c r="AI21">
-        <v>0.001611285075852005</v>
+        <v>0</v>
       </c>
       <c r="AJ21">
-        <v>-0.03168559414627686</v>
+        <v>-0.115132019836483</v>
       </c>
       <c r="AK21">
-        <v>-0.03001599598532134</v>
+        <v>-0.1130114458623865</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-2.14</v>
-      </c>
-      <c r="AQ21">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2842,7 +2854,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Atinum Investment Co., Ltd (KOSDAQ:A021080)</t>
+          <t>Woori Technology Investment Co., Ltd (KOSDAQ:A041190)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2851,10 +2863,7 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.713</v>
-      </c>
-      <c r="E22">
-        <v>0.802</v>
+        <v>-0.175</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -2869,19 +2878,19 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>55.5</v>
+        <v>-34.7</v>
       </c>
       <c r="L22">
-        <v>0.4450681635926223</v>
+        <v>-35.88417786970011</v>
       </c>
       <c r="M22">
-        <v>2.92</v>
+        <v>-0</v>
       </c>
       <c r="N22">
-        <v>0.02997946611909651</v>
+        <v>-0</v>
       </c>
       <c r="O22">
-        <v>0.05261261261261261</v>
+        <v>0</v>
       </c>
       <c r="P22">
         <v>-0</v>
@@ -2890,40 +2899,37 @@
         <v>-0</v>
       </c>
       <c r="R22">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>2.92</v>
-      </c>
-      <c r="T22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>30.2</v>
+        <v>27.1</v>
       </c>
       <c r="V22">
-        <v>0.3100616016427105</v>
+        <v>0.06954067231203491</v>
       </c>
       <c r="W22">
-        <v>0.6180400890868597</v>
+        <v>-0.1028148148148148</v>
       </c>
       <c r="X22">
-        <v>0.07730243933280354</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="Y22">
-        <v>0.5407376497540561</v>
+        <v>-0.1688127294332366</v>
       </c>
       <c r="Z22">
-        <v>2.250902527075812</v>
+        <v>0.002986411365040148</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.07730243933280354</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="AC22">
-        <v>-0.07730243933280354</v>
+        <v>-0.06599791461842178</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -2935,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AG22">
-        <v>-30.2</v>
+        <v>-27.1</v>
       </c>
       <c r="AH22">
         <v>0</v>
@@ -2944,19 +2950,16 @@
         <v>0</v>
       </c>
       <c r="AJ22">
-        <v>-0.4494047619047619</v>
+        <v>-0.07473800330943189</v>
       </c>
       <c r="AK22">
-        <v>-0.3370535714285715</v>
+        <v>-0.09075686537173477</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-0.384</v>
-      </c>
-      <c r="AQ22">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2967,7 +2970,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Daol Investment Co.,Ltd. (KOSDAQ:A298870)</t>
+          <t>Atinum Investment Co., Ltd (KOSDAQ:A021080)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2975,6 +2978,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D23">
+        <v>0.151</v>
+      </c>
+      <c r="E23">
+        <v>-0.183</v>
+      </c>
       <c r="G23">
         <v>0</v>
       </c>
@@ -2988,19 +2997,19 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>3.34</v>
+        <v>3.52</v>
       </c>
       <c r="L23">
-        <v>0.1546296296296296</v>
+        <v>0.0775330396475771</v>
       </c>
       <c r="M23">
-        <v>8.949999999999999</v>
+        <v>2.01</v>
       </c>
       <c r="N23">
-        <v>0.03547364248910027</v>
+        <v>0.01535523300229182</v>
       </c>
       <c r="O23">
-        <v>2.679640718562874</v>
+        <v>0.5710227272727272</v>
       </c>
       <c r="P23">
         <v>-0</v>
@@ -3012,37 +3021,37 @@
         <v>-0</v>
       </c>
       <c r="S23">
-        <v>8.949999999999999</v>
+        <v>2.01</v>
       </c>
       <c r="T23">
         <v>1</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="V23">
-        <v>0.03963535473642489</v>
+        <v>0.07792207792207791</v>
       </c>
       <c r="W23">
-        <v>0.0202179176755448</v>
+        <v>0.02938230383973289</v>
       </c>
       <c r="X23">
-        <v>0.07730243933280354</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="Y23">
-        <v>-0.05708452165725874</v>
+        <v>-0.03661561077868888</v>
       </c>
       <c r="Z23">
-        <v>0.1290399665451939</v>
+        <v>0.5066964285714286</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.07730243933280354</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="AC23">
-        <v>-0.07730243933280354</v>
+        <v>-0.06599791461842178</v>
       </c>
       <c r="AD23">
         <v>0</v>
@@ -3054,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="AG23">
-        <v>-10</v>
+        <v>-10.2</v>
       </c>
       <c r="AH23">
         <v>0</v>
@@ -3063,16 +3072,16 @@
         <v>0</v>
       </c>
       <c r="AJ23">
-        <v>-0.04127115146512587</v>
+        <v>-0.08450704225352113</v>
       </c>
       <c r="AK23">
-        <v>-0.05277044854881267</v>
+        <v>-0.08963093145869946</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-0.002</v>
+        <v>-0.556</v>
       </c>
       <c r="AQ23">
         <v>-0</v>
@@ -3086,7 +3095,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Stonebridge Ventures Inc. (KOSDAQ:A330730)</t>
+          <t>SBI Investment KOREA Co., Ltd. (KOSDAQ:A019550)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3094,6 +3103,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D24">
+        <v>0.0955</v>
+      </c>
+      <c r="E24">
+        <v>-0.189</v>
+      </c>
       <c r="G24">
         <v>0</v>
       </c>
@@ -3107,19 +3122,19 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>10.4</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0.3741007194244604</v>
+        <v>0.04830917874396135</v>
       </c>
       <c r="M24">
-        <v>2.25</v>
+        <v>-0</v>
       </c>
       <c r="N24">
-        <v>0.03488372093023256</v>
+        <v>-0</v>
       </c>
       <c r="O24">
-        <v>0.2163461538461538</v>
+        <v>-0</v>
       </c>
       <c r="P24">
         <v>-0</v>
@@ -3131,37 +3146,34 @@
         <v>-0</v>
       </c>
       <c r="S24">
-        <v>2.25</v>
-      </c>
-      <c r="T24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>7.33</v>
+        <v>15.1</v>
       </c>
       <c r="V24">
-        <v>0.1136434108527132</v>
+        <v>0.1405959031657356</v>
       </c>
       <c r="W24">
-        <v>0.2051282051282051</v>
+        <v>0.01140250855188141</v>
       </c>
       <c r="X24">
-        <v>0.07730243933280354</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="Y24">
-        <v>0.1278257657954016</v>
+        <v>-0.05459540606654036</v>
       </c>
       <c r="Z24">
-        <v>0.6414397784956161</v>
+        <v>0.2651466632509286</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.07730243933280354</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="AC24">
-        <v>-0.07730243933280354</v>
+        <v>-0.06599791461842178</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -3173,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="AG24">
-        <v>-7.33</v>
+        <v>-15.1</v>
       </c>
       <c r="AH24">
         <v>0</v>
@@ -3182,19 +3194,16 @@
         <v>0</v>
       </c>
       <c r="AJ24">
-        <v>-0.1282140983033059</v>
+        <v>-0.1635969664138678</v>
       </c>
       <c r="AK24">
-        <v>-0.1307294453361869</v>
+        <v>-0.1894604767879548</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-0.289</v>
-      </c>
-      <c r="AQ24">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3205,7 +3214,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SV Investment Corporation (KOSDAQ:A289080)</t>
+          <t>Lindeman Asia Investment Corporation (KOSDAQ:A277070)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3213,6 +3222,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D25">
+        <v>-0.0275</v>
+      </c>
+      <c r="E25">
+        <v>-0.136</v>
+      </c>
       <c r="G25">
         <v>0</v>
       </c>
@@ -3226,61 +3241,61 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>7.66</v>
+        <v>1.13</v>
       </c>
       <c r="L25">
-        <v>0.3191666666666667</v>
+        <v>0.2255489021956088</v>
       </c>
       <c r="M25">
-        <v>2.2344</v>
+        <v>0.4489</v>
       </c>
       <c r="N25">
-        <v>0.02786034912718205</v>
+        <v>0.009217659137577001</v>
       </c>
       <c r="O25">
-        <v>0.2916971279373369</v>
+        <v>0.3972566371681416</v>
       </c>
       <c r="P25">
-        <v>2.2344</v>
+        <v>0.2709</v>
       </c>
       <c r="Q25">
-        <v>0.02786034912718205</v>
+        <v>0.005562628336755647</v>
       </c>
       <c r="R25">
-        <v>0.2916971279373369</v>
+        <v>0.2397345132743363</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>0.178</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>0.3965248384940966</v>
       </c>
       <c r="U25">
-        <v>4.17</v>
+        <v>7.09</v>
       </c>
       <c r="V25">
-        <v>0.05199501246882793</v>
+        <v>0.1455852156057495</v>
       </c>
       <c r="W25">
-        <v>0.1478764478764479</v>
+        <v>0.02950391644908616</v>
       </c>
       <c r="X25">
-        <v>0.07730243933280354</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="Y25">
-        <v>0.07057400854364435</v>
+        <v>-0.03649399816933561</v>
       </c>
       <c r="Z25">
-        <v>0.4974093264248705</v>
+        <v>0.1601662404092072</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.07730243933280354</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="AC25">
-        <v>-0.07730243933280354</v>
+        <v>-0.06599791461842178</v>
       </c>
       <c r="AD25">
         <v>0</v>
@@ -3292,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="AG25">
-        <v>-4.17</v>
+        <v>-7.09</v>
       </c>
       <c r="AH25">
         <v>0</v>
@@ -3301,16 +3316,19 @@
         <v>0</v>
       </c>
       <c r="AJ25">
-        <v>-0.05484677101144285</v>
+        <v>-0.1703917327565489</v>
       </c>
       <c r="AK25">
-        <v>-0.09059309146208994</v>
+        <v>-0.2066452929175167</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>-0.026</v>
+      </c>
+      <c r="AQ25">
+        <v>-0</v>
       </c>
     </row>
     <row r="26">
@@ -3330,7 +3348,7 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.218</v>
+        <v>0.0428</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3345,10 +3363,10 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>3.88</v>
+        <v>-0.471</v>
       </c>
       <c r="L26">
-        <v>0.2621621621621621</v>
+        <v>-0.06578212290502793</v>
       </c>
       <c r="M26">
         <v>-0</v>
@@ -3357,7 +3375,7 @@
         <v>-0</v>
       </c>
       <c r="O26">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P26">
         <v>-0</v>
@@ -3366,37 +3384,37 @@
         <v>-0</v>
       </c>
       <c r="R26">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
       <c r="U26">
-        <v>4.37</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="V26">
-        <v>0.04860956618464961</v>
+        <v>0.1033462033462033</v>
       </c>
       <c r="W26">
-        <v>0.08362068965517241</v>
+        <v>-0.01121428571428571</v>
       </c>
       <c r="X26">
-        <v>0.07730243933280354</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="Y26">
-        <v>0.006318250322368879</v>
+        <v>-0.0772122003327075</v>
       </c>
       <c r="Z26">
-        <v>0.3935123637330498</v>
+        <v>0.1902737177783683</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.07730243933280354</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="AC26">
-        <v>-0.07730243933280354</v>
+        <v>-0.06599791461842178</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -3408,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="AG26">
-        <v>-4.37</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="AH26">
         <v>0</v>
@@ -3417,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="AJ26">
-        <v>-0.05109318367824155</v>
+        <v>-0.1152576431749677</v>
       </c>
       <c r="AK26">
-        <v>-0.1161307467446187</v>
+        <v>-0.1498973305954825</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-0.018</v>
+        <v>-0.029</v>
       </c>
       <c r="AQ26">
         <v>-0</v>
@@ -3440,7 +3458,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Woori Technology Investment Co., Ltd (KOSDAQ:A041190)</t>
+          <t>STIC Investments, Inc. (KOSE:A026890)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3449,10 +3467,10 @@
         </is>
       </c>
       <c r="D27">
-        <v>-0.196</v>
+        <v>-0.188</v>
       </c>
       <c r="E27">
-        <v>0.836</v>
+        <v>-0.19</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3467,58 +3485,61 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>64.3</v>
+        <v>10.8</v>
       </c>
       <c r="L27">
-        <v>65.67926455566905</v>
+        <v>0.2523364485981309</v>
       </c>
       <c r="M27">
-        <v>-0</v>
+        <v>5.4534</v>
       </c>
       <c r="N27">
-        <v>-0</v>
+        <v>0.02769629253428136</v>
       </c>
       <c r="O27">
-        <v>-0</v>
+        <v>0.5049444444444444</v>
       </c>
       <c r="P27">
-        <v>-0</v>
+        <v>5.4534</v>
       </c>
       <c r="Q27">
-        <v>-0</v>
+        <v>0.02769629253428136</v>
       </c>
       <c r="R27">
-        <v>-0</v>
+        <v>0.5049444444444444</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
       <c r="U27">
-        <v>13.7</v>
+        <v>30.7</v>
       </c>
       <c r="V27">
-        <v>0.0593073593073593</v>
+        <v>0.1559167089893347</v>
       </c>
       <c r="W27">
-        <v>0.193499849533554</v>
+        <v>0.06577344701583436</v>
       </c>
       <c r="X27">
-        <v>0.07730243933280354</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="Y27">
-        <v>0.1161974102007505</v>
+        <v>-0.0002244676025874165</v>
       </c>
       <c r="Z27">
-        <v>0.002979850246545322</v>
+        <v>0.272793906752924</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.07730243933280354</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="AC27">
-        <v>-0.07730243933280354</v>
+        <v>-0.06599791461842178</v>
       </c>
       <c r="AD27">
         <v>0</v>
@@ -3530,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="AG27">
-        <v>-13.7</v>
+        <v>-30.7</v>
       </c>
       <c r="AH27">
         <v>0</v>
@@ -3539,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AJ27">
-        <v>-0.06304647952139898</v>
+        <v>-0.1847172081829121</v>
       </c>
       <c r="AK27">
-        <v>-0.0423100679431748</v>
+        <v>-0.2048032021347565</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -3559,7 +3580,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lindeman Asia Investment Co., Ltd. (KOSDAQ:A277070)</t>
+          <t>NH Special Purpose Acquisition 19 Company (KOSE:A380440)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3567,113 +3588,95 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D28">
-        <v>0.0653</v>
-      </c>
-      <c r="E28">
-        <v>0.00219</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
       <c r="K28">
-        <v>2.4</v>
-      </c>
-      <c r="L28">
-        <v>0.2846975088967971</v>
+        <v>2.08</v>
       </c>
       <c r="M28">
-        <v>1.797</v>
+        <v>0.011</v>
       </c>
       <c r="N28">
-        <v>0.04361650485436893</v>
+        <v>0.0001341463414634146</v>
       </c>
       <c r="O28">
-        <v>0.74875</v>
+        <v>0.005288461538461538</v>
       </c>
       <c r="P28">
-        <v>0.377</v>
+        <v>-0</v>
       </c>
       <c r="Q28">
-        <v>0.009150485436893204</v>
+        <v>-0</v>
       </c>
       <c r="R28">
-        <v>0.1570833333333334</v>
+        <v>-0</v>
       </c>
       <c r="S28">
-        <v>1.42</v>
+        <v>0.011</v>
       </c>
       <c r="T28">
-        <v>0.7902058987200891</v>
+        <v>1</v>
       </c>
       <c r="U28">
-        <v>7.02</v>
+        <v>0.139</v>
       </c>
       <c r="V28">
-        <v>0.1703883495145631</v>
+        <v>0.001695121951219512</v>
       </c>
       <c r="W28">
-        <v>0.0525164113785558</v>
+        <v>0.02962962962962963</v>
       </c>
       <c r="X28">
-        <v>0.07730243933280354</v>
+        <v>0.0689332993058978</v>
       </c>
       <c r="Y28">
-        <v>-0.02478602795424774</v>
+        <v>-0.03930366967626817</v>
       </c>
       <c r="Z28">
-        <v>0.2044131910766246</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>-0.000465260278459701</v>
       </c>
       <c r="AB28">
-        <v>0.07730243933280354</v>
+        <v>0.06581889283667271</v>
       </c>
       <c r="AC28">
-        <v>-0.07730243933280354</v>
+        <v>-0.0662841531151324</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="AG28">
-        <v>-7.02</v>
+        <v>11.661</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>0.1257995735607676</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>0.133032694475761</v>
       </c>
       <c r="AJ28">
-        <v>-0.2053832650672908</v>
+        <v>0.1245021940829161</v>
       </c>
       <c r="AK28">
-        <v>-0.2244245524296675</v>
+        <v>0.1316719549237249</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="AM28">
-        <v>-0.02</v>
+        <v>-2.643</v>
+      </c>
+      <c r="AO28">
+        <v>-0.1983122362869199</v>
       </c>
       <c r="AQ28">
-        <v>-0</v>
+        <v>0.01778282255013243</v>
       </c>
     </row>
     <row r="29">
@@ -3684,7 +3687,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Samsung Special Purpose Acquisition 4 Company (KOSDAQ:A377630)</t>
+          <t>Hana Financial Twenty-four Special Purpose Acquisition Company (KOSDAQ:A430230)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3693,7 +3696,7 @@
         </is>
       </c>
       <c r="K29">
-        <v>-0.01</v>
+        <v>0.377</v>
       </c>
       <c r="M29">
         <v>-0</v>
@@ -3702,7 +3705,7 @@
         <v>-0</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P29">
         <v>-0</v>
@@ -3711,70 +3714,73 @@
         <v>-0</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S29">
         <v>0</v>
       </c>
       <c r="U29">
-        <v>0.963</v>
+        <v>0.354</v>
       </c>
       <c r="V29">
-        <v>0.06419999999999999</v>
+        <v>0.02602941176470588</v>
       </c>
       <c r="W29">
-        <v>-0.001540832049306626</v>
+        <v>0.03625</v>
       </c>
       <c r="X29">
-        <v>0.07890991617494809</v>
+        <v>0.06820274556451075</v>
       </c>
       <c r="Y29">
-        <v>-0.08045074822425471</v>
+        <v>-0.03195274556451076</v>
       </c>
       <c r="Z29">
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>-0.001813328202784925</v>
       </c>
       <c r="AB29">
-        <v>0.07731321346195724</v>
+        <v>0.06585910141113908</v>
       </c>
       <c r="AC29">
-        <v>-0.07731321346195724</v>
+        <v>-0.06767242961392402</v>
       </c>
       <c r="AD29">
-        <v>0.835</v>
+        <v>1.47</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>0.835</v>
+        <v>1.47</v>
       </c>
       <c r="AG29">
-        <v>-0.128</v>
+        <v>1.116</v>
       </c>
       <c r="AH29">
-        <v>0.05273129144300599</v>
+        <v>0.09754479097544791</v>
       </c>
       <c r="AI29">
-        <v>0.1354420113544201</v>
+        <v>0.1133384734001542</v>
       </c>
       <c r="AJ29">
-        <v>-0.008606777837547069</v>
+        <v>0.07583582495243274</v>
       </c>
       <c r="AK29">
-        <v>-0.02460592079969243</v>
+        <v>0.08845909955611922</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AM29">
-        <v>-0.064</v>
+        <v>-0.405</v>
+      </c>
+      <c r="AO29">
+        <v>-0.2608695652173912</v>
       </c>
       <c r="AQ29">
-        <v>-0</v>
+        <v>0.04444444444444445</v>
       </c>
     </row>
     <row r="30">
@@ -3785,7 +3791,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kyobo 10 Special Purpose Acquisition Company (KOSDAQ:A355150)</t>
+          <t>NH Special Purpose Acquisition 23 Company (KOSDAQ:A422040)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3794,7 +3800,7 @@
         </is>
       </c>
       <c r="K30">
-        <v>0.002</v>
+        <v>0.221</v>
       </c>
       <c r="M30">
         <v>-0</v>
@@ -3818,64 +3824,67 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>1.55</v>
+        <v>0.076</v>
       </c>
       <c r="V30">
-        <v>0.1697699890470975</v>
+        <v>0.006551724137931035</v>
       </c>
       <c r="W30">
-        <v>0.0002638522427440633</v>
+        <v>0.02378902045209903</v>
       </c>
       <c r="X30">
-        <v>0.07924442983803422</v>
+        <v>0.06798500363903492</v>
       </c>
       <c r="Y30">
-        <v>-0.07898057759529015</v>
+        <v>-0.04419598318693589</v>
       </c>
       <c r="Z30">
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>-0.003136552727994509</v>
       </c>
       <c r="AB30">
-        <v>0.07731531426247394</v>
+        <v>0.06587159327197796</v>
       </c>
       <c r="AC30">
-        <v>-0.07731531426247394</v>
+        <v>-0.06900814599997247</v>
       </c>
       <c r="AD30">
-        <v>0.614</v>
+        <v>1.13</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>0.614</v>
+        <v>1.13</v>
       </c>
       <c r="AG30">
-        <v>-0.9360000000000001</v>
+        <v>1.054</v>
       </c>
       <c r="AH30">
-        <v>0.06301313628899835</v>
+        <v>0.0887666928515318</v>
       </c>
       <c r="AI30">
-        <v>0.08958272541581558</v>
+        <v>0.1006233303650935</v>
       </c>
       <c r="AJ30">
-        <v>-0.1142299243348792</v>
+        <v>0.08329382013592539</v>
       </c>
       <c r="AK30">
-        <v>-0.1764705882352941</v>
+        <v>0.09449524834140217</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="AM30">
-        <v>-0.061</v>
+        <v>-0.324</v>
+      </c>
+      <c r="AO30">
+        <v>-1.108108108108108</v>
       </c>
       <c r="AQ30">
-        <v>-0</v>
+        <v>0.1265432098765432</v>
       </c>
     </row>
     <row r="31">
@@ -3886,7 +3895,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shinyoung HappyTomorrow No.6 Special Purpose Acquisition Company (KOSDAQ:A344050)</t>
+          <t>Kyobo 12 Special Purpose Acquisition Company (KOSDAQ:A421800)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3895,7 +3904,7 @@
         </is>
       </c>
       <c r="K31">
-        <v>-0.004</v>
+        <v>0.149</v>
       </c>
       <c r="M31">
         <v>-0</v>
@@ -3904,7 +3913,7 @@
         <v>-0</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31">
         <v>-0</v>
@@ -3913,70 +3922,73 @@
         <v>-0</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S31">
         <v>0</v>
       </c>
       <c r="U31">
-        <v>0.931</v>
+        <v>1.68</v>
       </c>
       <c r="V31">
-        <v>0.08166666666666667</v>
+        <v>0.1714285714285714</v>
       </c>
       <c r="W31">
-        <v>-0.0005563282336578581</v>
+        <v>0.01808252427184466</v>
       </c>
       <c r="X31">
-        <v>0.07982282927597062</v>
+        <v>0.06914093893529552</v>
       </c>
       <c r="Y31">
-        <v>-0.08037915750962847</v>
+        <v>-0.05105841466345086</v>
       </c>
       <c r="Z31">
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>-0.003302853976170684</v>
       </c>
       <c r="AB31">
-        <v>0.07731884108775815</v>
+        <v>0.06580792010986197</v>
       </c>
       <c r="AC31">
-        <v>-0.07731884108775815</v>
+        <v>-0.06911077408603265</v>
       </c>
       <c r="AD31">
-        <v>0.995</v>
+        <v>1.51</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>0.995</v>
+        <v>1.51</v>
       </c>
       <c r="AG31">
-        <v>0.06399999999999995</v>
+        <v>-0.1699999999999999</v>
       </c>
       <c r="AH31">
-        <v>0.08027430415490117</v>
+        <v>0.1335101679929266</v>
       </c>
       <c r="AI31">
-        <v>0.1440984793627806</v>
+        <v>0.1444976076555024</v>
       </c>
       <c r="AJ31">
-        <v>0.005582693649685969</v>
+        <v>-0.01765316718587746</v>
       </c>
       <c r="AK31">
-        <v>0.01071309005691328</v>
+        <v>-0.0193842645381984</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="AM31">
-        <v>-0.059</v>
+        <v>-0.212</v>
+      </c>
+      <c r="AO31">
+        <v>-0.627450980392157</v>
       </c>
       <c r="AQ31">
-        <v>-0</v>
+        <v>0.1509433962264151</v>
       </c>
     </row>
     <row r="32">
@@ -3987,7 +3999,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hana Financial Sixteenth Special Purpose Acquisition Company (KOSDAQ:A343510)</t>
+          <t>KB No.21 Special Purpose Acquisition Company (KOSDAQ:A424140)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3996,7 +4008,7 @@
         </is>
       </c>
       <c r="K32">
-        <v>0.005</v>
+        <v>0.215</v>
       </c>
       <c r="M32">
         <v>-0</v>
@@ -4020,64 +4032,67 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>0.89</v>
+        <v>0.171</v>
       </c>
       <c r="V32">
-        <v>0.1373456790123457</v>
+        <v>0.01425</v>
       </c>
       <c r="W32">
-        <v>0.0008012820512820513</v>
+        <v>0.0199074074074074</v>
       </c>
       <c r="X32">
-        <v>0.08028370460058659</v>
+        <v>0.06825874127107809</v>
       </c>
       <c r="Y32">
-        <v>-0.07948242254930454</v>
+        <v>-0.04835133386367069</v>
       </c>
       <c r="Z32">
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>-0.003734462356836562</v>
       </c>
       <c r="AB32">
-        <v>0.07732155962787678</v>
+        <v>0.06585592774441308</v>
       </c>
       <c r="AC32">
-        <v>-0.07732155962787678</v>
+        <v>-0.06959039010124965</v>
       </c>
       <c r="AD32">
-        <v>0.669</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>0.669</v>
+        <v>1.33</v>
       </c>
       <c r="AG32">
-        <v>-0.221</v>
+        <v>1.159</v>
       </c>
       <c r="AH32">
-        <v>0.09357952161141418</v>
+        <v>0.09977494373593399</v>
       </c>
       <c r="AI32">
-        <v>0.1151661215355483</v>
+        <v>0.1020721412125864</v>
       </c>
       <c r="AJ32">
-        <v>-0.03530915481706342</v>
+        <v>0.0880766015654685</v>
       </c>
       <c r="AK32">
-        <v>-0.04492783085993088</v>
+        <v>0.09013142546076679</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="AM32">
-        <v>-0.051</v>
+        <v>-0.315</v>
+      </c>
+      <c r="AO32">
+        <v>-0.3934426229508197</v>
       </c>
       <c r="AQ32">
-        <v>-0</v>
+        <v>0.1523809523809524</v>
       </c>
     </row>
     <row r="33">
@@ -4088,7 +4103,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shinhan 7th Special Purpose Acquisition Company (KOSDAQ:A366330)</t>
+          <t>Mirae Asset Vision Special Purpose Acquisition 1 Company (KOSDAQ:A412930)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4097,7 +4112,7 @@
         </is>
       </c>
       <c r="K33">
-        <v>-0.001</v>
+        <v>0.192</v>
       </c>
       <c r="M33">
         <v>-0</v>
@@ -4106,7 +4121,7 @@
         <v>-0</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P33">
         <v>-0</v>
@@ -4115,70 +4130,73 @@
         <v>-0</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S33">
         <v>0</v>
       </c>
       <c r="U33">
-        <v>1.18</v>
+        <v>0.741</v>
       </c>
       <c r="V33">
-        <v>0.1612021857923497</v>
+        <v>0.07194174757281553</v>
       </c>
       <c r="W33">
-        <v>-0.0001375515818431912</v>
+        <v>0.02291169451073986</v>
       </c>
       <c r="X33">
-        <v>0.08057672464491696</v>
+        <v>0.06999838458414111</v>
       </c>
       <c r="Y33">
-        <v>-0.08071427622676014</v>
+        <v>-0.04708669007340125</v>
       </c>
       <c r="Z33">
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>-0.00411372064276885</v>
       </c>
       <c r="AB33">
-        <v>0.07732324752033135</v>
+        <v>0.06576458634471299</v>
       </c>
       <c r="AC33">
-        <v>-0.07732324752033135</v>
+        <v>-0.06987830698748185</v>
       </c>
       <c r="AD33">
-        <v>0.83</v>
+        <v>2.02</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>0.83</v>
+        <v>2.02</v>
       </c>
       <c r="AG33">
-        <v>-0.35</v>
+        <v>1.279</v>
       </c>
       <c r="AH33">
-        <v>0.101840490797546</v>
+        <v>0.1639610389610389</v>
       </c>
       <c r="AI33">
-        <v>0.1218795888399413</v>
+        <v>0.1810035842293907</v>
       </c>
       <c r="AJ33">
-        <v>-0.05021520803443328</v>
+        <v>0.1104585888245962</v>
       </c>
       <c r="AK33">
-        <v>-0.06216696269982237</v>
+        <v>0.1227565025434303</v>
       </c>
       <c r="AL33">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="AM33">
-        <v>-0.049</v>
+        <v>-0.264</v>
+      </c>
+      <c r="AO33">
+        <v>-0.6842105263157895</v>
       </c>
       <c r="AQ33">
-        <v>-0</v>
+        <v>0.1477272727272727</v>
       </c>
     </row>
     <row r="34">
@@ -4189,7 +4207,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HMCIB No.4 Special Purpose Acquisition Company (KOSDAQ:A353070)</t>
+          <t>Shinyoung HappyTomorrow No.8 Special Purpose Acquisition Company (KOSDAQ:A430220)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4198,7 +4216,7 @@
         </is>
       </c>
       <c r="K34">
-        <v>0.027</v>
+        <v>0.171</v>
       </c>
       <c r="M34">
         <v>-0</v>
@@ -4222,64 +4240,67 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>1.1</v>
+        <v>1.66</v>
       </c>
       <c r="V34">
-        <v>0.1601164483260553</v>
+        <v>0.1495495495495495</v>
       </c>
       <c r="W34">
-        <v>0.003868194842406877</v>
+        <v>0.01875</v>
       </c>
       <c r="X34">
-        <v>0.08143850923493004</v>
+        <v>0.06835016669352853</v>
       </c>
       <c r="Y34">
-        <v>-0.07757031439252317</v>
+        <v>-0.04960016669352853</v>
       </c>
       <c r="Z34">
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>-0.004356832683445587</v>
       </c>
       <c r="AB34">
-        <v>0.07732803803635693</v>
+        <v>0.06585077960566255</v>
       </c>
       <c r="AC34">
-        <v>-0.07732803803635693</v>
+        <v>-0.07020761228910813</v>
       </c>
       <c r="AD34">
-        <v>0.984</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>0.984</v>
+        <v>1.28</v>
       </c>
       <c r="AG34">
-        <v>-0.1160000000000001</v>
+        <v>-0.3799999999999999</v>
       </c>
       <c r="AH34">
-        <v>0.1252864782276547</v>
+        <v>0.1033925686591276</v>
       </c>
       <c r="AI34">
-        <v>0.1456914421083802</v>
+        <v>0.1145926589077887</v>
       </c>
       <c r="AJ34">
-        <v>-0.01717500740302045</v>
+        <v>-0.03544776119402984</v>
       </c>
       <c r="AK34">
-        <v>-0.02051644853201275</v>
+        <v>-0.03995793901156675</v>
       </c>
       <c r="AL34">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="AM34">
-        <v>-0.07199999999999999</v>
+        <v>-0.253</v>
+      </c>
+      <c r="AO34">
+        <v>-0.7301587301587301</v>
       </c>
       <c r="AQ34">
-        <v>-0</v>
+        <v>0.1818181818181818</v>
       </c>
     </row>
     <row r="35">
@@ -4290,7 +4311,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IBKS No.13 Special Purpose Acquisition Company (KOSDAQ:A351340)</t>
+          <t>Kiwoom No.7 Special Purpose Acquisition Company (KOSDAQ:A433530)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4299,7 +4320,7 @@
         </is>
       </c>
       <c r="K35">
-        <v>-0.018</v>
+        <v>0.132</v>
       </c>
       <c r="M35">
         <v>-0</v>
@@ -4308,7 +4329,7 @@
         <v>-0</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P35">
         <v>-0</v>
@@ -4317,70 +4338,73 @@
         <v>-0</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S35">
         <v>0</v>
       </c>
       <c r="U35">
-        <v>1.52</v>
+        <v>0.956</v>
       </c>
       <c r="V35">
-        <v>0.1862745098039216</v>
+        <v>0.1431137724550898</v>
       </c>
       <c r="W35">
-        <v>-0.002155688622754491</v>
+        <v>0.02332155477031802</v>
       </c>
       <c r="X35">
-        <v>0.08218602079229517</v>
+        <v>0.0687187239662901</v>
       </c>
       <c r="Y35">
-        <v>-0.08434170941504966</v>
+        <v>-0.04539716919597207</v>
       </c>
       <c r="Z35">
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>-0.004825892825553174</v>
       </c>
       <c r="AB35">
-        <v>0.07733199525272538</v>
+        <v>0.06583043916427914</v>
       </c>
       <c r="AC35">
-        <v>-0.07733199525272538</v>
+        <v>-0.07065633198983232</v>
       </c>
       <c r="AD35">
-        <v>1.38</v>
+        <v>0.891</v>
       </c>
       <c r="AE35">
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>1.38</v>
+        <v>0.891</v>
       </c>
       <c r="AG35">
-        <v>-0.1400000000000001</v>
+        <v>-0.06499999999999995</v>
       </c>
       <c r="AH35">
-        <v>0.1446540880503145</v>
+        <v>0.1176859067494387</v>
       </c>
       <c r="AI35">
-        <v>0.1674757281553398</v>
+        <v>0.1265445249254367</v>
       </c>
       <c r="AJ35">
-        <v>-0.01745635910224441</v>
+        <v>-0.009826152683295532</v>
       </c>
       <c r="AK35">
-        <v>-0.02083333333333335</v>
+        <v>-0.01068200493015611</v>
       </c>
       <c r="AL35">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="AM35">
-        <v>-0.09</v>
+        <v>-0.184</v>
+      </c>
+      <c r="AO35">
+        <v>-0.6595744680851063</v>
       </c>
       <c r="AQ35">
-        <v>-0</v>
+        <v>0.1684782608695652</v>
       </c>
     </row>
     <row r="36">
@@ -4391,7 +4415,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DB Finance No.9 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A367360)</t>
+          <t>Samsung Special Purpose Acquisition 6 Company (KOSDAQ:A425290)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4400,7 +4424,7 @@
         </is>
       </c>
       <c r="K36">
-        <v>0.02</v>
+        <v>0.146</v>
       </c>
       <c r="M36">
         <v>-0</v>
@@ -4424,67 +4448,67 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="V36">
-        <v>0.1776913099870298</v>
+        <v>0.1344969199178645</v>
       </c>
       <c r="W36">
-        <v>0.002583979328165375</v>
+        <v>0.01983695652173913</v>
       </c>
       <c r="X36">
-        <v>0.08042233543827293</v>
+        <v>0.0680419468053504</v>
       </c>
       <c r="Y36">
-        <v>-0.07783835611010756</v>
+        <v>-0.04820499028361128</v>
       </c>
       <c r="Z36">
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>-0.002066070768360844</v>
+        <v>-0.005419019592247938</v>
       </c>
       <c r="AB36">
-        <v>0.07648136648865392</v>
+        <v>0.06586830303418383</v>
       </c>
       <c r="AC36">
-        <v>-0.07854743725701477</v>
+        <v>-0.07128732262643177</v>
       </c>
       <c r="AD36">
-        <v>0.833</v>
+        <v>0.976</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>0.833</v>
+        <v>0.976</v>
       </c>
       <c r="AG36">
-        <v>-0.5370000000000001</v>
+        <v>-0.3340000000000001</v>
       </c>
       <c r="AH36">
-        <v>0.09750673065667799</v>
+        <v>0.09107876073161626</v>
       </c>
       <c r="AI36">
-        <v>0.1095620149940813</v>
+        <v>0.1088556770020076</v>
       </c>
       <c r="AJ36">
-        <v>-0.07486407360936849</v>
+        <v>-0.03550924941526686</v>
       </c>
       <c r="AK36">
-        <v>-0.08615433980426764</v>
+        <v>-0.0436259143155695</v>
       </c>
       <c r="AL36">
-        <v>0.018</v>
+        <v>0.037</v>
       </c>
       <c r="AM36">
-        <v>-0.046</v>
+        <v>-0.205</v>
       </c>
       <c r="AO36">
-        <v>-1.055555555555556</v>
+        <v>-1.135135135135135</v>
       </c>
       <c r="AQ36">
-        <v>0.4130434782608696</v>
+        <v>0.2048780487804878</v>
       </c>
     </row>
     <row r="37">
@@ -4495,7 +4519,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DB Finance No.8 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A367340)</t>
+          <t>Shinhan 10th Special Purpose Acquisition Company Co., Ltd. (KOSDAQ:A418210)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4504,16 +4528,16 @@
         </is>
       </c>
       <c r="K37">
-        <v>0.054</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="M37">
-        <v>-0</v>
+        <v>0.002</v>
       </c>
       <c r="N37">
-        <v>-0</v>
+        <v>0.0003189792663476874</v>
       </c>
       <c r="O37">
-        <v>-0</v>
+        <v>0.02325581395348838</v>
       </c>
       <c r="P37">
         <v>-0</v>
@@ -4525,70 +4549,73 @@
         <v>-0</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>0.002</v>
+      </c>
+      <c r="T37">
+        <v>1</v>
       </c>
       <c r="U37">
-        <v>1.22</v>
+        <v>0.219</v>
       </c>
       <c r="V37">
-        <v>0.1265560165975104</v>
+        <v>0.03492822966507177</v>
       </c>
       <c r="W37">
-        <v>0.005831533477321815</v>
+        <v>0.01784232365145228</v>
       </c>
       <c r="X37">
-        <v>0.07915666728511206</v>
+        <v>0.06839237217334504</v>
       </c>
       <c r="Y37">
-        <v>-0.07332513380779024</v>
+        <v>-0.05055004852189276</v>
       </c>
       <c r="Z37">
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>-0.001731601731601731</v>
+        <v>-0.006065161190222395</v>
       </c>
       <c r="AB37">
-        <v>0.07731476752478186</v>
+        <v>0.06584841696093867</v>
       </c>
       <c r="AC37">
-        <v>-0.0790463692563836</v>
+        <v>-0.07191357815116106</v>
       </c>
       <c r="AD37">
-        <v>0.619</v>
+        <v>0.736</v>
       </c>
       <c r="AE37">
         <v>0</v>
       </c>
       <c r="AF37">
-        <v>0.619</v>
+        <v>0.736</v>
       </c>
       <c r="AG37">
-        <v>-0.601</v>
+        <v>0.517</v>
       </c>
       <c r="AH37">
-        <v>0.06033726484062774</v>
+        <v>0.1050528118755353</v>
       </c>
       <c r="AI37">
-        <v>0.07467728314633852</v>
+        <v>0.123989218328841</v>
       </c>
       <c r="AJ37">
-        <v>-0.06648965593539106</v>
+        <v>0.07617504051863858</v>
       </c>
       <c r="AK37">
-        <v>-0.08501909746781723</v>
+        <v>0.0904320447787301</v>
       </c>
       <c r="AL37">
-        <v>0.014</v>
+        <v>0.023</v>
       </c>
       <c r="AM37">
-        <v>-0.083</v>
+        <v>-0.144</v>
       </c>
       <c r="AO37">
-        <v>-1.285714285714286</v>
+        <v>-1.521739130434783</v>
       </c>
       <c r="AQ37">
-        <v>0.216867469879518</v>
+        <v>0.2430555555555556</v>
       </c>
     </row>
     <row r="38">
@@ -4599,7 +4626,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Samsung Must Special Purpose Acquisition 5 Company (KOSDAQ:A380320)</t>
+          <t>Sangsangin No.3 Special Purpose Acquisition Company (KOSDAQ:A415580)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4608,7 +4635,7 @@
         </is>
       </c>
       <c r="K38">
-        <v>0.033</v>
+        <v>0.106</v>
       </c>
       <c r="M38">
         <v>-0</v>
@@ -4632,67 +4659,67 @@
         <v>0</v>
       </c>
       <c r="U38">
-        <v>0.986</v>
+        <v>0.079</v>
       </c>
       <c r="V38">
-        <v>0.08285714285714285</v>
+        <v>0.009164733178654294</v>
       </c>
       <c r="W38">
-        <v>0.004471544715447155</v>
+        <v>0.01563421828908555</v>
       </c>
       <c r="X38">
-        <v>0.07855457748589556</v>
+        <v>0.06727577487601584</v>
       </c>
       <c r="Y38">
-        <v>-0.07408303277044841</v>
+        <v>-0.05164155658693029</v>
       </c>
       <c r="Z38">
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>-0.003754376005298514</v>
+        <v>-0.006478720913609457</v>
       </c>
       <c r="AB38">
-        <v>0.07731093078105428</v>
+        <v>0.06553904304813503</v>
       </c>
       <c r="AC38">
-        <v>-0.08106530678635279</v>
+        <v>-0.07201776396174449</v>
       </c>
       <c r="AD38">
-        <v>0.516</v>
+        <v>0.54</v>
       </c>
       <c r="AE38">
         <v>0</v>
       </c>
       <c r="AF38">
-        <v>0.516</v>
+        <v>0.54</v>
       </c>
       <c r="AG38">
-        <v>-0.47</v>
+        <v>0.461</v>
       </c>
       <c r="AH38">
-        <v>0.04155927835051546</v>
+        <v>0.05895196506550219</v>
       </c>
       <c r="AI38">
-        <v>0.07787503773015393</v>
+        <v>0.0685279187817259</v>
       </c>
       <c r="AJ38">
-        <v>-0.04111986001749781</v>
+        <v>0.05076533421429359</v>
       </c>
       <c r="AK38">
-        <v>-0.08333333333333331</v>
+        <v>0.0590949878220741</v>
       </c>
       <c r="AL38">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="AM38">
-        <v>-0.07000000000000001</v>
+        <v>-0.192</v>
       </c>
       <c r="AO38">
-        <v>-2.818181818181818</v>
+        <v>-4.214285714285714</v>
       </c>
       <c r="AQ38">
-        <v>0.4428571428571428</v>
+        <v>0.3072916666666667</v>
       </c>
     </row>
     <row r="39">
@@ -4712,7 +4739,7 @@
         </is>
       </c>
       <c r="K39">
-        <v>0.022</v>
+        <v>0.222</v>
       </c>
       <c r="M39">
         <v>-0</v>
@@ -4736,67 +4763,67 @@
         <v>0</v>
       </c>
       <c r="U39">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V39">
-        <v>0.1271186440677966</v>
+        <v>0.1341880341880342</v>
       </c>
       <c r="W39">
-        <v>0.001929824561403509</v>
+        <v>0.02361702127659574</v>
       </c>
       <c r="X39">
-        <v>0.07947799030103633</v>
+        <v>0.0676925539138773</v>
       </c>
       <c r="Y39">
-        <v>-0.07754816573963283</v>
+        <v>-0.04407553263728155</v>
       </c>
       <c r="Z39">
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>-0.005521638854972187</v>
+        <v>-0.006144043690977358</v>
       </c>
       <c r="AB39">
-        <v>0.07671248084029506</v>
+        <v>0.06588875856958278</v>
       </c>
       <c r="AC39">
-        <v>-0.08223411969526724</v>
+        <v>-0.07203280226056014</v>
       </c>
       <c r="AD39">
-        <v>0.889</v>
+        <v>0.972</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>0.889</v>
+        <v>0.972</v>
       </c>
       <c r="AG39">
-        <v>-0.611</v>
+        <v>-0.5980000000000001</v>
       </c>
       <c r="AH39">
-        <v>0.07006068248088895</v>
+        <v>0.07670454545454546</v>
       </c>
       <c r="AI39">
-        <v>0.08640295461172126</v>
+        <v>0.08623136976579134</v>
       </c>
       <c r="AJ39">
-        <v>-0.05460720350344088</v>
+        <v>-0.053864168618267</v>
       </c>
       <c r="AK39">
-        <v>-0.06951871657754011</v>
+        <v>-0.06163677592249022</v>
       </c>
       <c r="AL39">
-        <v>0.03</v>
+        <v>0.024</v>
       </c>
       <c r="AM39">
-        <v>-0.102</v>
+        <v>-0.264</v>
       </c>
       <c r="AO39">
-        <v>-2.466666666666667</v>
+        <v>-2.25</v>
       </c>
       <c r="AQ39">
-        <v>0.7254901960784312</v>
+        <v>0.2045454545454546</v>
       </c>
     </row>
     <row r="40">
@@ -4807,7 +4834,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Eugene Special Purpose Acquisition 7 Co., Ltd (KOSDAQ:A388800)</t>
+          <t>Samsung Must Special Purpose Acquisition 5 Company (KOSDAQ:A380320)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4816,7 +4843,7 @@
         </is>
       </c>
       <c r="K40">
-        <v>0.002</v>
+        <v>0.106</v>
       </c>
       <c r="M40">
         <v>-0</v>
@@ -4840,67 +4867,67 @@
         <v>0</v>
       </c>
       <c r="U40">
-        <v>0.001</v>
+        <v>1.02</v>
       </c>
       <c r="V40">
-        <v>0.0001237623762376238</v>
+        <v>0.1343873517786561</v>
       </c>
       <c r="W40">
-        <v>0.0002645502645502646</v>
+        <v>0.01734860883797054</v>
       </c>
       <c r="X40">
-        <v>0.07947177541031082</v>
+        <v>0.06750562510270386</v>
       </c>
       <c r="Y40">
-        <v>-0.07920722514576056</v>
+        <v>-0.05015701626473332</v>
       </c>
       <c r="Z40">
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>-0.007619738751814223</v>
+        <v>-0.006939071566731142</v>
       </c>
       <c r="AB40">
-        <v>0.07671404841133377</v>
+        <v>0.06576219816224355</v>
       </c>
       <c r="AC40">
-        <v>-0.08433378716314799</v>
+        <v>-0.07270126972897469</v>
       </c>
       <c r="AD40">
-        <v>0.607</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AE40">
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>0.607</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AG40">
-        <v>0.606</v>
+        <v>-0.459</v>
       </c>
       <c r="AH40">
-        <v>0.06987452515252676</v>
+        <v>0.0688259109311741</v>
       </c>
       <c r="AI40">
-        <v>0.08878162936960654</v>
+        <v>0.07812282411920346</v>
       </c>
       <c r="AJ40">
-        <v>0.06976744186046512</v>
+        <v>-0.06436684896928901</v>
       </c>
       <c r="AK40">
-        <v>0.08864833235810415</v>
+        <v>-0.07450089271222203</v>
       </c>
       <c r="AL40">
-        <v>0.027</v>
+        <v>0.01</v>
       </c>
       <c r="AM40">
-        <v>-0.064</v>
+        <v>-0.152</v>
       </c>
       <c r="AO40">
-        <v>-2.333333333333333</v>
+        <v>-4.1</v>
       </c>
       <c r="AQ40">
-        <v>0.984375</v>
+        <v>0.2697368421052632</v>
       </c>
     </row>
     <row r="41">
@@ -4911,7 +4938,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Eugene Special Purpose Acquisitions 6 Company (KOSDAQ:A373340)</t>
+          <t>HI Special Purpose Acquisition Company VI (KOSDAQ:A377400)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4920,7 +4947,7 @@
         </is>
       </c>
       <c r="K41">
-        <v>0.007</v>
+        <v>0.11</v>
       </c>
       <c r="M41">
         <v>-0</v>
@@ -4944,67 +4971,67 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>0.004</v>
+        <v>1.28</v>
       </c>
       <c r="V41">
-        <v>0.0007782101167315176</v>
+        <v>0.1630573248407644</v>
       </c>
       <c r="W41">
-        <v>0.001431492842535787</v>
+        <v>0.01639344262295082</v>
       </c>
       <c r="X41">
-        <v>0.0814598038911121</v>
+        <v>0.06748687051743665</v>
       </c>
       <c r="Y41">
-        <v>-0.08002831104857631</v>
+        <v>-0.05109342789448583</v>
       </c>
       <c r="Z41">
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>-0.004595836712625034</v>
+        <v>-0.007288519064032676</v>
       </c>
       <c r="AB41">
-        <v>0.08040519406171513</v>
+        <v>0.06590110588736074</v>
       </c>
       <c r="AC41">
-        <v>-0.08500103077434017</v>
+        <v>-0.07318962495139342</v>
       </c>
       <c r="AD41">
-        <v>0.74</v>
+        <v>0.573</v>
       </c>
       <c r="AE41">
         <v>0</v>
       </c>
       <c r="AF41">
-        <v>0.74</v>
+        <v>0.573</v>
       </c>
       <c r="AG41">
-        <v>0.736</v>
+        <v>-0.7070000000000001</v>
       </c>
       <c r="AH41">
-        <v>0.1258503401360544</v>
+        <v>0.06802801852071708</v>
       </c>
       <c r="AI41">
-        <v>0.1551362683438155</v>
+        <v>0.07305877852862425</v>
       </c>
       <c r="AJ41">
-        <v>0.1252552756977536</v>
+        <v>-0.09897802043959122</v>
       </c>
       <c r="AK41">
-        <v>0.1544271926143516</v>
+        <v>-0.1077251257047082</v>
       </c>
       <c r="AL41">
-        <v>0.024</v>
+        <v>0.021</v>
       </c>
       <c r="AM41">
-        <v>-0.042</v>
+        <v>-0.06799999999999999</v>
       </c>
       <c r="AO41">
-        <v>-1.416666666666667</v>
+        <v>-2.285714285714286</v>
       </c>
       <c r="AQ41">
-        <v>0.8095238095238095</v>
+        <v>0.7058823529411766</v>
       </c>
     </row>
     <row r="42">
@@ -5015,7 +5042,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Daishin Balance No.11 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A397500)</t>
+          <t>Hana Financial Twenty-Two Special Purpose Acquisition Company (KOSDAQ:A418170)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5024,7 +5051,7 @@
         </is>
       </c>
       <c r="K42">
-        <v>-0.047</v>
+        <v>0.12</v>
       </c>
       <c r="M42">
         <v>-0</v>
@@ -5033,7 +5060,7 @@
         <v>-0</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P42">
         <v>-0</v>
@@ -5042,58 +5069,73 @@
         <v>-0</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S42">
         <v>0</v>
       </c>
       <c r="U42">
-        <v>1.45</v>
+        <v>0.237</v>
       </c>
       <c r="V42">
-        <v>0.1178861788617886</v>
+        <v>0.02415902140672783</v>
+      </c>
+      <c r="W42">
+        <v>0.01572739187418086</v>
       </c>
       <c r="X42">
-        <v>0.0790021811667639</v>
+        <v>0.06772169682168415</v>
+      </c>
+      <c r="Y42">
+        <v>-0.05199430494750329</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>-0.009708858711211245</v>
       </c>
       <c r="AB42">
-        <v>0.07731379749191357</v>
+        <v>0.06588702767102833</v>
+      </c>
+      <c r="AC42">
+        <v>-0.07559588638223957</v>
       </c>
       <c r="AD42">
-        <v>0.724</v>
+        <v>0.829</v>
       </c>
       <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42">
-        <v>0.724</v>
+        <v>0.829</v>
       </c>
       <c r="AG42">
-        <v>-0.726</v>
+        <v>0.592</v>
       </c>
       <c r="AH42">
-        <v>0.05558968058968058</v>
+        <v>0.07792085722342325</v>
       </c>
       <c r="AI42">
-        <v>0.06859958309645632</v>
+        <v>0.09120915392232368</v>
       </c>
       <c r="AJ42">
-        <v>-0.06272680145152928</v>
+        <v>0.05691213228225341</v>
       </c>
       <c r="AK42">
-        <v>-0.07974516695957821</v>
+        <v>0.06687754179846361</v>
       </c>
       <c r="AL42">
-        <v>0.037</v>
+        <v>0.023</v>
       </c>
       <c r="AM42">
-        <v>0.001999999999999995</v>
+        <v>-0.216</v>
       </c>
       <c r="AO42">
-        <v>-1.243243243243243</v>
+        <v>-3.391304347826087</v>
       </c>
       <c r="AQ42">
-        <v>-23.00000000000006</v>
+        <v>0.3611111111111111</v>
       </c>
     </row>
     <row r="43">
@@ -5104,7 +5146,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mirae Asset Vision Special Purpose Acquisition 1 Company (KOSDAQ:A412930)</t>
+          <t>IBKS No.19 Special Purpose Acquisition Company (KOSDAQ:A426550)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5113,7 +5155,7 @@
         </is>
       </c>
       <c r="K43">
-        <v>-0.07000000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="M43">
         <v>-0</v>
@@ -5122,7 +5164,7 @@
         <v>-0</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P43">
         <v>-0</v>
@@ -5131,58 +5173,73 @@
         <v>-0</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S43">
         <v>0</v>
       </c>
       <c r="U43">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="V43">
-        <v>0.2142857142857143</v>
+        <v>0.1482142857142857</v>
+      </c>
+      <c r="W43">
+        <v>0.001724137931034483</v>
       </c>
       <c r="X43">
-        <v>0.08264784841522496</v>
+        <v>0.06809239688256363</v>
+      </c>
+      <c r="Y43">
+        <v>-0.06636825895152915</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>-0.01025502485411714</v>
       </c>
       <c r="AB43">
-        <v>0.07733435370473951</v>
+        <v>0.06586540189216587</v>
+      </c>
+      <c r="AC43">
+        <v>-0.07612042674628301</v>
       </c>
       <c r="AD43">
-        <v>1.84</v>
+        <v>1.15</v>
       </c>
       <c r="AE43">
         <v>0</v>
       </c>
       <c r="AF43">
-        <v>1.84</v>
+        <v>1.15</v>
       </c>
       <c r="AG43">
-        <v>-0.2899999999999998</v>
+        <v>-0.51</v>
       </c>
       <c r="AH43">
-        <v>0.1561969439728353</v>
+        <v>0.09311740890688258</v>
       </c>
       <c r="AI43">
-        <v>0.1800391389432485</v>
+        <v>0.1295045045045045</v>
       </c>
       <c r="AJ43">
-        <v>-0.03005181347150257</v>
+        <v>-0.04770813844714687</v>
       </c>
       <c r="AK43">
-        <v>-0.03584672435105065</v>
+        <v>-0.0706371191135734</v>
       </c>
       <c r="AL43">
-        <v>0.025</v>
+        <v>0.151</v>
       </c>
       <c r="AM43">
-        <v>0.024</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="AO43">
-        <v>-2.6</v>
+        <v>-0.4834437086092715</v>
       </c>
       <c r="AQ43">
-        <v>-2.708333333333333</v>
+        <v>0.8488372093023256</v>
       </c>
     </row>
     <row r="44">
@@ -5193,7 +5250,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sangsangin No.3 Special Purpose Acquisition Company (KOSDAQ:A415580)</t>
+          <t>Hana Financial Twenty-three Special Purpose Acquisition Company (KOSDAQ:A427950)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5202,7 +5259,7 @@
         </is>
       </c>
       <c r="K44">
-        <v>-0.028</v>
+        <v>0.164</v>
       </c>
       <c r="M44">
         <v>-0</v>
@@ -5211,7 +5268,7 @@
         <v>-0</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P44">
         <v>-0</v>
@@ -5220,58 +5277,73 @@
         <v>-0</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S44">
         <v>0</v>
       </c>
       <c r="U44">
-        <v>0.016</v>
+        <v>0.235</v>
       </c>
       <c r="V44">
-        <v>0.001927710843373494</v>
+        <v>0.01926229508196721</v>
+      </c>
+      <c r="W44">
+        <v>0.02526964560862866</v>
       </c>
       <c r="X44">
-        <v>0.07902113255844254</v>
+        <v>0.06798759812636782</v>
+      </c>
+      <c r="Y44">
+        <v>-0.04271795251773916</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>-0.01442307692307692</v>
       </c>
       <c r="AB44">
-        <v>0.07731391701663035</v>
+        <v>0.06587144299576894</v>
+      </c>
+      <c r="AC44">
+        <v>-0.08029451991884587</v>
       </c>
       <c r="AD44">
-        <v>0.494</v>
+        <v>1.19</v>
       </c>
       <c r="AE44">
         <v>0</v>
       </c>
       <c r="AF44">
-        <v>0.494</v>
+        <v>1.19</v>
       </c>
       <c r="AG44">
-        <v>0.478</v>
+        <v>0.955</v>
       </c>
       <c r="AH44">
-        <v>0.05617466454400728</v>
+        <v>0.08887229275578791</v>
       </c>
       <c r="AI44">
-        <v>0.06791311520483916</v>
+        <v>0.1438935912938331</v>
       </c>
       <c r="AJ44">
-        <v>0.05445431761221235</v>
+        <v>0.07259597111364501</v>
       </c>
       <c r="AK44">
-        <v>0.06585836318545053</v>
+        <v>0.118855009334163</v>
       </c>
       <c r="AL44">
-        <v>0.004</v>
+        <v>0.054</v>
       </c>
       <c r="AM44">
-        <v>0.004</v>
+        <v>-0.251</v>
       </c>
       <c r="AO44">
-        <v>-7.75</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AQ44">
-        <v>-7.75</v>
+        <v>0.3585657370517928</v>
       </c>
     </row>
     <row r="45">
@@ -5282,7 +5354,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Shinhan 9th Special Purpose Acquisition Company Co., Ltd. (KOSDAQ:A405640)</t>
+          <t>KB No.22 Special Purpose Acquisition Company (KOSDAQ:A436530)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5291,7 +5363,7 @@
         </is>
       </c>
       <c r="K45">
-        <v>-0.046</v>
+        <v>0.139</v>
       </c>
       <c r="M45">
         <v>-0</v>
@@ -5300,7 +5372,7 @@
         <v>-0</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P45">
         <v>-0</v>
@@ -5309,58 +5381,73 @@
         <v>-0</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S45">
         <v>0</v>
       </c>
       <c r="U45">
+        <v>1.39</v>
+      </c>
+      <c r="V45">
+        <v>0.1177966101694915</v>
+      </c>
+      <c r="W45">
+        <v>0.01941340782122905</v>
+      </c>
+      <c r="X45">
+        <v>0.06815876588577521</v>
+      </c>
+      <c r="Y45">
+        <v>-0.04874535806454616</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>-0.0157514450867052</v>
+      </c>
+      <c r="AB45">
+        <v>0.06586160509241308</v>
+      </c>
+      <c r="AC45">
+        <v>-0.08161305017911828</v>
+      </c>
+      <c r="AD45">
         <v>1.25</v>
       </c>
-      <c r="V45">
-        <v>0.1717032967032967</v>
-      </c>
-      <c r="X45">
-        <v>0.08094377579992376</v>
-      </c>
-      <c r="AB45">
-        <v>0.07732531893855908</v>
-      </c>
-      <c r="AD45">
-        <v>0.918</v>
-      </c>
       <c r="AE45">
         <v>0</v>
       </c>
       <c r="AF45">
-        <v>0.918</v>
+        <v>1.25</v>
       </c>
       <c r="AG45">
-        <v>-0.332</v>
+        <v>-0.1399999999999999</v>
       </c>
       <c r="AH45">
-        <v>0.1119785313491095</v>
+        <v>0.09578544061302681</v>
       </c>
       <c r="AI45">
-        <v>0.1342497806376133</v>
+        <v>0.1384274640088593</v>
       </c>
       <c r="AJ45">
-        <v>-0.04778353483016694</v>
+        <v>-0.01200686106346483</v>
       </c>
       <c r="AK45">
-        <v>-0.05941302791696491</v>
+        <v>-0.01832460732984292</v>
       </c>
       <c r="AL45">
-        <v>0.02</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AM45">
-        <v>0.019</v>
+        <v>-0.24</v>
       </c>
       <c r="AO45">
-        <v>-2</v>
+        <v>-1.535211267605634</v>
       </c>
       <c r="AQ45">
-        <v>-2.105263157894737</v>
+        <v>0.4541666666666667</v>
       </c>
     </row>
     <row r="46">
@@ -5371,7 +5458,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hana Financial Twenty Special Purpose Acquisition Company (KOSDAQ:A400560)</t>
+          <t>Mirae Asset Dream Special Purpose Acquisition 1 Company (KOSDAQ:A442900)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5380,7 +5467,7 @@
         </is>
       </c>
       <c r="K46">
-        <v>-0.012</v>
+        <v>-0.255</v>
       </c>
       <c r="M46">
         <v>-0</v>
@@ -5404,52 +5491,2455 @@
         <v>0</v>
       </c>
       <c r="U46">
-        <v>0.5590000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="V46">
-        <v>0.1077071290944123</v>
+        <v>0.05824372759856631</v>
       </c>
       <c r="X46">
-        <v>0.08077989953265935</v>
+        <v>0.06859341453496473</v>
       </c>
       <c r="AB46">
-        <v>0.07732439992603866</v>
+        <v>0.0658372817518738</v>
       </c>
       <c r="AD46">
-        <v>0.625</v>
+        <v>7.1</v>
       </c>
       <c r="AE46">
         <v>0</v>
       </c>
       <c r="AF46">
-        <v>0.625</v>
+        <v>7.1</v>
       </c>
       <c r="AG46">
-        <v>0.06599999999999995</v>
+        <v>3.85</v>
       </c>
       <c r="AH46">
-        <v>0.1074806534823732</v>
+        <v>0.1128775834658188</v>
       </c>
       <c r="AI46">
-        <v>0.1311647429171039</v>
+        <v>0.1123417721518987</v>
       </c>
       <c r="AJ46">
-        <v>0.01255707762557077</v>
+        <v>0.06454316848281642</v>
       </c>
       <c r="AK46">
-        <v>0.01569186875891582</v>
+        <v>0.06422018348623852</v>
       </c>
       <c r="AL46">
-        <v>0.012</v>
+        <v>0.287</v>
       </c>
       <c r="AM46">
-        <v>0.007</v>
+        <v>0.279</v>
       </c>
       <c r="AO46">
-        <v>-0.7499999999999999</v>
+        <v>-0.1498257839721254</v>
       </c>
       <c r="AQ46">
-        <v>-1.285714285714286</v>
+        <v>-0.1541218637992832</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Samsung Special Purpose Acquisition 8 Company (KOSDAQ:A448740)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K47">
+        <v>-0.095</v>
+      </c>
+      <c r="M47">
+        <v>-0</v>
+      </c>
+      <c r="N47">
+        <v>-0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>-0</v>
+      </c>
+      <c r="Q47">
+        <v>-0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>5.44</v>
+      </c>
+      <c r="V47">
+        <v>0.158600583090379</v>
+      </c>
+      <c r="X47">
+        <v>0.06762146360329696</v>
+      </c>
+      <c r="AB47">
+        <v>0.06589300008796865</v>
+      </c>
+      <c r="AD47">
+        <v>2.73</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>2.73</v>
+      </c>
+      <c r="AG47">
+        <v>-2.71</v>
+      </c>
+      <c r="AH47">
+        <v>0.07372400756143668</v>
+      </c>
+      <c r="AI47">
+        <v>0.07683647621728118</v>
+      </c>
+      <c r="AJ47">
+        <v>-0.08578664134219692</v>
+      </c>
+      <c r="AK47">
+        <v>-0.09006314390162848</v>
+      </c>
+      <c r="AL47">
+        <v>0.1</v>
+      </c>
+      <c r="AM47">
+        <v>0.098</v>
+      </c>
+      <c r="AO47">
+        <v>-0.23</v>
+      </c>
+      <c r="AQ47">
+        <v>-0.2346938775510204</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hana Financial Twenty-five Special Purpose Acquisition Company (KOSDAQ:A435620)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K48">
+        <v>0.324</v>
+      </c>
+      <c r="M48">
+        <v>-0</v>
+      </c>
+      <c r="N48">
+        <v>-0</v>
+      </c>
+      <c r="O48">
+        <v>-0</v>
+      </c>
+      <c r="P48">
+        <v>-0</v>
+      </c>
+      <c r="Q48">
+        <v>-0</v>
+      </c>
+      <c r="R48">
+        <v>-0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0.451</v>
+      </c>
+      <c r="V48">
+        <v>0.01445512820512821</v>
+      </c>
+      <c r="X48">
+        <v>0.06837119418728888</v>
+      </c>
+      <c r="AB48">
+        <v>0.06584960140082038</v>
+      </c>
+      <c r="AD48">
+        <v>3.63</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>3.63</v>
+      </c>
+      <c r="AG48">
+        <v>3.179</v>
+      </c>
+      <c r="AH48">
+        <v>0.1042204995693368</v>
+      </c>
+      <c r="AI48">
+        <v>0.1018804378332865</v>
+      </c>
+      <c r="AJ48">
+        <v>0.09246923994298846</v>
+      </c>
+      <c r="AK48">
+        <v>0.09036641177975496</v>
+      </c>
+      <c r="AL48">
+        <v>0.151</v>
+      </c>
+      <c r="AM48">
+        <v>-0.4349999999999999</v>
+      </c>
+      <c r="AO48">
+        <v>-0.1655629139072848</v>
+      </c>
+      <c r="AQ48">
+        <v>0.05747126436781611</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Samsung Special Purpose Acquisition 7 Company (KOSDAQ:A439250)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K49">
+        <v>0.197</v>
+      </c>
+      <c r="M49">
+        <v>-0</v>
+      </c>
+      <c r="N49">
+        <v>-0</v>
+      </c>
+      <c r="O49">
+        <v>-0</v>
+      </c>
+      <c r="P49">
+        <v>-0</v>
+      </c>
+      <c r="Q49">
+        <v>-0</v>
+      </c>
+      <c r="R49">
+        <v>-0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>4.05</v>
+      </c>
+      <c r="V49">
+        <v>0.1534090909090909</v>
+      </c>
+      <c r="X49">
+        <v>0.06769778428207315</v>
+      </c>
+      <c r="AB49">
+        <v>0.06588844758368866</v>
+      </c>
+      <c r="AD49">
+        <v>2.2</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>2.2</v>
+      </c>
+      <c r="AG49">
+        <v>-1.85</v>
+      </c>
+      <c r="AH49">
+        <v>0.07692307692307694</v>
+      </c>
+      <c r="AI49">
+        <v>0.08178438661710039</v>
+      </c>
+      <c r="AJ49">
+        <v>-0.07535641547861506</v>
+      </c>
+      <c r="AK49">
+        <v>-0.08096280087527351</v>
+      </c>
+      <c r="AL49">
+        <v>0.089</v>
+      </c>
+      <c r="AM49">
+        <v>-0.3100000000000001</v>
+      </c>
+      <c r="AO49">
+        <v>-0.550561797752809</v>
+      </c>
+      <c r="AQ49">
+        <v>0.1580645161290322</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Yuanta 13 SPECIAL PURPOSE ACQUISITION COMPANY (KOSDAQ:A449020)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K50">
+        <v>-0.039</v>
+      </c>
+      <c r="M50">
+        <v>-0</v>
+      </c>
+      <c r="N50">
+        <v>-0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>-0</v>
+      </c>
+      <c r="Q50">
+        <v>-0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0.131</v>
+      </c>
+      <c r="V50">
+        <v>0.008733333333333334</v>
+      </c>
+      <c r="X50">
+        <v>0.06738500826396129</v>
+      </c>
+      <c r="AB50">
+        <v>0.06590730707281869</v>
+      </c>
+      <c r="AD50">
+        <v>1.02</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>1.02</v>
+      </c>
+      <c r="AG50">
+        <v>0.889</v>
+      </c>
+      <c r="AH50">
+        <v>0.06367041198501873</v>
+      </c>
+      <c r="AI50">
+        <v>0.06882591093117409</v>
+      </c>
+      <c r="AJ50">
+        <v>0.05595065768770848</v>
+      </c>
+      <c r="AK50">
+        <v>0.06052147865749881</v>
+      </c>
+      <c r="AL50">
+        <v>0.047</v>
+      </c>
+      <c r="AM50">
+        <v>-0.001000000000000001</v>
+      </c>
+      <c r="AO50">
+        <v>-1.063829787234043</v>
+      </c>
+      <c r="AQ50">
+        <v>49.99999999999996</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NH Special Purpose Acquistion 26 Company (KOSDAQ:A439410)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K51">
+        <v>0.083</v>
+      </c>
+      <c r="M51">
+        <v>-0</v>
+      </c>
+      <c r="N51">
+        <v>-0</v>
+      </c>
+      <c r="O51">
+        <v>-0</v>
+      </c>
+      <c r="P51">
+        <v>-0</v>
+      </c>
+      <c r="Q51">
+        <v>-0</v>
+      </c>
+      <c r="R51">
+        <v>-0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0.126</v>
+      </c>
+      <c r="V51">
+        <v>0.009197080291970803</v>
+      </c>
+      <c r="X51">
+        <v>0.06756129839667048</v>
+      </c>
+      <c r="AB51">
+        <v>0.06589661122695688</v>
+      </c>
+      <c r="AD51">
+        <v>1.05</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>1.05</v>
+      </c>
+      <c r="AG51">
+        <v>0.924</v>
+      </c>
+      <c r="AH51">
+        <v>0.0711864406779661</v>
+      </c>
+      <c r="AI51">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="AJ51">
+        <v>0.06318380743982495</v>
+      </c>
+      <c r="AK51">
+        <v>0.06832298136645963</v>
+      </c>
+      <c r="AL51">
+        <v>0.048</v>
+      </c>
+      <c r="AM51">
+        <v>-0.127</v>
+      </c>
+      <c r="AO51">
+        <v>-0.7291666666666667</v>
+      </c>
+      <c r="AQ51">
+        <v>0.2755905511811024</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NH Special Purpose Acquisition 27 Company (KOSDAQ:A440820)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K52">
+        <v>0.042</v>
+      </c>
+      <c r="M52">
+        <v>-0</v>
+      </c>
+      <c r="N52">
+        <v>-0</v>
+      </c>
+      <c r="O52">
+        <v>-0</v>
+      </c>
+      <c r="P52">
+        <v>-0</v>
+      </c>
+      <c r="Q52">
+        <v>-0</v>
+      </c>
+      <c r="R52">
+        <v>-0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0.076</v>
+      </c>
+      <c r="V52">
+        <v>0.006178861788617885</v>
+      </c>
+      <c r="X52">
+        <v>0.06670771385358547</v>
+      </c>
+      <c r="AB52">
+        <v>0.06595006149293033</v>
+      </c>
+      <c r="AD52">
+        <v>0.428</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0.428</v>
+      </c>
+      <c r="AG52">
+        <v>0.352</v>
+      </c>
+      <c r="AH52">
+        <v>0.03362664990571967</v>
+      </c>
+      <c r="AI52">
+        <v>0.03778248587570621</v>
+      </c>
+      <c r="AJ52">
+        <v>0.02782168827062914</v>
+      </c>
+      <c r="AK52">
+        <v>0.03128332740846072</v>
+      </c>
+      <c r="AL52">
+        <v>0.021</v>
+      </c>
+      <c r="AM52">
+        <v>-0.08699999999999999</v>
+      </c>
+      <c r="AO52">
+        <v>-1.904761904761905</v>
+      </c>
+      <c r="AQ52">
+        <v>0.4597701149425288</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Daishin Balance No.14 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A442310)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K53">
+        <v>-0.01</v>
+      </c>
+      <c r="M53">
+        <v>-0</v>
+      </c>
+      <c r="N53">
+        <v>-0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>-0</v>
+      </c>
+      <c r="Q53">
+        <v>-0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>1.41</v>
+      </c>
+      <c r="V53">
+        <v>0.127027027027027</v>
+      </c>
+      <c r="X53">
+        <v>0.06698292017487273</v>
+      </c>
+      <c r="AB53">
+        <v>0.06593236234117697</v>
+      </c>
+      <c r="AD53">
+        <v>0.536</v>
+      </c>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>0.536</v>
+      </c>
+      <c r="AG53">
+        <v>-0.8739999999999999</v>
+      </c>
+      <c r="AH53">
+        <v>0.04606393949810932</v>
+      </c>
+      <c r="AI53">
+        <v>0.05466041199265757</v>
+      </c>
+      <c r="AJ53">
+        <v>-0.08546841384705652</v>
+      </c>
+      <c r="AK53">
+        <v>-0.1040971891376846</v>
+      </c>
+      <c r="AL53">
+        <v>0.036</v>
+      </c>
+      <c r="AM53">
+        <v>-0.057</v>
+      </c>
+      <c r="AO53">
+        <v>-1.722222222222222</v>
+      </c>
+      <c r="AQ53">
+        <v>1.087719298245614</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Korea No.11 Special Purpose Acquisition Co., Ltd. (KOSDAQ:A436610)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K54">
+        <v>0.064</v>
+      </c>
+      <c r="M54">
+        <v>-0</v>
+      </c>
+      <c r="N54">
+        <v>-0</v>
+      </c>
+      <c r="O54">
+        <v>-0</v>
+      </c>
+      <c r="P54">
+        <v>-0</v>
+      </c>
+      <c r="Q54">
+        <v>-0</v>
+      </c>
+      <c r="R54">
+        <v>-0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0.048</v>
+      </c>
+      <c r="V54">
+        <v>0.004923076923076923</v>
+      </c>
+      <c r="X54">
+        <v>0.06729295378371433</v>
+      </c>
+      <c r="AB54">
+        <v>0.06591296127398186</v>
+      </c>
+      <c r="AD54">
+        <v>0.619</v>
+      </c>
+      <c r="AE54">
+        <v>0</v>
+      </c>
+      <c r="AF54">
+        <v>0.619</v>
+      </c>
+      <c r="AG54">
+        <v>0.571</v>
+      </c>
+      <c r="AH54">
+        <v>0.05969717426945704</v>
+      </c>
+      <c r="AI54">
+        <v>0.0687090687090687</v>
+      </c>
+      <c r="AJ54">
+        <v>0.05532409650227691</v>
+      </c>
+      <c r="AK54">
+        <v>0.0637205669010155</v>
+      </c>
+      <c r="AL54">
+        <v>0.024</v>
+      </c>
+      <c r="AM54">
+        <v>-0.111</v>
+      </c>
+      <c r="AO54">
+        <v>-1.25</v>
+      </c>
+      <c r="AQ54">
+        <v>0.2702702702702702</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Hana 26 Special Purpose Acquisition Company (KOSDAQ:A446750)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K55">
+        <v>-0.053</v>
+      </c>
+      <c r="M55">
+        <v>-0</v>
+      </c>
+      <c r="N55">
+        <v>-0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>-0</v>
+      </c>
+      <c r="Q55">
+        <v>-0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>0.349</v>
+      </c>
+      <c r="V55">
+        <v>0.03590534979423868</v>
+      </c>
+      <c r="X55">
+        <v>0.06845328191036264</v>
+      </c>
+      <c r="AB55">
+        <v>0.06584502264429037</v>
+      </c>
+      <c r="AD55">
+        <v>1.17</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>1.17</v>
+      </c>
+      <c r="AG55">
+        <v>0.821</v>
+      </c>
+      <c r="AH55">
+        <v>0.1074380165289256</v>
+      </c>
+      <c r="AI55">
+        <v>0.1180625630676085</v>
+      </c>
+      <c r="AJ55">
+        <v>0.07788634854378142</v>
+      </c>
+      <c r="AK55">
+        <v>0.08586967890388034</v>
+      </c>
+      <c r="AL55">
+        <v>0.059</v>
+      </c>
+      <c r="AM55">
+        <v>0.021</v>
+      </c>
+      <c r="AO55">
+        <v>-0.7796610169491526</v>
+      </c>
+      <c r="AQ55">
+        <v>-2.190476190476191</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Hanwha Plus No3 Special Purpose Acquisition Company (KOSDAQ:A430460)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K56">
+        <v>0.193</v>
+      </c>
+      <c r="M56">
+        <v>-0</v>
+      </c>
+      <c r="N56">
+        <v>-0</v>
+      </c>
+      <c r="O56">
+        <v>-0</v>
+      </c>
+      <c r="P56">
+        <v>-0</v>
+      </c>
+      <c r="Q56">
+        <v>-0</v>
+      </c>
+      <c r="R56">
+        <v>-0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>1.34</v>
+      </c>
+      <c r="V56">
+        <v>0.1400208986415883</v>
+      </c>
+      <c r="X56">
+        <v>0.06748356873198291</v>
+      </c>
+      <c r="AB56">
+        <v>0.0659013059886646</v>
+      </c>
+      <c r="AD56">
+        <v>0.697</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>0.697</v>
+      </c>
+      <c r="AG56">
+        <v>-0.6430000000000001</v>
+      </c>
+      <c r="AH56">
+        <v>0.06788740625304374</v>
+      </c>
+      <c r="AI56">
+        <v>0.07772945243671239</v>
+      </c>
+      <c r="AJ56">
+        <v>-0.07202867704716032</v>
+      </c>
+      <c r="AK56">
+        <v>-0.08430575586731351</v>
+      </c>
+      <c r="AL56">
+        <v>0.032</v>
+      </c>
+      <c r="AM56">
+        <v>-0.266</v>
+      </c>
+      <c r="AO56">
+        <v>-1.0625</v>
+      </c>
+      <c r="AQ56">
+        <v>0.1278195488721804</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Kiwoom No.8Special Purpose Acquisition Company (KOSDAQ:A446840)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K57">
+        <v>-0.051</v>
+      </c>
+      <c r="M57">
+        <v>-0</v>
+      </c>
+      <c r="N57">
+        <v>-0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>-0</v>
+      </c>
+      <c r="Q57">
+        <v>-0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>1.34</v>
+      </c>
+      <c r="V57">
+        <v>0.1416490486257928</v>
+      </c>
+      <c r="X57">
+        <v>0.06742537387931463</v>
+      </c>
+      <c r="AB57">
+        <v>0.06590484276494288</v>
+      </c>
+      <c r="AD57">
+        <v>0.662</v>
+      </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>0.662</v>
+      </c>
+      <c r="AG57">
+        <v>-0.678</v>
+      </c>
+      <c r="AH57">
+        <v>0.06540209444773759</v>
+      </c>
+      <c r="AI57">
+        <v>0.07503967354341419</v>
+      </c>
+      <c r="AJ57">
+        <v>-0.07720337053063084</v>
+      </c>
+      <c r="AK57">
+        <v>-0.09061748195669607</v>
+      </c>
+      <c r="AL57">
+        <v>0.033</v>
+      </c>
+      <c r="AM57">
+        <v>0.032</v>
+      </c>
+      <c r="AO57">
+        <v>-1.03030303030303</v>
+      </c>
+      <c r="AQ57">
+        <v>-1.0625</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Yuanta 10 SPECIAL PURPOSE ACQUISITION COMPANY Co., Ltd. (KOSDAQ:A435380)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K58">
+        <v>0.218</v>
+      </c>
+      <c r="M58">
+        <v>-0</v>
+      </c>
+      <c r="N58">
+        <v>-0</v>
+      </c>
+      <c r="O58">
+        <v>-0</v>
+      </c>
+      <c r="P58">
+        <v>-0</v>
+      </c>
+      <c r="Q58">
+        <v>-0</v>
+      </c>
+      <c r="R58">
+        <v>-0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0.181</v>
+      </c>
+      <c r="V58">
+        <v>0.01973827699018539</v>
+      </c>
+      <c r="X58">
+        <v>0.06844483714407042</v>
+      </c>
+      <c r="AB58">
+        <v>0.0658454921649959</v>
+      </c>
+      <c r="AD58">
+        <v>1.1</v>
+      </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>1.1</v>
+      </c>
+      <c r="AG58">
+        <v>0.919</v>
+      </c>
+      <c r="AH58">
+        <v>0.1071080817916261</v>
+      </c>
+      <c r="AI58">
+        <v>0.1132852729145211</v>
+      </c>
+      <c r="AJ58">
+        <v>0.09108930518386361</v>
+      </c>
+      <c r="AK58">
+        <v>0.09644243887081541</v>
+      </c>
+      <c r="AL58">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="AM58">
+        <v>-0.328</v>
+      </c>
+      <c r="AO58">
+        <v>-0.7222222222222222</v>
+      </c>
+      <c r="AQ58">
+        <v>0.1585365853658536</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Hana 27 Special Purpose Acquisition Company (KOSDAQ:A448370)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K59">
+        <v>-0.036</v>
+      </c>
+      <c r="M59">
+        <v>-0</v>
+      </c>
+      <c r="N59">
+        <v>-0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>-0</v>
+      </c>
+      <c r="Q59">
+        <v>-0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0.286</v>
+      </c>
+      <c r="V59">
+        <v>0.03209876543209876</v>
+      </c>
+      <c r="X59">
+        <v>0.06837887684090989</v>
+      </c>
+      <c r="AB59">
+        <v>0.06584917147172911</v>
+      </c>
+      <c r="AD59">
+        <v>1.04</v>
+      </c>
+      <c r="AE59">
+        <v>0</v>
+      </c>
+      <c r="AF59">
+        <v>1.04</v>
+      </c>
+      <c r="AG59">
+        <v>0.754</v>
+      </c>
+      <c r="AH59">
+        <v>0.1045226130653266</v>
+      </c>
+      <c r="AI59">
+        <v>0.1145374449339207</v>
+      </c>
+      <c r="AJ59">
+        <v>0.07802152317880795</v>
+      </c>
+      <c r="AK59">
+        <v>0.08574027746190586</v>
+      </c>
+      <c r="AL59">
+        <v>0.042</v>
+      </c>
+      <c r="AM59">
+        <v>0.006000000000000005</v>
+      </c>
+      <c r="AO59">
+        <v>-0.8095238095238095</v>
+      </c>
+      <c r="AQ59">
+        <v>-5.666666666666662</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Shinyoung HappyTomorrow No.9 Special Purpose Acquisition Company (KOSDAQ:A445970)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K60">
+        <v>-0.058</v>
+      </c>
+      <c r="M60">
+        <v>-0</v>
+      </c>
+      <c r="N60">
+        <v>-0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>-0</v>
+      </c>
+      <c r="Q60">
+        <v>-0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>1.48</v>
+      </c>
+      <c r="V60">
+        <v>0.1691428571428572</v>
+      </c>
+      <c r="X60">
+        <v>0.06877210190950081</v>
+      </c>
+      <c r="AB60">
+        <v>0.06582754690943571</v>
+      </c>
+      <c r="AD60">
+        <v>1.19</v>
+      </c>
+      <c r="AE60">
+        <v>0</v>
+      </c>
+      <c r="AF60">
+        <v>1.19</v>
+      </c>
+      <c r="AG60">
+        <v>-0.29</v>
+      </c>
+      <c r="AH60">
+        <v>0.1197183098591549</v>
+      </c>
+      <c r="AI60">
+        <v>0.1280947255113025</v>
+      </c>
+      <c r="AJ60">
+        <v>-0.03427895981087471</v>
+      </c>
+      <c r="AK60">
+        <v>-0.03713188220230475</v>
+      </c>
+      <c r="AL60">
+        <v>0.052</v>
+      </c>
+      <c r="AM60">
+        <v>0.02</v>
+      </c>
+      <c r="AO60">
+        <v>-1.192307692307692</v>
+      </c>
+      <c r="AQ60">
+        <v>-3.100000000000001</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Yuanta 9 SPECIAL PURPOSE ACQUISITION COMPANY (KOSDAQ:A430700)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K61">
+        <v>0.194</v>
+      </c>
+      <c r="M61">
+        <v>-0</v>
+      </c>
+      <c r="N61">
+        <v>-0</v>
+      </c>
+      <c r="O61">
+        <v>-0</v>
+      </c>
+      <c r="P61">
+        <v>-0</v>
+      </c>
+      <c r="Q61">
+        <v>-0</v>
+      </c>
+      <c r="R61">
+        <v>-0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>0.039</v>
+      </c>
+      <c r="V61">
+        <v>0.004529616724738676</v>
+      </c>
+      <c r="X61">
+        <v>0.06865136970314586</v>
+      </c>
+      <c r="AB61">
+        <v>0.06583410783263408</v>
+      </c>
+      <c r="AD61">
+        <v>1.12</v>
+      </c>
+      <c r="AE61">
+        <v>0</v>
+      </c>
+      <c r="AF61">
+        <v>1.12</v>
+      </c>
+      <c r="AG61">
+        <v>1.081</v>
+      </c>
+      <c r="AH61">
+        <v>0.1151079136690648</v>
+      </c>
+      <c r="AI61">
+        <v>0.1248606465997771</v>
+      </c>
+      <c r="AJ61">
+        <v>0.1115467959962852</v>
+      </c>
+      <c r="AK61">
+        <v>0.1210390773709551</v>
+      </c>
+      <c r="AL61">
+        <v>0.06</v>
+      </c>
+      <c r="AM61">
+        <v>-0.267</v>
+      </c>
+      <c r="AO61">
+        <v>-0.6166666666666667</v>
+      </c>
+      <c r="AQ61">
+        <v>0.1385767790262172</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>NH Special Purpose Acquisition 24 Company (KOSDAQ:A437780)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K62">
+        <v>0.049</v>
+      </c>
+      <c r="M62">
+        <v>-0</v>
+      </c>
+      <c r="N62">
+        <v>-0</v>
+      </c>
+      <c r="O62">
+        <v>-0</v>
+      </c>
+      <c r="P62">
+        <v>-0</v>
+      </c>
+      <c r="Q62">
+        <v>-0</v>
+      </c>
+      <c r="R62">
+        <v>-0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>0.202</v>
+      </c>
+      <c r="V62">
+        <v>0.02454434993924666</v>
+      </c>
+      <c r="X62">
+        <v>0.06705129679152287</v>
+      </c>
+      <c r="AB62">
+        <v>0.06592803531548699</v>
+      </c>
+      <c r="AD62">
+        <v>0.425</v>
+      </c>
+      <c r="AE62">
+        <v>0</v>
+      </c>
+      <c r="AF62">
+        <v>0.425</v>
+      </c>
+      <c r="AG62">
+        <v>0.223</v>
+      </c>
+      <c r="AH62">
+        <v>0.04910456383593298</v>
+      </c>
+      <c r="AI62">
+        <v>0.0568561872909699</v>
+      </c>
+      <c r="AJ62">
+        <v>0.02638116644978114</v>
+      </c>
+      <c r="AK62">
+        <v>0.03066135019936752</v>
+      </c>
+      <c r="AL62">
+        <v>0.015</v>
+      </c>
+      <c r="AM62">
+        <v>-0.1</v>
+      </c>
+      <c r="AO62">
+        <v>-2.466666666666667</v>
+      </c>
+      <c r="AQ62">
+        <v>0.3699999999999999</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Mirae Asset Vision Special Purpose Acquisition 2 Company (KOSDAQ:A446190)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K63">
+        <v>-0.029</v>
+      </c>
+      <c r="M63">
+        <v>-0</v>
+      </c>
+      <c r="N63">
+        <v>-0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>-0</v>
+      </c>
+      <c r="Q63">
+        <v>-0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>0.064</v>
+      </c>
+      <c r="V63">
+        <v>0.007901234567901235</v>
+      </c>
+      <c r="X63">
+        <v>0.06962430323421134</v>
+      </c>
+      <c r="AB63">
+        <v>0.06578311138045487</v>
+      </c>
+      <c r="AD63">
+        <v>1.44</v>
+      </c>
+      <c r="AE63">
+        <v>0</v>
+      </c>
+      <c r="AF63">
+        <v>1.44</v>
+      </c>
+      <c r="AG63">
+        <v>1.376</v>
+      </c>
+      <c r="AH63">
+        <v>0.1509433962264151</v>
+      </c>
+      <c r="AI63">
+        <v>0.1623449830890643</v>
+      </c>
+      <c r="AJ63">
+        <v>0.1452089489235965</v>
+      </c>
+      <c r="AK63">
+        <v>0.156257097433568</v>
+      </c>
+      <c r="AL63">
+        <v>0.059</v>
+      </c>
+      <c r="AM63">
+        <v>0.011</v>
+      </c>
+      <c r="AO63">
+        <v>-0.4237288135593221</v>
+      </c>
+      <c r="AQ63">
+        <v>-2.272727272727274</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>HI Special purpose Acquisition Company 8 Co., Ltd. (KOSDAQ:A450050)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K64">
+        <v>-0.057</v>
+      </c>
+      <c r="M64">
+        <v>-0</v>
+      </c>
+      <c r="N64">
+        <v>-0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>-0</v>
+      </c>
+      <c r="Q64">
+        <v>-0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>1.34</v>
+      </c>
+      <c r="V64">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="X64">
+        <v>0.067710469876578</v>
+      </c>
+      <c r="AB64">
+        <v>0.06588769393801061</v>
+      </c>
+      <c r="AD64">
+        <v>0.675</v>
+      </c>
+      <c r="AE64">
+        <v>0</v>
+      </c>
+      <c r="AF64">
+        <v>0.675</v>
+      </c>
+      <c r="AG64">
+        <v>-0.665</v>
+      </c>
+      <c r="AH64">
+        <v>0.0774526678141136</v>
+      </c>
+      <c r="AI64">
+        <v>0.08817766165904638</v>
+      </c>
+      <c r="AJ64">
+        <v>-0.09016949152542375</v>
+      </c>
+      <c r="AK64">
+        <v>-0.105304829770388</v>
+      </c>
+      <c r="AL64">
+        <v>0.026</v>
+      </c>
+      <c r="AM64">
+        <v>0.026</v>
+      </c>
+      <c r="AO64">
+        <v>-1.807692307692308</v>
+      </c>
+      <c r="AQ64">
+        <v>-1.807692307692308</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Mirae Asset Vision Special Purpose Acquisition 3 Company (KOSDAQ:A448830)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K65">
+        <v>-0.093</v>
+      </c>
+      <c r="M65">
+        <v>-0</v>
+      </c>
+      <c r="N65">
+        <v>-0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>-0</v>
+      </c>
+      <c r="Q65">
+        <v>-0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0.296</v>
+      </c>
+      <c r="V65">
+        <v>0.03695380774032459</v>
+      </c>
+      <c r="X65">
+        <v>0.06984331265904134</v>
+      </c>
+      <c r="AB65">
+        <v>0.06577219635247519</v>
+      </c>
+      <c r="AD65">
+        <v>1.51</v>
+      </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>1.51</v>
+      </c>
+      <c r="AG65">
+        <v>1.214</v>
+      </c>
+      <c r="AH65">
+        <v>0.1586134453781513</v>
+      </c>
+      <c r="AI65">
+        <v>0.1713961407491487</v>
+      </c>
+      <c r="AJ65">
+        <v>0.1316131830008673</v>
+      </c>
+      <c r="AK65">
+        <v>0.1425886774723984</v>
+      </c>
+      <c r="AL65">
+        <v>0.082</v>
+      </c>
+      <c r="AM65">
+        <v>0.08</v>
+      </c>
+      <c r="AO65">
+        <v>-0.4634146341463414</v>
+      </c>
+      <c r="AQ65">
+        <v>-0.475</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>IBKS No.20 Special Purpose Acquisition Company (KOSDAQ:A439730)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K66">
+        <v>0.008</v>
+      </c>
+      <c r="M66">
+        <v>-0</v>
+      </c>
+      <c r="N66">
+        <v>-0</v>
+      </c>
+      <c r="O66">
+        <v>-0</v>
+      </c>
+      <c r="P66">
+        <v>-0</v>
+      </c>
+      <c r="Q66">
+        <v>-0</v>
+      </c>
+      <c r="R66">
+        <v>-0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>1.3</v>
+      </c>
+      <c r="V66">
+        <v>0.1645569620253164</v>
+      </c>
+      <c r="X66">
+        <v>0.06876074075529311</v>
+      </c>
+      <c r="AB66">
+        <v>0.06582816139064721</v>
+      </c>
+      <c r="AD66">
+        <v>1.07</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>1.07</v>
+      </c>
+      <c r="AG66">
+        <v>-0.23</v>
+      </c>
+      <c r="AH66">
+        <v>0.1192865105908584</v>
+      </c>
+      <c r="AI66">
+        <v>0.1440107671601615</v>
+      </c>
+      <c r="AJ66">
+        <v>-0.02998696219035202</v>
+      </c>
+      <c r="AK66">
+        <v>-0.03752039151712887</v>
+      </c>
+      <c r="AL66">
+        <v>0.04</v>
+      </c>
+      <c r="AM66">
+        <v>-0.055</v>
+      </c>
+      <c r="AO66">
+        <v>-1.15</v>
+      </c>
+      <c r="AQ66">
+        <v>0.8363636363636363</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Yuanta 12 Special Purpose Acquisition Company (KOSDAQ:A446150)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K67">
+        <v>-0.048</v>
+      </c>
+      <c r="M67">
+        <v>-0</v>
+      </c>
+      <c r="N67">
+        <v>-0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>-0</v>
+      </c>
+      <c r="Q67">
+        <v>-0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0.102</v>
+      </c>
+      <c r="V67">
+        <v>0.01326397919375813</v>
+      </c>
+      <c r="X67">
+        <v>0.06787329748271544</v>
+      </c>
+      <c r="AB67">
+        <v>0.06587809664578485</v>
+      </c>
+      <c r="AD67">
+        <v>0.707</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0.707</v>
+      </c>
+      <c r="AG67">
+        <v>0.605</v>
+      </c>
+      <c r="AH67">
+        <v>0.08419673692985589</v>
+      </c>
+      <c r="AI67">
+        <v>0.09161591291952831</v>
+      </c>
+      <c r="AJ67">
+        <v>0.07293550331525014</v>
+      </c>
+      <c r="AK67">
+        <v>0.0794484569927774</v>
+      </c>
+      <c r="AL67">
+        <v>0.027</v>
+      </c>
+      <c r="AM67">
+        <v>0.017</v>
+      </c>
+      <c r="AO67">
+        <v>-1.62962962962963</v>
+      </c>
+      <c r="AQ67">
+        <v>-2.588235294117647</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>IBKS No.22 Special Purpose Acquisition Company (KOSDAQ:A448760)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K68">
+        <v>-0.083</v>
+      </c>
+      <c r="M68">
+        <v>-0</v>
+      </c>
+      <c r="N68">
+        <v>-0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>-0</v>
+      </c>
+      <c r="Q68">
+        <v>-0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>1.32</v>
+      </c>
+      <c r="V68">
+        <v>0.1734559789750328</v>
+      </c>
+      <c r="X68">
+        <v>0.0684666346608232</v>
+      </c>
+      <c r="AB68">
+        <v>0.06584428095216227</v>
+      </c>
+      <c r="AD68">
+        <v>0.921</v>
+      </c>
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>0.921</v>
+      </c>
+      <c r="AG68">
+        <v>-0.399</v>
+      </c>
+      <c r="AH68">
+        <v>0.107959207595827</v>
+      </c>
+      <c r="AI68">
+        <v>0.1256308825535398</v>
+      </c>
+      <c r="AJ68">
+        <v>-0.05533213146581611</v>
+      </c>
+      <c r="AK68">
+        <v>-0.06637830643819664</v>
+      </c>
+      <c r="AL68">
+        <v>0.034</v>
+      </c>
+      <c r="AM68">
+        <v>0.033</v>
+      </c>
+      <c r="AO68">
+        <v>-1.735294117647059</v>
+      </c>
+      <c r="AQ68">
+        <v>-1.787878787878788</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>IBKS No.21 Special Purpose Acquisition Company (KOSDAQ:A442770)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K69">
+        <v>-0.048</v>
+      </c>
+      <c r="M69">
+        <v>-0</v>
+      </c>
+      <c r="N69">
+        <v>-0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>-0</v>
+      </c>
+      <c r="Q69">
+        <v>-0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>1.32</v>
+      </c>
+      <c r="V69">
+        <v>0.1810699588477366</v>
+      </c>
+      <c r="X69">
+        <v>0.06910384931250081</v>
+      </c>
+      <c r="AB69">
+        <v>0.06580986589089807</v>
+      </c>
+      <c r="AD69">
+        <v>1.11</v>
+      </c>
+      <c r="AE69">
+        <v>0</v>
+      </c>
+      <c r="AF69">
+        <v>1.11</v>
+      </c>
+      <c r="AG69">
+        <v>-0.21</v>
+      </c>
+      <c r="AH69">
+        <v>0.1321428571428571</v>
+      </c>
+      <c r="AI69">
+        <v>0.15</v>
+      </c>
+      <c r="AJ69">
+        <v>-0.02966101694915254</v>
+      </c>
+      <c r="AK69">
+        <v>-0.03453947368421052</v>
+      </c>
+      <c r="AL69">
+        <v>0.041</v>
+      </c>
+      <c r="AM69">
+        <v>0.001000000000000001</v>
+      </c>
+      <c r="AO69">
+        <v>-1.48780487804878</v>
+      </c>
+      <c r="AQ69">
+        <v>-60.99999999999994</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Yuanta 14 SPECIAL PURPOSE ACQUISITION COMPANY (KOSDAQ:A450940)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K70">
+        <v>-0.096</v>
+      </c>
+      <c r="M70">
+        <v>-0</v>
+      </c>
+      <c r="N70">
+        <v>-0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>-0</v>
+      </c>
+      <c r="Q70">
+        <v>-0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>0.241</v>
+      </c>
+      <c r="V70">
+        <v>0.03347222222222222</v>
+      </c>
+      <c r="X70">
+        <v>0.0700492706501242</v>
+      </c>
+      <c r="AB70">
+        <v>0.06576211019481935</v>
+      </c>
+      <c r="AD70">
+        <v>1.43</v>
+      </c>
+      <c r="AE70">
+        <v>0</v>
+      </c>
+      <c r="AF70">
+        <v>1.43</v>
+      </c>
+      <c r="AG70">
+        <v>1.189</v>
+      </c>
+      <c r="AH70">
+        <v>0.1657010428736964</v>
+      </c>
+      <c r="AI70">
+        <v>0.1780821917808219</v>
+      </c>
+      <c r="AJ70">
+        <v>0.1417332220765288</v>
+      </c>
+      <c r="AK70">
+        <v>0.1526511747335987</v>
+      </c>
+      <c r="AL70">
+        <v>0.035</v>
+      </c>
+      <c r="AM70">
+        <v>0.035</v>
+      </c>
+      <c r="AO70">
+        <v>-2.485714285714285</v>
+      </c>
+      <c r="AQ70">
+        <v>-2.485714285714285</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Bnk 1 Special Purpose Acquisition Company (KOSDAQ:A445360)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K71">
+        <v>-0.031</v>
+      </c>
+      <c r="M71">
+        <v>-0</v>
+      </c>
+      <c r="N71">
+        <v>-0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>-0</v>
+      </c>
+      <c r="Q71">
+        <v>-0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="U71">
+        <v>0.151</v>
+      </c>
+      <c r="V71">
+        <v>0.02150997150997151</v>
+      </c>
+      <c r="X71">
+        <v>0.06842422430927458</v>
+      </c>
+      <c r="AB71">
+        <v>0.06584663967736154</v>
+      </c>
+      <c r="AD71">
+        <v>0.835</v>
+      </c>
+      <c r="AE71">
+        <v>0</v>
+      </c>
+      <c r="AF71">
+        <v>0.835</v>
+      </c>
+      <c r="AG71">
+        <v>0.6839999999999999</v>
+      </c>
+      <c r="AH71">
+        <v>0.1063017186505411</v>
+      </c>
+      <c r="AI71">
+        <v>0.1147766323024055</v>
+      </c>
+      <c r="AJ71">
+        <v>0.08878504672897196</v>
+      </c>
+      <c r="AK71">
+        <v>0.09601347557551936</v>
+      </c>
+      <c r="AL71">
+        <v>0.037</v>
+      </c>
+      <c r="AM71">
+        <v>-0.01</v>
+      </c>
+      <c r="AO71">
+        <v>-1.324324324324324</v>
+      </c>
+      <c r="AQ71">
+        <v>4.899999999999999</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Kyobo 13 Special Purpose Acquisition Company (KOSDAQ:A440790)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K72">
+        <v>-0.018</v>
+      </c>
+      <c r="M72">
+        <v>-0</v>
+      </c>
+      <c r="N72">
+        <v>-0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>-0</v>
+      </c>
+      <c r="Q72">
+        <v>-0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>1.62</v>
+      </c>
+      <c r="V72">
+        <v>0.242152466367713</v>
+      </c>
+      <c r="X72">
+        <v>0.0701141909339901</v>
+      </c>
+      <c r="AB72">
+        <v>0.06575896605379908</v>
+      </c>
+      <c r="AD72">
+        <v>1.35</v>
+      </c>
+      <c r="AE72">
+        <v>0</v>
+      </c>
+      <c r="AF72">
+        <v>1.35</v>
+      </c>
+      <c r="AG72">
+        <v>-0.27</v>
+      </c>
+      <c r="AH72">
+        <v>0.167910447761194</v>
+      </c>
+      <c r="AI72">
+        <v>0.1812080536912752</v>
+      </c>
+      <c r="AJ72">
+        <v>-0.04205607476635514</v>
+      </c>
+      <c r="AK72">
+        <v>-0.04631217838765009</v>
+      </c>
+      <c r="AL72">
+        <v>0.048</v>
+      </c>
+      <c r="AM72">
+        <v>-0.047</v>
+      </c>
+      <c r="AO72">
+        <v>-1.395833333333333</v>
+      </c>
+      <c r="AQ72">
+        <v>1.425531914893617</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Eugene Special Purpose Acquisitions 9 Company (KOSDAQ:A442130)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K73">
+        <v>-0.003</v>
+      </c>
+      <c r="M73">
+        <v>-0</v>
+      </c>
+      <c r="N73">
+        <v>-0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>-0</v>
+      </c>
+      <c r="Q73">
+        <v>-0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="U73">
+        <v>0.988</v>
+      </c>
+      <c r="V73">
+        <v>0.1652173913043478</v>
+      </c>
+      <c r="X73">
+        <v>0.06859718020444654</v>
+      </c>
+      <c r="AB73">
+        <v>0.06583707503876196</v>
+      </c>
+      <c r="AD73">
+        <v>0.762</v>
+      </c>
+      <c r="AE73">
+        <v>0</v>
+      </c>
+      <c r="AF73">
+        <v>0.762</v>
+      </c>
+      <c r="AG73">
+        <v>-0.226</v>
+      </c>
+      <c r="AH73">
+        <v>0.1130228418866805</v>
+      </c>
+      <c r="AI73">
+        <v>0.1284558327714093</v>
+      </c>
+      <c r="AJ73">
+        <v>-0.03927702467848453</v>
+      </c>
+      <c r="AK73">
+        <v>-0.04571197411003236</v>
+      </c>
+      <c r="AL73">
+        <v>0.039</v>
+      </c>
+      <c r="AM73">
+        <v>-0.026</v>
+      </c>
+      <c r="AO73">
+        <v>-1.128205128205128</v>
+      </c>
+      <c r="AQ73">
+        <v>1.692307692307692</v>
       </c>
     </row>
   </sheetData>
